--- a/research/traditional_assets/database/data/denmark/denmark_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_farming_agriculture.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="cpse_ffarms" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,43 +590,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.21</v>
+        <v>0.187</v>
       </c>
       <c r="G2">
-        <v>0.1928166351606805</v>
+        <v>0.2610294117647059</v>
       </c>
       <c r="H2">
-        <v>0.1928166351606805</v>
+        <v>0.2610294117647059</v>
       </c>
       <c r="I2">
-        <v>-0.02722117202268431</v>
+        <v>0.2003676470588235</v>
       </c>
       <c r="J2">
-        <v>-0.01836275672038705</v>
+        <v>0.1587528280542986</v>
       </c>
       <c r="K2">
-        <v>3.98</v>
+        <v>10.3</v>
       </c>
       <c r="L2">
-        <v>0.07523629489603025</v>
+        <v>0.1893382352941177</v>
       </c>
       <c r="M2">
-        <v>0.9196200000000001</v>
+        <v>0.916</v>
       </c>
       <c r="N2">
-        <v>0.01073068844807468</v>
+        <v>0.008732125834127741</v>
       </c>
       <c r="O2">
-        <v>0.2310603015075377</v>
+        <v>0.08893203883495146</v>
       </c>
       <c r="P2">
-        <v>0.9196200000000001</v>
+        <v>0.916</v>
       </c>
       <c r="Q2">
-        <v>0.01073068844807468</v>
+        <v>0.008732125834127741</v>
       </c>
       <c r="R2">
-        <v>0.2310603015075377</v>
+        <v>0.08893203883495146</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.512</v>
+        <v>3.75</v>
       </c>
       <c r="V2">
-        <v>0.005974329054842474</v>
+        <v>0.03574833174451859</v>
       </c>
       <c r="W2">
-        <v>0.05467032967032967</v>
+        <v>0.1293969849246231</v>
       </c>
       <c r="X2">
-        <v>0.06702950223958865</v>
+        <v>0.09587266395113143</v>
       </c>
       <c r="Y2">
-        <v>-0.01235917256925897</v>
+        <v>0.03352432097349169</v>
       </c>
       <c r="Z2">
-        <v>0.3687696061345417</v>
+        <v>0.3567727803355238</v>
       </c>
       <c r="AA2">
-        <v>-0.006771626563321538</v>
+        <v>0.05663868785105947</v>
       </c>
       <c r="AB2">
-        <v>0.04410003035739397</v>
+        <v>0.07411940221704987</v>
       </c>
       <c r="AC2">
-        <v>-0.05087165692071551</v>
+        <v>-0.0174807143659904</v>
       </c>
       <c r="AD2">
-        <v>75.90000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>75.90000000000001</v>
+        <v>61.3</v>
       </c>
       <c r="AG2">
-        <v>75.38800000000001</v>
+        <v>57.55</v>
       </c>
       <c r="AH2">
-        <v>0.4696782178217822</v>
+        <v>0.3688327316486161</v>
       </c>
       <c r="AI2">
-        <v>0.4881028938906753</v>
+        <v>0.4116856950973808</v>
       </c>
       <c r="AJ2">
-        <v>0.4679926499801351</v>
+        <v>0.3542628501077255</v>
       </c>
       <c r="AK2">
-        <v>0.4864118512400961</v>
+        <v>0.3964863933861523</v>
       </c>
       <c r="AL2">
-        <v>2.62</v>
+        <v>1.52</v>
       </c>
       <c r="AM2">
-        <v>2.62</v>
+        <v>1.032</v>
       </c>
       <c r="AN2">
-        <v>16.0126582278481</v>
+        <v>3.648809523809523</v>
       </c>
       <c r="AO2">
-        <v>-0.5496183206106869</v>
+        <v>7.171052631578948</v>
       </c>
       <c r="AP2">
-        <v>15.90464135021097</v>
+        <v>3.425595238095238</v>
       </c>
       <c r="AQ2">
-        <v>-0.5496183206106869</v>
+        <v>10.56201550387597</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +721,8830 @@
         </is>
       </c>
       <c r="D3">
+        <v>0.187</v>
+      </c>
+      <c r="G3">
+        <v>0.2610294117647059</v>
+      </c>
+      <c r="H3">
+        <v>0.2610294117647059</v>
+      </c>
+      <c r="I3">
+        <v>0.2003676470588235</v>
+      </c>
+      <c r="J3">
+        <v>0.1587528280542986</v>
+      </c>
+      <c r="K3">
+        <v>10.3</v>
+      </c>
+      <c r="L3">
+        <v>0.1893382352941177</v>
+      </c>
+      <c r="M3">
+        <v>0.916</v>
+      </c>
+      <c r="N3">
+        <v>0.008732125834127741</v>
+      </c>
+      <c r="O3">
+        <v>0.08893203883495146</v>
+      </c>
+      <c r="P3">
+        <v>0.916</v>
+      </c>
+      <c r="Q3">
+        <v>0.008732125834127741</v>
+      </c>
+      <c r="R3">
+        <v>0.08893203883495146</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>3.75</v>
+      </c>
+      <c r="V3">
+        <v>0.03574833174451859</v>
+      </c>
+      <c r="W3">
+        <v>0.1293969849246231</v>
+      </c>
+      <c r="X3">
+        <v>0.09587266395113143</v>
+      </c>
+      <c r="Y3">
+        <v>0.03352432097349169</v>
+      </c>
+      <c r="Z3">
+        <v>0.3567727803355238</v>
+      </c>
+      <c r="AA3">
+        <v>0.05663868785105947</v>
+      </c>
+      <c r="AB3">
+        <v>0.07411940221704987</v>
+      </c>
+      <c r="AC3">
+        <v>-0.0174807143659904</v>
+      </c>
+      <c r="AD3">
+        <v>61.3</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>61.3</v>
+      </c>
+      <c r="AG3">
+        <v>57.55</v>
+      </c>
+      <c r="AH3">
+        <v>0.3688327316486161</v>
+      </c>
+      <c r="AI3">
+        <v>0.4116856950973808</v>
+      </c>
+      <c r="AJ3">
+        <v>0.3542628501077255</v>
+      </c>
+      <c r="AK3">
+        <v>0.3964863933861523</v>
+      </c>
+      <c r="AL3">
+        <v>1.52</v>
+      </c>
+      <c r="AM3">
+        <v>1.032</v>
+      </c>
+      <c r="AN3">
+        <v>3.648809523809523</v>
+      </c>
+      <c r="AO3">
+        <v>7.171052631578948</v>
+      </c>
+      <c r="AP3">
+        <v>3.425595238095238</v>
+      </c>
+      <c r="AQ3">
+        <v>10.56201550387597</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FirstFarms A/S (CPSE:FFARMS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CPSE:FFARMS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Farming/Agriculture</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.368832731648616</v>
+      </c>
+      <c r="F2">
+        <v>0.13</v>
+      </c>
+      <c r="G2">
+        <v>104.9</v>
+      </c>
+      <c r="H2">
+        <v>133.794946246808</v>
+      </c>
+      <c r="I2">
+        <v>162.45</v>
+      </c>
+      <c r="J2">
+        <v>151.650946246808</v>
+      </c>
+      <c r="K2">
+        <v>61.3</v>
+      </c>
+      <c r="L2">
+        <v>21.606</v>
+      </c>
+      <c r="M2">
+        <v>0.07411940221704991</v>
+      </c>
+      <c r="N2">
+        <v>0.0766344944898787</v>
+      </c>
+      <c r="O2">
+        <v>0.036894</v>
+      </c>
+      <c r="P2">
+        <v>0.036894</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.09587266395113141</v>
+      </c>
+      <c r="T2">
+        <v>0.08257272929871121</v>
+      </c>
+      <c r="U2">
+        <v>0.965004141710345</v>
+      </c>
+      <c r="V2">
+        <v>0.740124293188607</v>
+      </c>
+      <c r="W2">
+        <v>10.69509507088216</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>104.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.0473</v>
+      </c>
+      <c r="AD2">
+        <v>0.22</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>16.8</v>
+      </c>
+      <c r="AH2">
+        <v>5.87</v>
+      </c>
+      <c r="AI2">
+        <v>26.68</v>
+      </c>
+      <c r="AJ2">
+        <v>61.3</v>
+      </c>
+      <c r="AK2">
+        <v>61.3</v>
+      </c>
+      <c r="AL2">
+        <v>1.52</v>
+      </c>
+      <c r="AM2">
+        <v>61.3</v>
+      </c>
+      <c r="AN2">
+        <v>3.75</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.07800349443059371</v>
+      </c>
+      <c r="C2">
+        <v>150.1052413756821</v>
+      </c>
+      <c r="D2">
+        <v>146.3552413756821</v>
+      </c>
+      <c r="E2">
+        <v>-61.3</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>3.75</v>
+      </c>
+      <c r="H2">
+        <v>104.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>16.8</v>
+      </c>
+      <c r="K2">
+        <v>5.87</v>
+      </c>
+      <c r="L2">
+        <v>10.93</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>10.93</v>
+      </c>
+      <c r="O2">
+        <v>2.4046</v>
+      </c>
+      <c r="P2">
+        <v>8.525399999999999</v>
+      </c>
+      <c r="Q2">
+        <v>14.3954</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.07800349443059371</v>
+      </c>
+      <c r="T2">
+        <v>0.662866105697023</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.22</v>
+      </c>
+      <c r="W2">
+        <v>0.035646</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.07788570674284639</v>
+      </c>
+      <c r="C3">
+        <v>148.8842937937632</v>
+      </c>
+      <c r="D3">
+        <v>146.7962937937632</v>
+      </c>
+      <c r="E3">
+        <v>-59.638</v>
+      </c>
+      <c r="F3">
+        <v>1.662</v>
+      </c>
+      <c r="G3">
+        <v>3.75</v>
+      </c>
+      <c r="H3">
+        <v>104.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>16.8</v>
+      </c>
+      <c r="K3">
+        <v>5.87</v>
+      </c>
+      <c r="L3">
+        <v>10.93</v>
+      </c>
+      <c r="M3">
+        <v>0.0759534</v>
+      </c>
+      <c r="N3">
+        <v>10.8540466</v>
+      </c>
+      <c r="O3">
+        <v>2.387890252</v>
+      </c>
+      <c r="P3">
+        <v>8.466156348</v>
+      </c>
+      <c r="Q3">
+        <v>14.336156348</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.07831237044731959</v>
+      </c>
+      <c r="T3">
+        <v>0.668088687135848</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.22</v>
+      </c>
+      <c r="W3">
+        <v>0.035646</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>143.9040253629199</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.07776791905509911</v>
+      </c>
+      <c r="C4">
+        <v>147.6660125356182</v>
+      </c>
+      <c r="D4">
+        <v>147.2400125356182</v>
+      </c>
+      <c r="E4">
+        <v>-57.976</v>
+      </c>
+      <c r="F4">
+        <v>3.324</v>
+      </c>
+      <c r="G4">
+        <v>3.75</v>
+      </c>
+      <c r="H4">
+        <v>104.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>16.8</v>
+      </c>
+      <c r="K4">
+        <v>5.87</v>
+      </c>
+      <c r="L4">
+        <v>10.93</v>
+      </c>
+      <c r="M4">
+        <v>0.1519068</v>
+      </c>
+      <c r="N4">
+        <v>10.7780932</v>
+      </c>
+      <c r="O4">
+        <v>2.371180503999999</v>
+      </c>
+      <c r="P4">
+        <v>8.406912695999999</v>
+      </c>
+      <c r="Q4">
+        <v>14.276912696</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.07862755005622357</v>
+      </c>
+      <c r="T4">
+        <v>0.6734178518693429</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.22</v>
+      </c>
+      <c r="W4">
+        <v>0.035646</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>71.95201268145993</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.07765013136735179</v>
+      </c>
+      <c r="C5">
+        <v>146.4504218529116</v>
+      </c>
+      <c r="D5">
+        <v>147.6864218529116</v>
+      </c>
+      <c r="E5">
+        <v>-56.314</v>
+      </c>
+      <c r="F5">
+        <v>4.986</v>
+      </c>
+      <c r="G5">
+        <v>3.75</v>
+      </c>
+      <c r="H5">
+        <v>104.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>16.8</v>
+      </c>
+      <c r="K5">
+        <v>5.87</v>
+      </c>
+      <c r="L5">
+        <v>10.93</v>
+      </c>
+      <c r="M5">
+        <v>0.2278602</v>
+      </c>
+      <c r="N5">
+        <v>10.7021398</v>
+      </c>
+      <c r="O5">
+        <v>2.354470756</v>
+      </c>
+      <c r="P5">
+        <v>8.347669044</v>
+      </c>
+      <c r="Q5">
+        <v>14.217669044</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.07894922821376474</v>
+      </c>
+      <c r="T5">
+        <v>0.6788568962880646</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.22</v>
+      </c>
+      <c r="W5">
+        <v>0.035646</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>47.96800845430663</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.07753234367960447</v>
+      </c>
+      <c r="C6">
+        <v>145.2375462923111</v>
+      </c>
+      <c r="D6">
+        <v>148.1355462923111</v>
+      </c>
+      <c r="E6">
+        <v>-54.652</v>
+      </c>
+      <c r="F6">
+        <v>6.648</v>
+      </c>
+      <c r="G6">
+        <v>3.75</v>
+      </c>
+      <c r="H6">
+        <v>104.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>16.8</v>
+      </c>
+      <c r="K6">
+        <v>5.87</v>
+      </c>
+      <c r="L6">
+        <v>10.93</v>
+      </c>
+      <c r="M6">
+        <v>0.3038136</v>
+      </c>
+      <c r="N6">
+        <v>10.6261864</v>
+      </c>
+      <c r="O6">
+        <v>2.337761008</v>
+      </c>
+      <c r="P6">
+        <v>8.288425392000001</v>
+      </c>
+      <c r="Q6">
+        <v>14.158425392</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.079277607999588</v>
+      </c>
+      <c r="T6">
+        <v>0.6844092541321762</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.22</v>
+      </c>
+      <c r="W6">
+        <v>0.035646</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>35.97600634072997</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.07741455599185718</v>
+      </c>
+      <c r="C7">
+        <v>144.0274106999876</v>
+      </c>
+      <c r="D7">
+        <v>148.5874106999876</v>
+      </c>
+      <c r="E7">
+        <v>-52.98999999999999</v>
+      </c>
+      <c r="F7">
+        <v>8.31</v>
+      </c>
+      <c r="G7">
+        <v>3.75</v>
+      </c>
+      <c r="H7">
+        <v>104.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>16.8</v>
+      </c>
+      <c r="K7">
+        <v>5.87</v>
+      </c>
+      <c r="L7">
+        <v>10.93</v>
+      </c>
+      <c r="M7">
+        <v>0.3797670000000001</v>
+      </c>
+      <c r="N7">
+        <v>10.550233</v>
+      </c>
+      <c r="O7">
+        <v>2.32105126</v>
+      </c>
+      <c r="P7">
+        <v>8.229181740000001</v>
+      </c>
+      <c r="Q7">
+        <v>14.09918174</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.07961290104406019</v>
+      </c>
+      <c r="T7">
+        <v>0.6900785037203745</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.22</v>
+      </c>
+      <c r="W7">
+        <v>0.035646</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>28.78080507258397</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.07729676830410986</v>
+      </c>
+      <c r="C8">
+        <v>142.8200402261976</v>
+      </c>
+      <c r="D8">
+        <v>149.0420402261976</v>
+      </c>
+      <c r="E8">
+        <v>-51.328</v>
+      </c>
+      <c r="F8">
+        <v>9.972</v>
+      </c>
+      <c r="G8">
+        <v>3.75</v>
+      </c>
+      <c r="H8">
+        <v>104.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>16.8</v>
+      </c>
+      <c r="K8">
+        <v>5.87</v>
+      </c>
+      <c r="L8">
+        <v>10.93</v>
+      </c>
+      <c r="M8">
+        <v>0.4557204</v>
+      </c>
+      <c r="N8">
+        <v>10.4742796</v>
+      </c>
+      <c r="O8">
+        <v>2.304341512</v>
+      </c>
+      <c r="P8">
+        <v>8.169938087999999</v>
+      </c>
+      <c r="Q8">
+        <v>14.039938088</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.0799553279830956</v>
+      </c>
+      <c r="T8">
+        <v>0.6958683756402364</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.22</v>
+      </c>
+      <c r="W8">
+        <v>0.035646</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>23.98400422715331</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.07717898061636257</v>
+      </c>
+      <c r="C9">
+        <v>141.6154603299483</v>
+      </c>
+      <c r="D9">
+        <v>149.4994603299483</v>
+      </c>
+      <c r="E9">
+        <v>-49.666</v>
+      </c>
+      <c r="F9">
+        <v>11.634</v>
+      </c>
+      <c r="G9">
+        <v>3.75</v>
+      </c>
+      <c r="H9">
+        <v>104.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>16.8</v>
+      </c>
+      <c r="K9">
+        <v>5.87</v>
+      </c>
+      <c r="L9">
+        <v>10.93</v>
+      </c>
+      <c r="M9">
+        <v>0.5316738000000001</v>
+      </c>
+      <c r="N9">
+        <v>10.3983262</v>
+      </c>
+      <c r="O9">
+        <v>2.287631763999999</v>
+      </c>
+      <c r="P9">
+        <v>8.110694435999999</v>
+      </c>
+      <c r="Q9">
+        <v>13.980694436</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08030511894232534</v>
+      </c>
+      <c r="T9">
+        <v>0.7017827609347193</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.22</v>
+      </c>
+      <c r="W9">
+        <v>0.035646</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>20.55771790898855</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.07706119292861525</v>
+      </c>
+      <c r="C10">
+        <v>140.4136967837512</v>
+      </c>
+      <c r="D10">
+        <v>149.9596967837512</v>
+      </c>
+      <c r="E10">
+        <v>-48.004</v>
+      </c>
+      <c r="F10">
+        <v>13.296</v>
+      </c>
+      <c r="G10">
+        <v>3.75</v>
+      </c>
+      <c r="H10">
+        <v>104.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>16.8</v>
+      </c>
+      <c r="K10">
+        <v>5.87</v>
+      </c>
+      <c r="L10">
+        <v>10.93</v>
+      </c>
+      <c r="M10">
+        <v>0.6076272</v>
+      </c>
+      <c r="N10">
+        <v>10.3223728</v>
+      </c>
+      <c r="O10">
+        <v>2.270922016</v>
+      </c>
+      <c r="P10">
+        <v>8.051450784</v>
+      </c>
+      <c r="Q10">
+        <v>13.921450784</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08066251405284267</v>
+      </c>
+      <c r="T10">
+        <v>0.7078257198225602</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.22</v>
+      </c>
+      <c r="W10">
+        <v>0.035646</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>17.98800317036499</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.07694340524086796</v>
+      </c>
+      <c r="C11">
+        <v>139.214775678462</v>
+      </c>
+      <c r="D11">
+        <v>150.422775678462</v>
+      </c>
+      <c r="E11">
+        <v>-46.342</v>
+      </c>
+      <c r="F11">
+        <v>14.958</v>
+      </c>
+      <c r="G11">
+        <v>3.75</v>
+      </c>
+      <c r="H11">
+        <v>104.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>16.8</v>
+      </c>
+      <c r="K11">
+        <v>5.87</v>
+      </c>
+      <c r="L11">
+        <v>10.93</v>
+      </c>
+      <c r="M11">
+        <v>0.6835806</v>
+      </c>
+      <c r="N11">
+        <v>10.2464194</v>
+      </c>
+      <c r="O11">
+        <v>2.254212268</v>
+      </c>
+      <c r="P11">
+        <v>7.992207132000001</v>
+      </c>
+      <c r="Q11">
+        <v>13.862207132</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08102776400095379</v>
+      </c>
+      <c r="T11">
+        <v>0.7140014909936505</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.22</v>
+      </c>
+      <c r="W11">
+        <v>0.035646</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>15.98933615143554</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.07682561755312065</v>
+      </c>
+      <c r="C12">
+        <v>138.0187234282111</v>
+      </c>
+      <c r="D12">
+        <v>150.8887234282111</v>
+      </c>
+      <c r="E12">
+        <v>-44.67999999999999</v>
+      </c>
+      <c r="F12">
+        <v>16.62</v>
+      </c>
+      <c r="G12">
+        <v>3.75</v>
+      </c>
+      <c r="H12">
+        <v>104.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>16.8</v>
+      </c>
+      <c r="K12">
+        <v>5.87</v>
+      </c>
+      <c r="L12">
+        <v>10.93</v>
+      </c>
+      <c r="M12">
+        <v>0.7595340000000002</v>
+      </c>
+      <c r="N12">
+        <v>10.170466</v>
+      </c>
+      <c r="O12">
+        <v>2.23750252</v>
+      </c>
+      <c r="P12">
+        <v>7.93296348</v>
+      </c>
+      <c r="Q12">
+        <v>13.80296348</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08140113061457849</v>
+      </c>
+      <c r="T12">
+        <v>0.7203145015240983</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.22</v>
+      </c>
+      <c r="W12">
+        <v>0.035646</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>14.39040253629199</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.07670782986537335</v>
+      </c>
+      <c r="C13">
+        <v>136.8255667754264</v>
+      </c>
+      <c r="D13">
+        <v>151.3575667754264</v>
+      </c>
+      <c r="E13">
+        <v>-43.018</v>
+      </c>
+      <c r="F13">
+        <v>18.282</v>
+      </c>
+      <c r="G13">
+        <v>3.75</v>
+      </c>
+      <c r="H13">
+        <v>104.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>16.8</v>
+      </c>
+      <c r="K13">
+        <v>5.87</v>
+      </c>
+      <c r="L13">
+        <v>10.93</v>
+      </c>
+      <c r="M13">
+        <v>0.8354874000000001</v>
+      </c>
+      <c r="N13">
+        <v>10.0945126</v>
+      </c>
+      <c r="O13">
+        <v>2.220792772</v>
+      </c>
+      <c r="P13">
+        <v>7.873719828</v>
+      </c>
+      <c r="Q13">
+        <v>13.743719828</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08178288748918353</v>
+      </c>
+      <c r="T13">
+        <v>0.7267693774597248</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.22</v>
+      </c>
+      <c r="W13">
+        <v>0.035646</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>13.08218412390181</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.07673980217762605</v>
+      </c>
+      <c r="C14">
+        <v>135.0360159947424</v>
+      </c>
+      <c r="D14">
+        <v>151.2300159947424</v>
+      </c>
+      <c r="E14">
+        <v>-41.35599999999999</v>
+      </c>
+      <c r="F14">
+        <v>19.944</v>
+      </c>
+      <c r="G14">
+        <v>3.75</v>
+      </c>
+      <c r="H14">
+        <v>104.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>16.8</v>
+      </c>
+      <c r="K14">
+        <v>5.87</v>
+      </c>
+      <c r="L14">
+        <v>10.93</v>
+      </c>
+      <c r="M14">
+        <v>0.9433511999999999</v>
+      </c>
+      <c r="N14">
+        <v>9.986648799999999</v>
+      </c>
+      <c r="O14">
+        <v>2.197062735999999</v>
+      </c>
+      <c r="P14">
+        <v>7.789586064</v>
+      </c>
+      <c r="Q14">
+        <v>13.659586064</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08217332065639323</v>
+      </c>
+      <c r="T14">
+        <v>0.7333709551211609</v>
+      </c>
+      <c r="U14">
+        <v>0.0473</v>
+      </c>
+      <c r="V14">
+        <v>0.22</v>
+      </c>
+      <c r="W14">
+        <v>0.036894</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>11.58635299345567</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.07663449448987873</v>
+      </c>
+      <c r="C15">
+        <v>133.7949462468079</v>
+      </c>
+      <c r="D15">
+        <v>151.6509462468079</v>
+      </c>
+      <c r="E15">
+        <v>-39.694</v>
+      </c>
+      <c r="F15">
+        <v>21.606</v>
+      </c>
+      <c r="G15">
+        <v>3.75</v>
+      </c>
+      <c r="H15">
+        <v>104.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>16.8</v>
+      </c>
+      <c r="K15">
+        <v>5.87</v>
+      </c>
+      <c r="L15">
+        <v>10.93</v>
+      </c>
+      <c r="M15">
+        <v>1.0219638</v>
+      </c>
+      <c r="N15">
+        <v>9.9080362</v>
+      </c>
+      <c r="O15">
+        <v>2.179767964</v>
+      </c>
+      <c r="P15">
+        <v>7.728268236</v>
+      </c>
+      <c r="Q15">
+        <v>13.598268236</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08257272929871118</v>
+      </c>
+      <c r="T15">
+        <v>0.7401242931886071</v>
+      </c>
+      <c r="U15">
+        <v>0.0473</v>
+      </c>
+      <c r="V15">
+        <v>0.22</v>
+      </c>
+      <c r="W15">
+        <v>0.036894</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>10.69509507088216</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.07694414680213142</v>
+      </c>
+      <c r="C16">
+        <v>130.9018513057092</v>
+      </c>
+      <c r="D16">
+        <v>150.4198513057092</v>
+      </c>
+      <c r="E16">
+        <v>-38.032</v>
+      </c>
+      <c r="F16">
+        <v>23.268</v>
+      </c>
+      <c r="G16">
+        <v>3.75</v>
+      </c>
+      <c r="H16">
+        <v>104.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>16.8</v>
+      </c>
+      <c r="K16">
+        <v>5.87</v>
+      </c>
+      <c r="L16">
+        <v>10.93</v>
+      </c>
+      <c r="M16">
+        <v>1.1889948</v>
+      </c>
+      <c r="N16">
+        <v>9.7410052</v>
+      </c>
+      <c r="O16">
+        <v>2.143021144</v>
+      </c>
+      <c r="P16">
+        <v>7.597984056</v>
+      </c>
+      <c r="Q16">
+        <v>13.467984056</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08298142651410631</v>
+      </c>
+      <c r="T16">
+        <v>0.7470346856297148</v>
+      </c>
+      <c r="U16">
+        <v>0.0511</v>
+      </c>
+      <c r="V16">
+        <v>0.22</v>
+      </c>
+      <c r="W16">
+        <v>0.039858</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>9.192639025839306</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.07686847911438412</v>
+      </c>
+      <c r="C17">
+        <v>129.5388367814724</v>
+      </c>
+      <c r="D17">
+        <v>150.7188367814724</v>
+      </c>
+      <c r="E17">
+        <v>-36.37</v>
+      </c>
+      <c r="F17">
+        <v>24.93</v>
+      </c>
+      <c r="G17">
+        <v>3.75</v>
+      </c>
+      <c r="H17">
+        <v>104.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>16.8</v>
+      </c>
+      <c r="K17">
+        <v>5.87</v>
+      </c>
+      <c r="L17">
+        <v>10.93</v>
+      </c>
+      <c r="M17">
+        <v>1.273923</v>
+      </c>
+      <c r="N17">
+        <v>9.656077</v>
+      </c>
+      <c r="O17">
+        <v>2.12433694</v>
+      </c>
+      <c r="P17">
+        <v>7.531740060000001</v>
+      </c>
+      <c r="Q17">
+        <v>13.40174006</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08339974013456955</v>
+      </c>
+      <c r="T17">
+        <v>0.754107675540025</v>
+      </c>
+      <c r="U17">
+        <v>0.0511</v>
+      </c>
+      <c r="V17">
+        <v>0.22</v>
+      </c>
+      <c r="W17">
+        <v>0.039858</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>8.579796424116687</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.07679281142663681</v>
+      </c>
+      <c r="C18">
+        <v>128.1770131951405</v>
+      </c>
+      <c r="D18">
+        <v>151.0190131951405</v>
+      </c>
+      <c r="E18">
+        <v>-34.708</v>
+      </c>
+      <c r="F18">
+        <v>26.592</v>
+      </c>
+      <c r="G18">
+        <v>3.75</v>
+      </c>
+      <c r="H18">
+        <v>104.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>16.8</v>
+      </c>
+      <c r="K18">
+        <v>5.87</v>
+      </c>
+      <c r="L18">
+        <v>10.93</v>
+      </c>
+      <c r="M18">
+        <v>1.3588512</v>
+      </c>
+      <c r="N18">
+        <v>9.5711488</v>
+      </c>
+      <c r="O18">
+        <v>2.105652736</v>
+      </c>
+      <c r="P18">
+        <v>7.465496064</v>
+      </c>
+      <c r="Q18">
+        <v>13.335496064</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08382801360313906</v>
+      </c>
+      <c r="T18">
+        <v>0.7613490699720092</v>
+      </c>
+      <c r="U18">
+        <v>0.0511</v>
+      </c>
+      <c r="V18">
+        <v>0.22</v>
+      </c>
+      <c r="W18">
+        <v>0.039858</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>8.043559147609393</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.0769690837388895</v>
+      </c>
+      <c r="C19">
+        <v>125.8175777829589</v>
+      </c>
+      <c r="D19">
+        <v>150.3215777829589</v>
+      </c>
+      <c r="E19">
+        <v>-33.04599999999999</v>
+      </c>
+      <c r="F19">
+        <v>28.254</v>
+      </c>
+      <c r="G19">
+        <v>3.75</v>
+      </c>
+      <c r="H19">
+        <v>104.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>16.8</v>
+      </c>
+      <c r="K19">
+        <v>5.87</v>
+      </c>
+      <c r="L19">
+        <v>10.93</v>
+      </c>
+      <c r="M19">
+        <v>1.497462</v>
+      </c>
+      <c r="N19">
+        <v>9.432537999999999</v>
+      </c>
+      <c r="O19">
+        <v>2.07515836</v>
+      </c>
+      <c r="P19">
+        <v>7.35737964</v>
+      </c>
+      <c r="Q19">
+        <v>13.22737964</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08426660691432471</v>
+      </c>
+      <c r="T19">
+        <v>0.7687649558360896</v>
+      </c>
+      <c r="U19">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V19">
+        <v>0.22</v>
+      </c>
+      <c r="W19">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>7.299016602758532</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.07690823605114219</v>
+      </c>
+      <c r="C20">
+        <v>124.3955973003762</v>
+      </c>
+      <c r="D20">
+        <v>150.5615973003762</v>
+      </c>
+      <c r="E20">
+        <v>-31.384</v>
+      </c>
+      <c r="F20">
+        <v>29.916</v>
+      </c>
+      <c r="G20">
+        <v>3.75</v>
+      </c>
+      <c r="H20">
+        <v>104.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>16.8</v>
+      </c>
+      <c r="K20">
+        <v>5.87</v>
+      </c>
+      <c r="L20">
+        <v>10.93</v>
+      </c>
+      <c r="M20">
+        <v>1.585548</v>
+      </c>
+      <c r="N20">
+        <v>9.344452</v>
+      </c>
+      <c r="O20">
+        <v>2.05577944</v>
+      </c>
+      <c r="P20">
+        <v>7.28867256</v>
+      </c>
+      <c r="Q20">
+        <v>13.15867256</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08471589762334414</v>
+      </c>
+      <c r="T20">
+        <v>0.7763617169651473</v>
+      </c>
+      <c r="U20">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0.22</v>
+      </c>
+      <c r="W20">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>6.893515680383061</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.0768473883633949</v>
+      </c>
+      <c r="C21">
+        <v>122.9743845252908</v>
+      </c>
+      <c r="D21">
+        <v>150.8023845252908</v>
+      </c>
+      <c r="E21">
+        <v>-29.722</v>
+      </c>
+      <c r="F21">
+        <v>31.578</v>
+      </c>
+      <c r="G21">
+        <v>3.75</v>
+      </c>
+      <c r="H21">
+        <v>104.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>16.8</v>
+      </c>
+      <c r="K21">
+        <v>5.87</v>
+      </c>
+      <c r="L21">
+        <v>10.93</v>
+      </c>
+      <c r="M21">
+        <v>1.673634</v>
+      </c>
+      <c r="N21">
+        <v>9.256366</v>
+      </c>
+      <c r="O21">
+        <v>2.03640052</v>
+      </c>
+      <c r="P21">
+        <v>7.21996548</v>
+      </c>
+      <c r="Q21">
+        <v>13.08996548</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.08517628193011714</v>
+      </c>
+      <c r="T21">
+        <v>0.7841460524430709</v>
+      </c>
+      <c r="U21">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0.22</v>
+      </c>
+      <c r="W21">
+        <v>0.04134000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>6.530699065626057</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.0770985406756476</v>
+      </c>
+      <c r="C22">
+        <v>120.3234599631904</v>
+      </c>
+      <c r="D22">
+        <v>149.8134599631904</v>
+      </c>
+      <c r="E22">
+        <v>-28.06</v>
+      </c>
+      <c r="F22">
+        <v>33.24</v>
+      </c>
+      <c r="G22">
+        <v>3.75</v>
+      </c>
+      <c r="H22">
+        <v>104.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>16.8</v>
+      </c>
+      <c r="K22">
+        <v>5.87</v>
+      </c>
+      <c r="L22">
+        <v>10.93</v>
+      </c>
+      <c r="M22">
+        <v>1.8282</v>
+      </c>
+      <c r="N22">
+        <v>9.101799999999999</v>
+      </c>
+      <c r="O22">
+        <v>2.002396</v>
+      </c>
+      <c r="P22">
+        <v>7.099404</v>
+      </c>
+      <c r="Q22">
+        <v>12.969404</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.08564817584455948</v>
+      </c>
+      <c r="T22">
+        <v>0.7921249963079425</v>
+      </c>
+      <c r="U22">
+        <v>0.055</v>
+      </c>
+      <c r="V22">
+        <v>0.22</v>
+      </c>
+      <c r="W22">
+        <v>0.0429</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>5.978558144623126</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
         <v>0.21</v>
       </c>
-      <c r="G3">
-        <v>0.1928166351606805</v>
-      </c>
-      <c r="H3">
-        <v>0.1928166351606805</v>
-      </c>
-      <c r="I3">
-        <v>-0.02722117202268431</v>
-      </c>
-      <c r="J3">
-        <v>-0.01836275672038705</v>
-      </c>
-      <c r="K3">
-        <v>3.98</v>
-      </c>
-      <c r="L3">
-        <v>0.07523629489603025</v>
-      </c>
-      <c r="M3">
-        <v>0.9196200000000001</v>
-      </c>
-      <c r="N3">
-        <v>0.01073068844807468</v>
-      </c>
-      <c r="O3">
-        <v>0.2310603015075377</v>
-      </c>
-      <c r="P3">
-        <v>0.9196200000000001</v>
-      </c>
-      <c r="Q3">
-        <v>0.01073068844807468</v>
-      </c>
-      <c r="R3">
-        <v>0.2310603015075377</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0.512</v>
-      </c>
-      <c r="V3">
-        <v>0.005974329054842474</v>
-      </c>
-      <c r="W3">
-        <v>0.05467032967032967</v>
-      </c>
-      <c r="X3">
-        <v>0.06702950223958865</v>
-      </c>
-      <c r="Y3">
-        <v>-0.01235917256925897</v>
-      </c>
-      <c r="Z3">
-        <v>0.3687696061345417</v>
-      </c>
-      <c r="AA3">
-        <v>-0.006771626563321538</v>
-      </c>
-      <c r="AB3">
-        <v>0.04410003035739397</v>
-      </c>
-      <c r="AC3">
-        <v>-0.05087165692071551</v>
-      </c>
-      <c r="AD3">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="AG3">
-        <v>75.38800000000001</v>
-      </c>
-      <c r="AH3">
-        <v>0.4696782178217822</v>
-      </c>
-      <c r="AI3">
-        <v>0.4881028938906753</v>
-      </c>
-      <c r="AJ3">
-        <v>0.4679926499801351</v>
-      </c>
-      <c r="AK3">
-        <v>0.4864118512400961</v>
-      </c>
-      <c r="AL3">
-        <v>2.62</v>
-      </c>
-      <c r="AM3">
-        <v>2.62</v>
-      </c>
-      <c r="AN3">
-        <v>16.0126582278481</v>
-      </c>
-      <c r="AO3">
-        <v>-0.5496183206106869</v>
-      </c>
-      <c r="AP3">
-        <v>15.90464135021097</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.5496183206106869</v>
+      <c r="B23">
+        <v>0.07705329298790028</v>
+      </c>
+      <c r="C23">
+        <v>118.8386659532447</v>
+      </c>
+      <c r="D23">
+        <v>149.9906659532447</v>
+      </c>
+      <c r="E23">
+        <v>-26.398</v>
+      </c>
+      <c r="F23">
+        <v>34.90199999999999</v>
+      </c>
+      <c r="G23">
+        <v>3.75</v>
+      </c>
+      <c r="H23">
+        <v>104.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>16.8</v>
+      </c>
+      <c r="K23">
+        <v>5.87</v>
+      </c>
+      <c r="L23">
+        <v>10.93</v>
+      </c>
+      <c r="M23">
+        <v>1.91961</v>
+      </c>
+      <c r="N23">
+        <v>9.010390000000001</v>
+      </c>
+      <c r="O23">
+        <v>1.9822858</v>
+      </c>
+      <c r="P23">
+        <v>7.028104200000001</v>
+      </c>
+      <c r="Q23">
+        <v>12.8981042</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.0861320164403801</v>
+      </c>
+      <c r="T23">
+        <v>0.8003059387516714</v>
+      </c>
+      <c r="U23">
+        <v>0.055</v>
+      </c>
+      <c r="V23">
+        <v>0.22</v>
+      </c>
+      <c r="W23">
+        <v>0.0429</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.693864899641074</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.07700804530015298</v>
+      </c>
+      <c r="C24">
+        <v>117.354291653925</v>
+      </c>
+      <c r="D24">
+        <v>150.168291653925</v>
+      </c>
+      <c r="E24">
+        <v>-24.736</v>
+      </c>
+      <c r="F24">
+        <v>36.564</v>
+      </c>
+      <c r="G24">
+        <v>3.75</v>
+      </c>
+      <c r="H24">
+        <v>104.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>16.8</v>
+      </c>
+      <c r="K24">
+        <v>5.87</v>
+      </c>
+      <c r="L24">
+        <v>10.93</v>
+      </c>
+      <c r="M24">
+        <v>2.01102</v>
+      </c>
+      <c r="N24">
+        <v>8.918979999999999</v>
+      </c>
+      <c r="O24">
+        <v>1.9621756</v>
+      </c>
+      <c r="P24">
+        <v>6.956804399999999</v>
+      </c>
+      <c r="Q24">
+        <v>12.8268044</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.08662826320532432</v>
+      </c>
+      <c r="T24">
+        <v>0.808696648950368</v>
+      </c>
+      <c r="U24">
+        <v>0.055</v>
+      </c>
+      <c r="V24">
+        <v>0.22</v>
+      </c>
+      <c r="W24">
+        <v>0.0429</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.435052858748297</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.07696279761240567</v>
+      </c>
+      <c r="C25">
+        <v>115.8703385581199</v>
+      </c>
+      <c r="D25">
+        <v>150.3463385581199</v>
+      </c>
+      <c r="E25">
+        <v>-23.074</v>
+      </c>
+      <c r="F25">
+        <v>38.226</v>
+      </c>
+      <c r="G25">
+        <v>3.75</v>
+      </c>
+      <c r="H25">
+        <v>104.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>16.8</v>
+      </c>
+      <c r="K25">
+        <v>5.87</v>
+      </c>
+      <c r="L25">
+        <v>10.93</v>
+      </c>
+      <c r="M25">
+        <v>2.10243</v>
+      </c>
+      <c r="N25">
+        <v>8.82757</v>
+      </c>
+      <c r="O25">
+        <v>1.9420654</v>
+      </c>
+      <c r="P25">
+        <v>6.8855046</v>
+      </c>
+      <c r="Q25">
+        <v>12.7555046</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.08713739949663074</v>
+      </c>
+      <c r="T25">
+        <v>0.817305299673706</v>
+      </c>
+      <c r="U25">
+        <v>0.055</v>
+      </c>
+      <c r="V25">
+        <v>0.22</v>
+      </c>
+      <c r="W25">
+        <v>0.0429</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.198746212715762</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.07691754992465837</v>
+      </c>
+      <c r="C26">
+        <v>114.3868081658064</v>
+      </c>
+      <c r="D26">
+        <v>150.5248081658064</v>
+      </c>
+      <c r="E26">
+        <v>-21.412</v>
+      </c>
+      <c r="F26">
+        <v>39.888</v>
+      </c>
+      <c r="G26">
+        <v>3.75</v>
+      </c>
+      <c r="H26">
+        <v>104.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>16.8</v>
+      </c>
+      <c r="K26">
+        <v>5.87</v>
+      </c>
+      <c r="L26">
+        <v>10.93</v>
+      </c>
+      <c r="M26">
+        <v>2.19384</v>
+      </c>
+      <c r="N26">
+        <v>8.73616</v>
+      </c>
+      <c r="O26">
+        <v>1.9219552</v>
+      </c>
+      <c r="P26">
+        <v>6.814204800000001</v>
+      </c>
+      <c r="Q26">
+        <v>12.6842048</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.08765993411139258</v>
+      </c>
+      <c r="T26">
+        <v>0.8261404938371318</v>
+      </c>
+      <c r="U26">
+        <v>0.055</v>
+      </c>
+      <c r="V26">
+        <v>0.22</v>
+      </c>
+      <c r="W26">
+        <v>0.0429</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>4.982131787185939</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.07687230223691106</v>
+      </c>
+      <c r="C27">
+        <v>112.9037019840927</v>
+      </c>
+      <c r="D27">
+        <v>150.7037019840927</v>
+      </c>
+      <c r="E27">
+        <v>-19.75</v>
+      </c>
+      <c r="F27">
+        <v>41.55</v>
+      </c>
+      <c r="G27">
+        <v>3.75</v>
+      </c>
+      <c r="H27">
+        <v>104.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>16.8</v>
+      </c>
+      <c r="K27">
+        <v>5.87</v>
+      </c>
+      <c r="L27">
+        <v>10.93</v>
+      </c>
+      <c r="M27">
+        <v>2.28525</v>
+      </c>
+      <c r="N27">
+        <v>8.64475</v>
+      </c>
+      <c r="O27">
+        <v>1.901845</v>
+      </c>
+      <c r="P27">
+        <v>6.742905</v>
+      </c>
+      <c r="Q27">
+        <v>12.612905</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.08819640298254808</v>
+      </c>
+      <c r="T27">
+        <v>0.8352112931782489</v>
+      </c>
+      <c r="U27">
+        <v>0.055</v>
+      </c>
+      <c r="V27">
+        <v>0.22</v>
+      </c>
+      <c r="W27">
+        <v>0.0429</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.782846515698502</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.07682705454916375</v>
+      </c>
+      <c r="C28">
+        <v>111.4210215272597</v>
+      </c>
+      <c r="D28">
+        <v>150.8830215272596</v>
+      </c>
+      <c r="E28">
+        <v>-18.088</v>
+      </c>
+      <c r="F28">
+        <v>43.212</v>
+      </c>
+      <c r="G28">
+        <v>3.75</v>
+      </c>
+      <c r="H28">
+        <v>104.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>16.8</v>
+      </c>
+      <c r="K28">
+        <v>5.87</v>
+      </c>
+      <c r="L28">
+        <v>10.93</v>
+      </c>
+      <c r="M28">
+        <v>2.37666</v>
+      </c>
+      <c r="N28">
+        <v>8.55334</v>
+      </c>
+      <c r="O28">
+        <v>1.8817348</v>
+      </c>
+      <c r="P28">
+        <v>6.6716052</v>
+      </c>
+      <c r="Q28">
+        <v>12.5416052</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.08874737101238345</v>
+      </c>
+      <c r="T28">
+        <v>0.8445272492583152</v>
+      </c>
+      <c r="U28">
+        <v>0.055</v>
+      </c>
+      <c r="V28">
+        <v>0.22</v>
+      </c>
+      <c r="W28">
+        <v>0.0429</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.598890880479328</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.07758208686141646</v>
+      </c>
+      <c r="C29">
+        <v>106.8215427621151</v>
+      </c>
+      <c r="D29">
+        <v>147.9455427621151</v>
+      </c>
+      <c r="E29">
+        <v>-16.42599999999999</v>
+      </c>
+      <c r="F29">
+        <v>44.874</v>
+      </c>
+      <c r="G29">
+        <v>3.75</v>
+      </c>
+      <c r="H29">
+        <v>104.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>16.8</v>
+      </c>
+      <c r="K29">
+        <v>5.87</v>
+      </c>
+      <c r="L29">
+        <v>10.93</v>
+      </c>
+      <c r="M29">
+        <v>2.6385912</v>
+      </c>
+      <c r="N29">
+        <v>8.291408799999999</v>
+      </c>
+      <c r="O29">
+        <v>1.824109936</v>
+      </c>
+      <c r="P29">
+        <v>6.467298864</v>
+      </c>
+      <c r="Q29">
+        <v>12.337298864</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.08931343405673486</v>
+      </c>
+      <c r="T29">
+        <v>0.854098437011808</v>
+      </c>
+      <c r="U29">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V29">
+        <v>0.22</v>
+      </c>
+      <c r="W29">
+        <v>0.04586400000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>4.142362030162156</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.07848375917366913</v>
+      </c>
+      <c r="C30">
+        <v>101.7980063954115</v>
+      </c>
+      <c r="D30">
+        <v>144.5840063954115</v>
+      </c>
+      <c r="E30">
+        <v>-14.764</v>
+      </c>
+      <c r="F30">
+        <v>46.536</v>
+      </c>
+      <c r="G30">
+        <v>3.75</v>
+      </c>
+      <c r="H30">
+        <v>104.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>16.8</v>
+      </c>
+      <c r="K30">
+        <v>5.87</v>
+      </c>
+      <c r="L30">
+        <v>10.93</v>
+      </c>
+      <c r="M30">
+        <v>2.931768</v>
+      </c>
+      <c r="N30">
+        <v>7.998232</v>
+      </c>
+      <c r="O30">
+        <v>1.75961104</v>
+      </c>
+      <c r="P30">
+        <v>6.23862096</v>
+      </c>
+      <c r="Q30">
+        <v>12.10862096</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.08989522107454047</v>
+      </c>
+      <c r="T30">
+        <v>0.8639354910917867</v>
+      </c>
+      <c r="U30">
+        <v>0.063</v>
+      </c>
+      <c r="V30">
+        <v>0.22</v>
+      </c>
+      <c r="W30">
+        <v>0.04914</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>3.728125827145941</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.07850091148592184</v>
+      </c>
+      <c r="C31">
+        <v>100.0735405745621</v>
+      </c>
+      <c r="D31">
+        <v>144.5215405745621</v>
+      </c>
+      <c r="E31">
+        <v>-13.102</v>
+      </c>
+      <c r="F31">
+        <v>48.19799999999999</v>
+      </c>
+      <c r="G31">
+        <v>3.75</v>
+      </c>
+      <c r="H31">
+        <v>104.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>16.8</v>
+      </c>
+      <c r="K31">
+        <v>5.87</v>
+      </c>
+      <c r="L31">
+        <v>10.93</v>
+      </c>
+      <c r="M31">
+        <v>3.036474</v>
+      </c>
+      <c r="N31">
+        <v>7.893526</v>
+      </c>
+      <c r="O31">
+        <v>1.73657572</v>
+      </c>
+      <c r="P31">
+        <v>6.15695028</v>
+      </c>
+      <c r="Q31">
+        <v>12.02695028</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09049339645904483</v>
+      </c>
+      <c r="T31">
+        <v>0.8740496452866943</v>
+      </c>
+      <c r="U31">
+        <v>0.063</v>
+      </c>
+      <c r="V31">
+        <v>0.22</v>
+      </c>
+      <c r="W31">
+        <v>0.04914</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.599569764140908</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.08017946379817452</v>
+      </c>
+      <c r="C32">
+        <v>92.54904396791315</v>
+      </c>
+      <c r="D32">
+        <v>138.6590439679131</v>
+      </c>
+      <c r="E32">
+        <v>-11.44</v>
+      </c>
+      <c r="F32">
+        <v>49.85999999999999</v>
+      </c>
+      <c r="G32">
+        <v>3.75</v>
+      </c>
+      <c r="H32">
+        <v>104.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>16.8</v>
+      </c>
+      <c r="K32">
+        <v>5.87</v>
+      </c>
+      <c r="L32">
+        <v>10.93</v>
+      </c>
+      <c r="M32">
+        <v>3.495185999999999</v>
+      </c>
+      <c r="N32">
+        <v>7.434814</v>
+      </c>
+      <c r="O32">
+        <v>1.63565908</v>
+      </c>
+      <c r="P32">
+        <v>5.79915492</v>
+      </c>
+      <c r="Q32">
+        <v>11.66915492</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09110866256882075</v>
+      </c>
+      <c r="T32">
+        <v>0.8844527753157421</v>
+      </c>
+      <c r="U32">
+        <v>0.0701</v>
+      </c>
+      <c r="V32">
+        <v>0.22</v>
+      </c>
+      <c r="W32">
+        <v>0.054678</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>3.127158325765782</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.0802519961104272</v>
+      </c>
+      <c r="C33">
+        <v>90.64441967915883</v>
+      </c>
+      <c r="D33">
+        <v>138.4164196791588</v>
+      </c>
+      <c r="E33">
+        <v>-9.777999999999999</v>
+      </c>
+      <c r="F33">
+        <v>51.522</v>
+      </c>
+      <c r="G33">
+        <v>3.75</v>
+      </c>
+      <c r="H33">
+        <v>104.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>16.8</v>
+      </c>
+      <c r="K33">
+        <v>5.87</v>
+      </c>
+      <c r="L33">
+        <v>10.93</v>
+      </c>
+      <c r="M33">
+        <v>3.6116922</v>
+      </c>
+      <c r="N33">
+        <v>7.318307799999999</v>
+      </c>
+      <c r="O33">
+        <v>1.610027716</v>
+      </c>
+      <c r="P33">
+        <v>5.708280084</v>
+      </c>
+      <c r="Q33">
+        <v>11.578280084</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09174176247888002</v>
+      </c>
+      <c r="T33">
+        <v>0.895157445345632</v>
+      </c>
+      <c r="U33">
+        <v>0.0701</v>
+      </c>
+      <c r="V33">
+        <v>0.22</v>
+      </c>
+      <c r="W33">
+        <v>0.054678</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>3.026282250741079</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.08564100842267991</v>
+      </c>
+      <c r="C34">
+        <v>73.05774565980626</v>
+      </c>
+      <c r="D34">
+        <v>122.4917456598063</v>
+      </c>
+      <c r="E34">
+        <v>-8.116</v>
+      </c>
+      <c r="F34">
+        <v>53.184</v>
+      </c>
+      <c r="G34">
+        <v>3.75</v>
+      </c>
+      <c r="H34">
+        <v>104.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>16.8</v>
+      </c>
+      <c r="K34">
+        <v>5.87</v>
+      </c>
+      <c r="L34">
+        <v>10.93</v>
+      </c>
+      <c r="M34">
+        <v>4.8610176</v>
+      </c>
+      <c r="N34">
+        <v>6.068982399999999</v>
+      </c>
+      <c r="O34">
+        <v>1.335176128</v>
+      </c>
+      <c r="P34">
+        <v>4.733806272</v>
+      </c>
+      <c r="Q34">
+        <v>10.603806272</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09239348297452929</v>
+      </c>
+      <c r="T34">
+        <v>0.906176958611695</v>
+      </c>
+      <c r="U34">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V34">
+        <v>0.22</v>
+      </c>
+      <c r="W34">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>2.248500396295623</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.0858796807349326</v>
+      </c>
+      <c r="C35">
+        <v>70.77476888782908</v>
+      </c>
+      <c r="D35">
+        <v>121.8707688878291</v>
+      </c>
+      <c r="E35">
+        <v>-6.454000000000001</v>
+      </c>
+      <c r="F35">
+        <v>54.846</v>
+      </c>
+      <c r="G35">
+        <v>3.75</v>
+      </c>
+      <c r="H35">
+        <v>104.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>16.8</v>
+      </c>
+      <c r="K35">
+        <v>5.87</v>
+      </c>
+      <c r="L35">
+        <v>10.93</v>
+      </c>
+      <c r="M35">
+        <v>5.0129244</v>
+      </c>
+      <c r="N35">
+        <v>5.9170756</v>
+      </c>
+      <c r="O35">
+        <v>1.301756632</v>
+      </c>
+      <c r="P35">
+        <v>4.615318968</v>
+      </c>
+      <c r="Q35">
+        <v>10.485318968</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.09306465781333226</v>
+      </c>
+      <c r="T35">
+        <v>0.9175254125722674</v>
+      </c>
+      <c r="U35">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V35">
+        <v>0.22</v>
+      </c>
+      <c r="W35">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.180364020650301</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08611835304718529</v>
+      </c>
+      <c r="C36">
+        <v>68.49805649119375</v>
+      </c>
+      <c r="D36">
+        <v>121.2560564911938</v>
+      </c>
+      <c r="E36">
+        <v>-4.791999999999994</v>
+      </c>
+      <c r="F36">
+        <v>56.508</v>
+      </c>
+      <c r="G36">
+        <v>3.75</v>
+      </c>
+      <c r="H36">
+        <v>104.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>16.8</v>
+      </c>
+      <c r="K36">
+        <v>5.87</v>
+      </c>
+      <c r="L36">
+        <v>10.93</v>
+      </c>
+      <c r="M36">
+        <v>5.164831200000001</v>
+      </c>
+      <c r="N36">
+        <v>5.765168799999999</v>
+      </c>
+      <c r="O36">
+        <v>1.268337136</v>
+      </c>
+      <c r="P36">
+        <v>4.496831663999999</v>
+      </c>
+      <c r="Q36">
+        <v>10.366831664</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.09375617128361409</v>
+      </c>
+      <c r="T36">
+        <v>0.9292177590770995</v>
+      </c>
+      <c r="U36">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V36">
+        <v>0.22</v>
+      </c>
+      <c r="W36">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>2.116235667101763</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.08635702535943798</v>
+      </c>
+      <c r="C37">
+        <v>66.2275141536808</v>
+      </c>
+      <c r="D37">
+        <v>120.6475141536808</v>
+      </c>
+      <c r="E37">
+        <v>-3.129999999999995</v>
+      </c>
+      <c r="F37">
+        <v>58.17</v>
+      </c>
+      <c r="G37">
+        <v>3.75</v>
+      </c>
+      <c r="H37">
+        <v>104.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>16.8</v>
+      </c>
+      <c r="K37">
+        <v>5.87</v>
+      </c>
+      <c r="L37">
+        <v>10.93</v>
+      </c>
+      <c r="M37">
+        <v>5.316738000000001</v>
+      </c>
+      <c r="N37">
+        <v>5.613261999999999</v>
+      </c>
+      <c r="O37">
+        <v>1.23491764</v>
+      </c>
+      <c r="P37">
+        <v>4.378344359999999</v>
+      </c>
+      <c r="Q37">
+        <v>10.24834436</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.09446896209144306</v>
+      </c>
+      <c r="T37">
+        <v>0.9412698700897727</v>
+      </c>
+      <c r="U37">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V37">
+        <v>0.22</v>
+      </c>
+      <c r="W37">
+        <v>0.07129200000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>2.055771790898855</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.0925205776716907</v>
+      </c>
+      <c r="C38">
+        <v>50.72319716718034</v>
+      </c>
+      <c r="D38">
+        <v>106.8051971671803</v>
+      </c>
+      <c r="E38">
+        <v>-1.468000000000004</v>
+      </c>
+      <c r="F38">
+        <v>59.83199999999999</v>
+      </c>
+      <c r="G38">
+        <v>3.75</v>
+      </c>
+      <c r="H38">
+        <v>104.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>16.8</v>
+      </c>
+      <c r="K38">
+        <v>5.87</v>
+      </c>
+      <c r="L38">
+        <v>10.93</v>
+      </c>
+      <c r="M38">
+        <v>6.7311</v>
+      </c>
+      <c r="N38">
+        <v>4.1989</v>
+      </c>
+      <c r="O38">
+        <v>0.9237579999999999</v>
+      </c>
+      <c r="P38">
+        <v>3.275142</v>
+      </c>
+      <c r="Q38">
+        <v>9.145142</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.0952040276120167</v>
+      </c>
+      <c r="T38">
+        <v>0.9536986095715918</v>
+      </c>
+      <c r="U38">
+        <v>0.1125</v>
+      </c>
+      <c r="V38">
+        <v>0.22</v>
+      </c>
+      <c r="W38">
+        <v>0.08775000000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>1.623805915823565</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.09292382998394338</v>
+      </c>
+      <c r="C39">
+        <v>48.26543968418169</v>
+      </c>
+      <c r="D39">
+        <v>106.0094396841817</v>
+      </c>
+      <c r="E39">
+        <v>0.1939999999999955</v>
+      </c>
+      <c r="F39">
+        <v>61.49399999999999</v>
+      </c>
+      <c r="G39">
+        <v>3.75</v>
+      </c>
+      <c r="H39">
+        <v>104.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>16.8</v>
+      </c>
+      <c r="K39">
+        <v>5.87</v>
+      </c>
+      <c r="L39">
+        <v>10.93</v>
+      </c>
+      <c r="M39">
+        <v>6.918074999999999</v>
+      </c>
+      <c r="N39">
+        <v>4.011925000000001</v>
+      </c>
+      <c r="O39">
+        <v>0.8826235</v>
+      </c>
+      <c r="P39">
+        <v>3.1293015</v>
+      </c>
+      <c r="Q39">
+        <v>8.999301500000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.09596242854594188</v>
+      </c>
+      <c r="T39">
+        <v>0.966521912211564</v>
+      </c>
+      <c r="U39">
+        <v>0.1125</v>
+      </c>
+      <c r="V39">
+        <v>0.22</v>
+      </c>
+      <c r="W39">
+        <v>0.08775000000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>1.579919269449956</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.09332708229619607</v>
+      </c>
+      <c r="C40">
+        <v>45.81945217058166</v>
+      </c>
+      <c r="D40">
+        <v>105.2254521705817</v>
+      </c>
+      <c r="E40">
+        <v>1.856000000000002</v>
+      </c>
+      <c r="F40">
+        <v>63.156</v>
+      </c>
+      <c r="G40">
+        <v>3.75</v>
+      </c>
+      <c r="H40">
+        <v>104.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>16.8</v>
+      </c>
+      <c r="K40">
+        <v>5.87</v>
+      </c>
+      <c r="L40">
+        <v>10.93</v>
+      </c>
+      <c r="M40">
+        <v>7.10505</v>
+      </c>
+      <c r="N40">
+        <v>3.824949999999999</v>
+      </c>
+      <c r="O40">
+        <v>0.8414889999999998</v>
+      </c>
+      <c r="P40">
+        <v>2.983461</v>
+      </c>
+      <c r="Q40">
+        <v>8.853460999999999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.0967452940261227</v>
+      </c>
+      <c r="T40">
+        <v>0.9797588697754062</v>
+      </c>
+      <c r="U40">
+        <v>0.1125</v>
+      </c>
+      <c r="V40">
+        <v>0.22</v>
+      </c>
+      <c r="W40">
+        <v>0.08775000000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>1.538342446569693</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1221923354111438</v>
+      </c>
+      <c r="C41">
+        <v>7.734928493030623</v>
+      </c>
+      <c r="D41">
+        <v>68.80292849303062</v>
+      </c>
+      <c r="E41">
+        <v>3.518000000000001</v>
+      </c>
+      <c r="F41">
+        <v>64.818</v>
+      </c>
+      <c r="G41">
+        <v>3.75</v>
+      </c>
+      <c r="H41">
+        <v>104.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>16.8</v>
+      </c>
+      <c r="K41">
+        <v>5.87</v>
+      </c>
+      <c r="L41">
+        <v>10.93</v>
+      </c>
+      <c r="M41">
+        <v>12.7432188</v>
+      </c>
+      <c r="N41">
+        <v>-1.8132188</v>
+      </c>
+      <c r="O41">
+        <v>-0.3989081359999999</v>
+      </c>
+      <c r="P41">
+        <v>-1.414310664</v>
+      </c>
+      <c r="Q41">
+        <v>4.455689336000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.09833843626415037</v>
+      </c>
+      <c r="T41">
+        <v>1.006696264170502</v>
+      </c>
+      <c r="U41">
+        <v>0.1966</v>
+      </c>
+      <c r="V41">
+        <v>0.1886964382970494</v>
+      </c>
+      <c r="W41">
+        <v>0.1595022802308001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.8577110831684064</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1237703354111438</v>
+      </c>
+      <c r="C42">
+        <v>4.795176432424284</v>
+      </c>
+      <c r="D42">
+        <v>67.52517643242429</v>
+      </c>
+      <c r="E42">
+        <v>5.180000000000007</v>
+      </c>
+      <c r="F42">
+        <v>66.48</v>
+      </c>
+      <c r="G42">
+        <v>3.75</v>
+      </c>
+      <c r="H42">
+        <v>104.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>16.8</v>
+      </c>
+      <c r="K42">
+        <v>5.87</v>
+      </c>
+      <c r="L42">
+        <v>10.93</v>
+      </c>
+      <c r="M42">
+        <v>13.069968</v>
+      </c>
+      <c r="N42">
+        <v>-2.139968000000001</v>
+      </c>
+      <c r="O42">
+        <v>-0.4707929600000003</v>
+      </c>
+      <c r="P42">
+        <v>-1.669175040000001</v>
+      </c>
+      <c r="Q42">
+        <v>4.200824959999998</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.09933074353521953</v>
+      </c>
+      <c r="T42">
+        <v>1.02347453524001</v>
+      </c>
+      <c r="U42">
+        <v>0.1966</v>
+      </c>
+      <c r="V42">
+        <v>0.1839790273396231</v>
+      </c>
+      <c r="W42">
+        <v>0.1604297232250301</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.8362683060891961</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1253483354111438</v>
+      </c>
+      <c r="C43">
+        <v>1.902017821410183</v>
+      </c>
+      <c r="D43">
+        <v>66.29401782141018</v>
+      </c>
+      <c r="E43">
+        <v>6.841999999999999</v>
+      </c>
+      <c r="F43">
+        <v>68.142</v>
+      </c>
+      <c r="G43">
+        <v>3.75</v>
+      </c>
+      <c r="H43">
+        <v>104.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>16.8</v>
+      </c>
+      <c r="K43">
+        <v>5.87</v>
+      </c>
+      <c r="L43">
+        <v>10.93</v>
+      </c>
+      <c r="M43">
+        <v>13.3967172</v>
+      </c>
+      <c r="N43">
+        <v>-2.4667172</v>
+      </c>
+      <c r="O43">
+        <v>-0.5426777839999999</v>
+      </c>
+      <c r="P43">
+        <v>-1.924039416</v>
+      </c>
+      <c r="Q43">
+        <v>3.945960584</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1003566883409012</v>
+      </c>
+      <c r="T43">
+        <v>1.040821561261027</v>
+      </c>
+      <c r="U43">
+        <v>0.1966</v>
+      </c>
+      <c r="V43">
+        <v>0.1794917339898763</v>
+      </c>
+      <c r="W43">
+        <v>0.1613119250975903</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.8158715181358012</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1343824347138694</v>
+      </c>
+      <c r="C44">
+        <v>-6.025848307320906</v>
+      </c>
+      <c r="D44">
+        <v>60.02815169267908</v>
+      </c>
+      <c r="E44">
+        <v>8.503999999999991</v>
+      </c>
+      <c r="F44">
+        <v>69.80399999999999</v>
+      </c>
+      <c r="G44">
+        <v>3.75</v>
+      </c>
+      <c r="H44">
+        <v>104.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>16.8</v>
+      </c>
+      <c r="K44">
+        <v>5.87</v>
+      </c>
+      <c r="L44">
+        <v>10.93</v>
+      </c>
+      <c r="M44">
+        <v>14.9240952</v>
+      </c>
+      <c r="N44">
+        <v>-3.994095199999997</v>
+      </c>
+      <c r="O44">
+        <v>-0.8787009439999992</v>
+      </c>
+      <c r="P44">
+        <v>-3.115394255999997</v>
+      </c>
+      <c r="Q44">
+        <v>2.754605744000003</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1018181817652713</v>
+      </c>
+      <c r="T44">
+        <v>1.065532992442989</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.1611219955230519</v>
+      </c>
+      <c r="W44">
+        <v>0.1793521173571715</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.7323727069229633</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1361324347138694</v>
+      </c>
+      <c r="C45">
+        <v>-8.76713154698303</v>
+      </c>
+      <c r="D45">
+        <v>58.94886845301696</v>
+      </c>
+      <c r="E45">
+        <v>10.166</v>
+      </c>
+      <c r="F45">
+        <v>71.46599999999999</v>
+      </c>
+      <c r="G45">
+        <v>3.75</v>
+      </c>
+      <c r="H45">
+        <v>104.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>16.8</v>
+      </c>
+      <c r="K45">
+        <v>5.87</v>
+      </c>
+      <c r="L45">
+        <v>10.93</v>
+      </c>
+      <c r="M45">
+        <v>15.2794308</v>
+      </c>
+      <c r="N45">
+        <v>-4.349430799999999</v>
+      </c>
+      <c r="O45">
+        <v>-0.9568747759999996</v>
+      </c>
+      <c r="P45">
+        <v>-3.392556023999999</v>
+      </c>
+      <c r="Q45">
+        <v>2.477443976000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1029237639015042</v>
+      </c>
+      <c r="T45">
+        <v>1.084226553713918</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.157374972371353</v>
+      </c>
+      <c r="W45">
+        <v>0.1801532309070047</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.71534078350615</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1378824347138694</v>
+      </c>
+      <c r="C46">
+        <v>-11.47029005394431</v>
+      </c>
+      <c r="D46">
+        <v>57.90770994605569</v>
+      </c>
+      <c r="E46">
+        <v>11.828</v>
+      </c>
+      <c r="F46">
+        <v>73.128</v>
+      </c>
+      <c r="G46">
+        <v>3.75</v>
+      </c>
+      <c r="H46">
+        <v>104.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>16.8</v>
+      </c>
+      <c r="K46">
+        <v>5.87</v>
+      </c>
+      <c r="L46">
+        <v>10.93</v>
+      </c>
+      <c r="M46">
+        <v>15.6347664</v>
+      </c>
+      <c r="N46">
+        <v>-4.7047664</v>
+      </c>
+      <c r="O46">
+        <v>-1.035048608</v>
+      </c>
+      <c r="P46">
+        <v>-3.669717792000001</v>
+      </c>
+      <c r="Q46">
+        <v>2.200282208</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.104068831114031</v>
+      </c>
+      <c r="T46">
+        <v>1.103587742173096</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.1537982684538222</v>
+      </c>
+      <c r="W46">
+        <v>0.1809179302045728</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.6990830384264648</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1396324347138694</v>
+      </c>
+      <c r="C47">
+        <v>-14.13730885263903</v>
+      </c>
+      <c r="D47">
+        <v>56.90269114736096</v>
+      </c>
+      <c r="E47">
+        <v>13.48999999999999</v>
+      </c>
+      <c r="F47">
+        <v>74.78999999999999</v>
+      </c>
+      <c r="G47">
+        <v>3.75</v>
+      </c>
+      <c r="H47">
+        <v>104.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>16.8</v>
+      </c>
+      <c r="K47">
+        <v>5.87</v>
+      </c>
+      <c r="L47">
+        <v>10.93</v>
+      </c>
+      <c r="M47">
+        <v>15.990102</v>
+      </c>
+      <c r="N47">
+        <v>-5.060101999999997</v>
+      </c>
+      <c r="O47">
+        <v>-1.113222439999999</v>
+      </c>
+      <c r="P47">
+        <v>-3.946879559999998</v>
+      </c>
+      <c r="Q47">
+        <v>1.923120440000003</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1052555371342862</v>
+      </c>
+      <c r="T47">
+        <v>1.12365297384897</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.1503805291548484</v>
+      </c>
+      <c r="W47">
+        <v>0.1816486428666934</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.6835478597947657</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1413824347138694</v>
+      </c>
+      <c r="C48">
+        <v>-16.77003751379469</v>
+      </c>
+      <c r="D48">
+        <v>55.93196248620531</v>
+      </c>
+      <c r="E48">
+        <v>15.152</v>
+      </c>
+      <c r="F48">
+        <v>76.452</v>
+      </c>
+      <c r="G48">
+        <v>3.75</v>
+      </c>
+      <c r="H48">
+        <v>104.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>16.8</v>
+      </c>
+      <c r="K48">
+        <v>5.87</v>
+      </c>
+      <c r="L48">
+        <v>10.93</v>
+      </c>
+      <c r="M48">
+        <v>16.3454376</v>
+      </c>
+      <c r="N48">
+        <v>-5.415437600000001</v>
+      </c>
+      <c r="O48">
+        <v>-1.191396272</v>
+      </c>
+      <c r="P48">
+        <v>-4.224041328</v>
+      </c>
+      <c r="Q48">
+        <v>1.645958672</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1064861952293655</v>
+      </c>
+      <c r="T48">
+        <v>1.144461362253581</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.1471113872166995</v>
+      </c>
+      <c r="W48">
+        <v>0.1823475854130696</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.6686881237122706</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1431324347138694</v>
+      </c>
+      <c r="C49">
+        <v>-19.37020151446521</v>
+      </c>
+      <c r="D49">
+        <v>54.9937984855348</v>
+      </c>
+      <c r="E49">
+        <v>16.81400000000001</v>
+      </c>
+      <c r="F49">
+        <v>78.114</v>
+      </c>
+      <c r="G49">
+        <v>3.75</v>
+      </c>
+      <c r="H49">
+        <v>104.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>16.8</v>
+      </c>
+      <c r="K49">
+        <v>5.87</v>
+      </c>
+      <c r="L49">
+        <v>10.93</v>
+      </c>
+      <c r="M49">
+        <v>16.7007732</v>
+      </c>
+      <c r="N49">
+        <v>-5.770773200000001</v>
+      </c>
+      <c r="O49">
+        <v>-1.269570104</v>
+      </c>
+      <c r="P49">
+        <v>-4.501203096000001</v>
+      </c>
+      <c r="Q49">
+        <v>1.368796903999999</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1077632932525611</v>
+      </c>
+      <c r="T49">
+        <v>1.166054972862139</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.1439813577014506</v>
+      </c>
+      <c r="W49">
+        <v>0.1830167857234299</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.6544607168247755</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1448824347138694</v>
+      </c>
+      <c r="C50">
+        <v>-21.93941247365242</v>
+      </c>
+      <c r="D50">
+        <v>54.08658752634758</v>
+      </c>
+      <c r="E50">
+        <v>18.476</v>
+      </c>
+      <c r="F50">
+        <v>79.776</v>
+      </c>
+      <c r="G50">
+        <v>3.75</v>
+      </c>
+      <c r="H50">
+        <v>104.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>16.8</v>
+      </c>
+      <c r="K50">
+        <v>5.87</v>
+      </c>
+      <c r="L50">
+        <v>10.93</v>
+      </c>
+      <c r="M50">
+        <v>17.0561088</v>
+      </c>
+      <c r="N50">
+        <v>-6.126108799999997</v>
+      </c>
+      <c r="O50">
+        <v>-1.347743935999999</v>
+      </c>
+      <c r="P50">
+        <v>-4.778364863999998</v>
+      </c>
+      <c r="Q50">
+        <v>1.091635136000002</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.109089510430495</v>
+      </c>
+      <c r="T50">
+        <v>1.188479106955642</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.1409817460826704</v>
+      </c>
+      <c r="W50">
+        <v>0.1836581026875251</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.6408261185575927</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1466324347138694</v>
+      </c>
+      <c r="C51">
+        <v>-24.47917739125132</v>
+      </c>
+      <c r="D51">
+        <v>53.20882260874867</v>
+      </c>
+      <c r="E51">
+        <v>20.13799999999999</v>
+      </c>
+      <c r="F51">
+        <v>81.43799999999999</v>
+      </c>
+      <c r="G51">
+        <v>3.75</v>
+      </c>
+      <c r="H51">
+        <v>104.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>16.8</v>
+      </c>
+      <c r="K51">
+        <v>5.87</v>
+      </c>
+      <c r="L51">
+        <v>10.93</v>
+      </c>
+      <c r="M51">
+        <v>17.4114444</v>
+      </c>
+      <c r="N51">
+        <v>-6.481444399999997</v>
+      </c>
+      <c r="O51">
+        <v>-1.425917767999999</v>
+      </c>
+      <c r="P51">
+        <v>-5.055526631999998</v>
+      </c>
+      <c r="Q51">
+        <v>0.8144733680000025</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1104677361252105</v>
+      </c>
+      <c r="T51">
+        <v>1.211782618856732</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0.1381045675911873</v>
+      </c>
+      <c r="W51">
+        <v>0.1842732434490041</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.627748034505397</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1483824347138694</v>
+      </c>
+      <c r="C52">
+        <v>-26.99090700173537</v>
+      </c>
+      <c r="D52">
+        <v>52.35909299826463</v>
+      </c>
+      <c r="E52">
+        <v>21.8</v>
+      </c>
+      <c r="F52">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="G52">
+        <v>3.75</v>
+      </c>
+      <c r="H52">
+        <v>104.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>16.8</v>
+      </c>
+      <c r="K52">
+        <v>5.87</v>
+      </c>
+      <c r="L52">
+        <v>10.93</v>
+      </c>
+      <c r="M52">
+        <v>17.76678</v>
+      </c>
+      <c r="N52">
+        <v>-6.836779999999997</v>
+      </c>
+      <c r="O52">
+        <v>-1.504091599999999</v>
+      </c>
+      <c r="P52">
+        <v>-5.332688399999999</v>
+      </c>
+      <c r="Q52">
+        <v>0.5373116000000016</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1119010908477148</v>
+      </c>
+      <c r="T52">
+        <v>1.236018271233867</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.1353424762393636</v>
+      </c>
+      <c r="W52">
+        <v>0.1848637785800241</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.6151930738152891</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1501324347138694</v>
+      </c>
+      <c r="C53">
+        <v>-29.47592333998805</v>
+      </c>
+      <c r="D53">
+        <v>51.53607666001195</v>
+      </c>
+      <c r="E53">
+        <v>23.462</v>
+      </c>
+      <c r="F53">
+        <v>84.762</v>
+      </c>
+      <c r="G53">
+        <v>3.75</v>
+      </c>
+      <c r="H53">
+        <v>104.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>16.8</v>
+      </c>
+      <c r="K53">
+        <v>5.87</v>
+      </c>
+      <c r="L53">
+        <v>10.93</v>
+      </c>
+      <c r="M53">
+        <v>18.1221156</v>
+      </c>
+      <c r="N53">
+        <v>-7.192115600000001</v>
+      </c>
+      <c r="O53">
+        <v>-1.582265432</v>
+      </c>
+      <c r="P53">
+        <v>-5.609850168000001</v>
+      </c>
+      <c r="Q53">
+        <v>0.2601498319999989</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1133929498446069</v>
+      </c>
+      <c r="T53">
+        <v>1.26124313391211</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.1326887021954545</v>
+      </c>
+      <c r="W53">
+        <v>0.1854311554706118</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.603130464524793</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1518824347138694</v>
+      </c>
+      <c r="C54">
+        <v>-31.935466604627</v>
+      </c>
+      <c r="D54">
+        <v>50.73853339537299</v>
+      </c>
+      <c r="E54">
+        <v>25.124</v>
+      </c>
+      <c r="F54">
+        <v>86.42399999999999</v>
+      </c>
+      <c r="G54">
+        <v>3.75</v>
+      </c>
+      <c r="H54">
+        <v>104.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>16.8</v>
+      </c>
+      <c r="K54">
+        <v>5.87</v>
+      </c>
+      <c r="L54">
+        <v>10.93</v>
+      </c>
+      <c r="M54">
+        <v>18.4774512</v>
+      </c>
+      <c r="N54">
+        <v>-7.547451199999998</v>
+      </c>
+      <c r="O54">
+        <v>-1.660439263999999</v>
+      </c>
+      <c r="P54">
+        <v>-5.887011935999999</v>
+      </c>
+      <c r="Q54">
+        <v>-0.01701193599999851</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1149469696330362</v>
+      </c>
+      <c r="T54">
+        <v>1.287519032535278</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.1301369963840034</v>
+      </c>
+      <c r="W54">
+        <v>0.1859767101731001</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5915318017454703</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1536324347138694</v>
+      </c>
+      <c r="C55">
+        <v>-34.37070139376256</v>
+      </c>
+      <c r="D55">
+        <v>49.96529860623744</v>
+      </c>
+      <c r="E55">
+        <v>26.786</v>
+      </c>
+      <c r="F55">
+        <v>88.086</v>
+      </c>
+      <c r="G55">
+        <v>3.75</v>
+      </c>
+      <c r="H55">
+        <v>104.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>16.8</v>
+      </c>
+      <c r="K55">
+        <v>5.87</v>
+      </c>
+      <c r="L55">
+        <v>10.93</v>
+      </c>
+      <c r="M55">
+        <v>18.8327868</v>
+      </c>
+      <c r="N55">
+        <v>-7.902786799999998</v>
+      </c>
+      <c r="O55">
+        <v>-1.738613095999999</v>
+      </c>
+      <c r="P55">
+        <v>-6.164173703999999</v>
+      </c>
+      <c r="Q55">
+        <v>-0.2941737039999985</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1165671179231008</v>
+      </c>
+      <c r="T55">
+        <v>1.314913054504114</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.1276815813578902</v>
+      </c>
+      <c r="W55">
+        <v>0.1865016779056831</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.5803708243540463</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1553824347138694</v>
+      </c>
+      <c r="C56">
+        <v>-36.78272237913245</v>
+      </c>
+      <c r="D56">
+        <v>49.21527762086755</v>
+      </c>
+      <c r="E56">
+        <v>28.44800000000001</v>
+      </c>
+      <c r="F56">
+        <v>89.748</v>
+      </c>
+      <c r="G56">
+        <v>3.75</v>
+      </c>
+      <c r="H56">
+        <v>104.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>16.8</v>
+      </c>
+      <c r="K56">
+        <v>5.87</v>
+      </c>
+      <c r="L56">
+        <v>10.93</v>
+      </c>
+      <c r="M56">
+        <v>19.1881224</v>
+      </c>
+      <c r="N56">
+        <v>-8.258122400000001</v>
+      </c>
+      <c r="O56">
+        <v>-1.816786928</v>
+      </c>
+      <c r="P56">
+        <v>-6.441335472000001</v>
+      </c>
+      <c r="Q56">
+        <v>-0.5713354720000012</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1182577074431682</v>
+      </c>
+      <c r="T56">
+        <v>1.343498120906377</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.1253171076290403</v>
+      </c>
+      <c r="W56">
+        <v>0.1870072023889112</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.5696232164956379</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1571324347138694</v>
+      </c>
+      <c r="C57">
+        <v>-39.17255947675302</v>
+      </c>
+      <c r="D57">
+        <v>48.48744052324698</v>
+      </c>
+      <c r="E57">
+        <v>30.11</v>
+      </c>
+      <c r="F57">
+        <v>91.41</v>
+      </c>
+      <c r="G57">
+        <v>3.75</v>
+      </c>
+      <c r="H57">
+        <v>104.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>16.8</v>
+      </c>
+      <c r="K57">
+        <v>5.87</v>
+      </c>
+      <c r="L57">
+        <v>10.93</v>
+      </c>
+      <c r="M57">
+        <v>19.543458</v>
+      </c>
+      <c r="N57">
+        <v>-8.613457999999998</v>
+      </c>
+      <c r="O57">
+        <v>-1.894960759999999</v>
+      </c>
+      <c r="P57">
+        <v>-6.718497239999999</v>
+      </c>
+      <c r="Q57">
+        <v>-0.8484972399999986</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1200234342752386</v>
+      </c>
+      <c r="T57">
+        <v>1.373353634704297</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.1230386147630578</v>
+      </c>
+      <c r="W57">
+        <v>0.1874943441636582</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.5592664307411719</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1588824347138694</v>
+      </c>
+      <c r="C58">
+        <v>-41.5411825654493</v>
+      </c>
+      <c r="D58">
+        <v>47.78081743455071</v>
+      </c>
+      <c r="E58">
+        <v>31.77200000000001</v>
+      </c>
+      <c r="F58">
+        <v>93.072</v>
+      </c>
+      <c r="G58">
+        <v>3.75</v>
+      </c>
+      <c r="H58">
+        <v>104.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>16.8</v>
+      </c>
+      <c r="K58">
+        <v>5.87</v>
+      </c>
+      <c r="L58">
+        <v>10.93</v>
+      </c>
+      <c r="M58">
+        <v>19.8987936</v>
+      </c>
+      <c r="N58">
+        <v>-8.968793600000001</v>
+      </c>
+      <c r="O58">
+        <v>-1.973134592</v>
+      </c>
+      <c r="P58">
+        <v>-6.995659008000001</v>
+      </c>
+      <c r="Q58">
+        <v>-1.125659008000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1218694214178577</v>
+      </c>
+      <c r="T58">
+        <v>1.404566217311213</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.1208414966422889</v>
+      </c>
+      <c r="W58">
+        <v>0.1879640880178786</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.5492795301922222</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1606324347138694</v>
+      </c>
+      <c r="C59">
+        <v>-43.88950579872326</v>
+      </c>
+      <c r="D59">
+        <v>47.09449420127675</v>
+      </c>
+      <c r="E59">
+        <v>33.43400000000001</v>
+      </c>
+      <c r="F59">
+        <v>94.73400000000001</v>
+      </c>
+      <c r="G59">
+        <v>3.75</v>
+      </c>
+      <c r="H59">
+        <v>104.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>16.8</v>
+      </c>
+      <c r="K59">
+        <v>5.87</v>
+      </c>
+      <c r="L59">
+        <v>10.93</v>
+      </c>
+      <c r="M59">
+        <v>20.2541292</v>
+      </c>
+      <c r="N59">
+        <v>-9.324129200000002</v>
+      </c>
+      <c r="O59">
+        <v>-2.051308424</v>
+      </c>
+      <c r="P59">
+        <v>-7.272820776000001</v>
+      </c>
+      <c r="Q59">
+        <v>-1.402820776000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1238012684275753</v>
+      </c>
+      <c r="T59">
+        <v>1.437230547946357</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.1187214703854066</v>
+      </c>
+      <c r="W59">
+        <v>0.1884173496316001</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.5396430472063938</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1623824347138694</v>
+      </c>
+      <c r="C60">
+        <v>-46.21839155027078</v>
+      </c>
+      <c r="D60">
+        <v>46.42760844972921</v>
+      </c>
+      <c r="E60">
+        <v>35.09599999999999</v>
+      </c>
+      <c r="F60">
+        <v>96.39599999999999</v>
+      </c>
+      <c r="G60">
+        <v>3.75</v>
+      </c>
+      <c r="H60">
+        <v>104.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>16.8</v>
+      </c>
+      <c r="K60">
+        <v>5.87</v>
+      </c>
+      <c r="L60">
+        <v>10.93</v>
+      </c>
+      <c r="M60">
+        <v>20.6094648</v>
+      </c>
+      <c r="N60">
+        <v>-9.679464799999998</v>
+      </c>
+      <c r="O60">
+        <v>-2.129482255999999</v>
+      </c>
+      <c r="P60">
+        <v>-7.549982543999999</v>
+      </c>
+      <c r="Q60">
+        <v>-1.679982543999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1258251081520414</v>
+      </c>
+      <c r="T60">
+        <v>1.471450322897461</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.11667454848221</v>
+      </c>
+      <c r="W60">
+        <v>0.1888549815345035</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.5303388567373182</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1641324347138694</v>
+      </c>
+      <c r="C61">
+        <v>-48.5286540289541</v>
+      </c>
+      <c r="D61">
+        <v>45.77934597104589</v>
+      </c>
+      <c r="E61">
+        <v>36.758</v>
+      </c>
+      <c r="F61">
+        <v>98.05799999999999</v>
+      </c>
+      <c r="G61">
+        <v>3.75</v>
+      </c>
+      <c r="H61">
+        <v>104.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>16.8</v>
+      </c>
+      <c r="K61">
+        <v>5.87</v>
+      </c>
+      <c r="L61">
+        <v>10.93</v>
+      </c>
+      <c r="M61">
+        <v>20.9648004</v>
+      </c>
+      <c r="N61">
+        <v>-10.0348004</v>
+      </c>
+      <c r="O61">
+        <v>-2.207656087999999</v>
+      </c>
+      <c r="P61">
+        <v>-7.827144311999999</v>
+      </c>
+      <c r="Q61">
+        <v>-1.957144311999999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1279476717655058</v>
+      </c>
+      <c r="T61">
+        <v>1.507339355163252</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.1146970137621725</v>
+      </c>
+      <c r="W61">
+        <v>0.1892777784576475</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.5213500625553297</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1658824347138694</v>
+      </c>
+      <c r="C62">
+        <v>-50.82106259509236</v>
+      </c>
+      <c r="D62">
+        <v>45.14893740490763</v>
+      </c>
+      <c r="E62">
+        <v>38.41999999999999</v>
+      </c>
+      <c r="F62">
+        <v>99.71999999999998</v>
+      </c>
+      <c r="G62">
+        <v>3.75</v>
+      </c>
+      <c r="H62">
+        <v>104.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>16.8</v>
+      </c>
+      <c r="K62">
+        <v>5.87</v>
+      </c>
+      <c r="L62">
+        <v>10.93</v>
+      </c>
+      <c r="M62">
+        <v>21.32013599999999</v>
+      </c>
+      <c r="N62">
+        <v>-10.39013599999999</v>
+      </c>
+      <c r="O62">
+        <v>-2.285829919999999</v>
+      </c>
+      <c r="P62">
+        <v>-8.104306079999997</v>
+      </c>
+      <c r="Q62">
+        <v>-2.234306079999997</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1301763635596435</v>
+      </c>
+      <c r="T62">
+        <v>1.545022839042334</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.1127853968661363</v>
+      </c>
+      <c r="W62">
+        <v>0.18968648215002</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5126608948460742</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1676324347138694</v>
+      </c>
+      <c r="C63">
+        <v>-53.0963448064708</v>
+      </c>
+      <c r="D63">
+        <v>44.53565519352919</v>
+      </c>
+      <c r="E63">
+        <v>40.08199999999999</v>
+      </c>
+      <c r="F63">
+        <v>101.382</v>
+      </c>
+      <c r="G63">
+        <v>3.75</v>
+      </c>
+      <c r="H63">
+        <v>104.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>16.8</v>
+      </c>
+      <c r="K63">
+        <v>5.87</v>
+      </c>
+      <c r="L63">
+        <v>10.93</v>
+      </c>
+      <c r="M63">
+        <v>21.6754716</v>
+      </c>
+      <c r="N63">
+        <v>-10.7454716</v>
+      </c>
+      <c r="O63">
+        <v>-2.364003751999999</v>
+      </c>
+      <c r="P63">
+        <v>-8.381467848</v>
+      </c>
+      <c r="Q63">
+        <v>-2.511467848</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1325193472406599</v>
+      </c>
+      <c r="T63">
+        <v>1.584638809274189</v>
+      </c>
+      <c r="U63">
+        <v>0.2138</v>
+      </c>
+      <c r="V63">
+        <v>0.1109364559339046</v>
+      </c>
+      <c r="W63">
+        <v>0.1900817857213312</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.5042566178813844</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1851601722564507</v>
+      </c>
+      <c r="C64">
+        <v>-60.09182633689223</v>
+      </c>
+      <c r="D64">
+        <v>39.20217366310777</v>
+      </c>
+      <c r="E64">
+        <v>41.744</v>
+      </c>
+      <c r="F64">
+        <v>103.044</v>
+      </c>
+      <c r="G64">
+        <v>3.75</v>
+      </c>
+      <c r="H64">
+        <v>104.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>16.8</v>
+      </c>
+      <c r="K64">
+        <v>5.87</v>
+      </c>
+      <c r="L64">
+        <v>10.93</v>
+      </c>
+      <c r="M64">
+        <v>24.6069072</v>
+      </c>
+      <c r="N64">
+        <v>-13.6769072</v>
+      </c>
+      <c r="O64">
+        <v>-3.008919584</v>
+      </c>
+      <c r="P64">
+        <v>-10.667987616</v>
+      </c>
+      <c r="Q64">
+        <v>-4.797987616000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.135716534122207</v>
+      </c>
+      <c r="T64">
+        <v>1.638697939669025</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.09772052946174395</v>
+      </c>
+      <c r="W64">
+        <v>0.2154643375645356</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.444184224826109</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1871601722564507</v>
+      </c>
+      <c r="C65">
+        <v>-62.28229935046277</v>
+      </c>
+      <c r="D65">
+        <v>38.67370064953722</v>
+      </c>
+      <c r="E65">
+        <v>43.40599999999999</v>
+      </c>
+      <c r="F65">
+        <v>104.706</v>
+      </c>
+      <c r="G65">
+        <v>3.75</v>
+      </c>
+      <c r="H65">
+        <v>104.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>16.8</v>
+      </c>
+      <c r="K65">
+        <v>5.87</v>
+      </c>
+      <c r="L65">
+        <v>10.93</v>
+      </c>
+      <c r="M65">
+        <v>25.0037928</v>
+      </c>
+      <c r="N65">
+        <v>-14.0737928</v>
+      </c>
+      <c r="O65">
+        <v>-3.096234416</v>
+      </c>
+      <c r="P65">
+        <v>-10.977558384</v>
+      </c>
+      <c r="Q65">
+        <v>-5.107558384</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1383358999092937</v>
+      </c>
+      <c r="T65">
+        <v>1.682987073173593</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.09616940994647818</v>
+      </c>
+      <c r="W65">
+        <v>0.215834744904781</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.437133681574901</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1891601722564507</v>
+      </c>
+      <c r="C66">
+        <v>-64.45871350773811</v>
+      </c>
+      <c r="D66">
+        <v>38.15928649226189</v>
+      </c>
+      <c r="E66">
+        <v>45.068</v>
+      </c>
+      <c r="F66">
+        <v>106.368</v>
+      </c>
+      <c r="G66">
+        <v>3.75</v>
+      </c>
+      <c r="H66">
+        <v>104.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>16.8</v>
+      </c>
+      <c r="K66">
+        <v>5.87</v>
+      </c>
+      <c r="L66">
+        <v>10.93</v>
+      </c>
+      <c r="M66">
+        <v>25.4006784</v>
+      </c>
+      <c r="N66">
+        <v>-14.4706784</v>
+      </c>
+      <c r="O66">
+        <v>-3.183549248</v>
+      </c>
+      <c r="P66">
+        <v>-11.287129152</v>
+      </c>
+      <c r="Q66">
+        <v>-5.417129152</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1411007860178852</v>
+      </c>
+      <c r="T66">
+        <v>1.729736714095082</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.09466676291606446</v>
+      </c>
+      <c r="W66">
+        <v>0.2161935770156438</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.430303467800293</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1911601722564507</v>
+      </c>
+      <c r="C67">
+        <v>-66.62162245168486</v>
+      </c>
+      <c r="D67">
+        <v>37.65837754831514</v>
+      </c>
+      <c r="E67">
+        <v>46.73</v>
+      </c>
+      <c r="F67">
+        <v>108.03</v>
+      </c>
+      <c r="G67">
+        <v>3.75</v>
+      </c>
+      <c r="H67">
+        <v>104.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>16.8</v>
+      </c>
+      <c r="K67">
+        <v>5.87</v>
+      </c>
+      <c r="L67">
+        <v>10.93</v>
+      </c>
+      <c r="M67">
+        <v>25.797564</v>
+      </c>
+      <c r="N67">
+        <v>-14.867564</v>
+      </c>
+      <c r="O67">
+        <v>-3.27086408</v>
+      </c>
+      <c r="P67">
+        <v>-11.59669992</v>
+      </c>
+      <c r="Q67">
+        <v>-5.726699920000002</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1440236656183962</v>
+      </c>
+      <c r="T67">
+        <v>1.779157763069227</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.09321035117889423</v>
+      </c>
+      <c r="W67">
+        <v>0.2165413681384801</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.4236834144495193</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1931601722564507</v>
+      </c>
+      <c r="C68">
+        <v>-68.77155113170409</v>
+      </c>
+      <c r="D68">
+        <v>37.17044886829591</v>
+      </c>
+      <c r="E68">
+        <v>48.392</v>
+      </c>
+      <c r="F68">
+        <v>109.692</v>
+      </c>
+      <c r="G68">
+        <v>3.75</v>
+      </c>
+      <c r="H68">
+        <v>104.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>16.8</v>
+      </c>
+      <c r="K68">
+        <v>5.87</v>
+      </c>
+      <c r="L68">
+        <v>10.93</v>
+      </c>
+      <c r="M68">
+        <v>26.1944496</v>
+      </c>
+      <c r="N68">
+        <v>-15.2644496</v>
+      </c>
+      <c r="O68">
+        <v>-3.358178911999999</v>
+      </c>
+      <c r="P68">
+        <v>-11.906270688</v>
+      </c>
+      <c r="Q68">
+        <v>-6.036270687999999</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1471184793130549</v>
+      </c>
+      <c r="T68">
+        <v>1.831485932571263</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.09179807313072919</v>
+      </c>
+      <c r="W68">
+        <v>0.2168786201363819</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.4172639687760418</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1951601722564507</v>
+      </c>
+      <c r="C69">
+        <v>-70.90899763872548</v>
+      </c>
+      <c r="D69">
+        <v>36.69500236127452</v>
+      </c>
+      <c r="E69">
+        <v>50.054</v>
+      </c>
+      <c r="F69">
+        <v>111.354</v>
+      </c>
+      <c r="G69">
+        <v>3.75</v>
+      </c>
+      <c r="H69">
+        <v>104.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>16.8</v>
+      </c>
+      <c r="K69">
+        <v>5.87</v>
+      </c>
+      <c r="L69">
+        <v>10.93</v>
+      </c>
+      <c r="M69">
+        <v>26.5913352</v>
+      </c>
+      <c r="N69">
+        <v>-15.6613352</v>
+      </c>
+      <c r="O69">
+        <v>-3.445493744</v>
+      </c>
+      <c r="P69">
+        <v>-12.215841456</v>
+      </c>
+      <c r="Q69">
+        <v>-6.345841456</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1504008574740566</v>
+      </c>
+      <c r="T69">
+        <v>1.886985506285544</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.09042795263624068</v>
+      </c>
+      <c r="W69">
+        <v>0.2172058049104657</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.4110361483465486</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1971601722564507</v>
+      </c>
+      <c r="C70">
+        <v>-73.03443490124437</v>
+      </c>
+      <c r="D70">
+        <v>36.23156509875564</v>
+      </c>
+      <c r="E70">
+        <v>51.71600000000001</v>
+      </c>
+      <c r="F70">
+        <v>113.016</v>
+      </c>
+      <c r="G70">
+        <v>3.75</v>
+      </c>
+      <c r="H70">
+        <v>104.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>16.8</v>
+      </c>
+      <c r="K70">
+        <v>5.87</v>
+      </c>
+      <c r="L70">
+        <v>10.93</v>
+      </c>
+      <c r="M70">
+        <v>26.9882208</v>
+      </c>
+      <c r="N70">
+        <v>-16.0582208</v>
+      </c>
+      <c r="O70">
+        <v>-3.532808576000001</v>
+      </c>
+      <c r="P70">
+        <v>-12.525412224</v>
+      </c>
+      <c r="Q70">
+        <v>-6.655412224000004</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1538883842701208</v>
+      </c>
+      <c r="T70">
+        <v>1.945953803356967</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.08909812980335477</v>
+      </c>
+      <c r="W70">
+        <v>0.2175233666029589</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.4049914991061582</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1991601722564507</v>
+      </c>
+      <c r="C71">
+        <v>-75.14831225444166</v>
+      </c>
+      <c r="D71">
+        <v>35.77968774555833</v>
+      </c>
+      <c r="E71">
+        <v>53.378</v>
+      </c>
+      <c r="F71">
+        <v>114.678</v>
+      </c>
+      <c r="G71">
+        <v>3.75</v>
+      </c>
+      <c r="H71">
+        <v>104.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>16.8</v>
+      </c>
+      <c r="K71">
+        <v>5.87</v>
+      </c>
+      <c r="L71">
+        <v>10.93</v>
+      </c>
+      <c r="M71">
+        <v>27.3851064</v>
+      </c>
+      <c r="N71">
+        <v>-16.4551064</v>
+      </c>
+      <c r="O71">
+        <v>-3.620123408</v>
+      </c>
+      <c r="P71">
+        <v>-12.834982992</v>
+      </c>
+      <c r="Q71">
+        <v>-6.964982992000002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1576009127949634</v>
+      </c>
+      <c r="T71">
+        <v>2.008726506691063</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.0878068525598279</v>
+      </c>
+      <c r="W71">
+        <v>0.2178317236087131</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3991220570901269</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2011601722564507</v>
+      </c>
+      <c r="C72">
+        <v>-77.25105689333063</v>
+      </c>
+      <c r="D72">
+        <v>35.33894310666938</v>
+      </c>
+      <c r="E72">
+        <v>55.04000000000001</v>
+      </c>
+      <c r="F72">
+        <v>116.34</v>
+      </c>
+      <c r="G72">
+        <v>3.75</v>
+      </c>
+      <c r="H72">
+        <v>104.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>16.8</v>
+      </c>
+      <c r="K72">
+        <v>5.87</v>
+      </c>
+      <c r="L72">
+        <v>10.93</v>
+      </c>
+      <c r="M72">
+        <v>27.781992</v>
+      </c>
+      <c r="N72">
+        <v>-16.851992</v>
+      </c>
+      <c r="O72">
+        <v>-3.70743824</v>
+      </c>
+      <c r="P72">
+        <v>-13.14455376</v>
+      </c>
+      <c r="Q72">
+        <v>-7.274553760000003</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1615609432214622</v>
+      </c>
+      <c r="T72">
+        <v>2.075684056914098</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.08655246895183036</v>
+      </c>
+      <c r="W72">
+        <v>0.2181312704143029</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3934203134174108</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2031601722564507</v>
+      </c>
+      <c r="C73">
+        <v>-79.34307521980853</v>
+      </c>
+      <c r="D73">
+        <v>34.90892478019145</v>
+      </c>
+      <c r="E73">
+        <v>56.70199999999998</v>
+      </c>
+      <c r="F73">
+        <v>118.002</v>
+      </c>
+      <c r="G73">
+        <v>3.75</v>
+      </c>
+      <c r="H73">
+        <v>104.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>16.8</v>
+      </c>
+      <c r="K73">
+        <v>5.87</v>
+      </c>
+      <c r="L73">
+        <v>10.93</v>
+      </c>
+      <c r="M73">
+        <v>28.1788776</v>
+      </c>
+      <c r="N73">
+        <v>-17.2488776</v>
+      </c>
+      <c r="O73">
+        <v>-3.794753071999999</v>
+      </c>
+      <c r="P73">
+        <v>-13.454124528</v>
+      </c>
+      <c r="Q73">
+        <v>-7.584124527999998</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1657940791946161</v>
+      </c>
+      <c r="T73">
+        <v>2.147259369221481</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.0853334200933539</v>
+      </c>
+      <c r="W73">
+        <v>0.2184223792817071</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3878791822425177</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2051601722564507</v>
+      </c>
+      <c r="C74">
+        <v>-81.42475409254232</v>
+      </c>
+      <c r="D74">
+        <v>34.48924590745768</v>
+      </c>
+      <c r="E74">
+        <v>58.36399999999999</v>
+      </c>
+      <c r="F74">
+        <v>119.664</v>
+      </c>
+      <c r="G74">
+        <v>3.75</v>
+      </c>
+      <c r="H74">
+        <v>104.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>16.8</v>
+      </c>
+      <c r="K74">
+        <v>5.87</v>
+      </c>
+      <c r="L74">
+        <v>10.93</v>
+      </c>
+      <c r="M74">
+        <v>28.5757632</v>
+      </c>
+      <c r="N74">
+        <v>-17.6457632</v>
+      </c>
+      <c r="O74">
+        <v>-3.882067903999999</v>
+      </c>
+      <c r="P74">
+        <v>-13.763695296</v>
+      </c>
+      <c r="Q74">
+        <v>-7.893695295999998</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1703295820229952</v>
+      </c>
+      <c r="T74">
+        <v>2.223947203836533</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.08414823370316842</v>
+      </c>
+      <c r="W74">
+        <v>0.2187054017916834</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3824919713780384</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2071601722564507</v>
+      </c>
+      <c r="C75">
+        <v>-83.49646198776733</v>
+      </c>
+      <c r="D75">
+        <v>34.07953801223265</v>
+      </c>
+      <c r="E75">
+        <v>60.026</v>
+      </c>
+      <c r="F75">
+        <v>121.326</v>
+      </c>
+      <c r="G75">
+        <v>3.75</v>
+      </c>
+      <c r="H75">
+        <v>104.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>16.8</v>
+      </c>
+      <c r="K75">
+        <v>5.87</v>
+      </c>
+      <c r="L75">
+        <v>10.93</v>
+      </c>
+      <c r="M75">
+        <v>28.9726488</v>
+      </c>
+      <c r="N75">
+        <v>-18.0426488</v>
+      </c>
+      <c r="O75">
+        <v>-3.969382735999999</v>
+      </c>
+      <c r="P75">
+        <v>-14.073266064</v>
+      </c>
+      <c r="Q75">
+        <v>-8.203266063999997</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1752010480238469</v>
+      </c>
+      <c r="T75">
+        <v>2.306315618793442</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.08299551817298803</v>
+      </c>
+      <c r="W75">
+        <v>0.2189806702602905</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3772523553317638</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2091601722564507</v>
+      </c>
+      <c r="C76">
+        <v>-85.55855007832093</v>
+      </c>
+      <c r="D76">
+        <v>33.67944992167905</v>
+      </c>
+      <c r="E76">
+        <v>61.68799999999999</v>
+      </c>
+      <c r="F76">
+        <v>122.988</v>
+      </c>
+      <c r="G76">
+        <v>3.75</v>
+      </c>
+      <c r="H76">
+        <v>104.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>16.8</v>
+      </c>
+      <c r="K76">
+        <v>5.87</v>
+      </c>
+      <c r="L76">
+        <v>10.93</v>
+      </c>
+      <c r="M76">
+        <v>29.3695344</v>
+      </c>
+      <c r="N76">
+        <v>-18.4395344</v>
+      </c>
+      <c r="O76">
+        <v>-4.056697568</v>
+      </c>
+      <c r="P76">
+        <v>-14.382836832</v>
+      </c>
+      <c r="Q76">
+        <v>-8.512836831999998</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1804472421786102</v>
+      </c>
+      <c r="T76">
+        <v>2.395020065670113</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.08187395711659629</v>
+      </c>
+      <c r="W76">
+        <v>0.2192484990405568</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3721543505299832</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2111601722564507</v>
+      </c>
+      <c r="C77">
+        <v>-87.61135323755158</v>
+      </c>
+      <c r="D77">
+        <v>33.28864676244841</v>
+      </c>
+      <c r="E77">
+        <v>63.34999999999999</v>
+      </c>
+      <c r="F77">
+        <v>124.65</v>
+      </c>
+      <c r="G77">
+        <v>3.75</v>
+      </c>
+      <c r="H77">
+        <v>104.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>16.8</v>
+      </c>
+      <c r="K77">
+        <v>5.87</v>
+      </c>
+      <c r="L77">
+        <v>10.93</v>
+      </c>
+      <c r="M77">
+        <v>29.76642</v>
+      </c>
+      <c r="N77">
+        <v>-18.83642</v>
+      </c>
+      <c r="O77">
+        <v>-4.144012399999999</v>
+      </c>
+      <c r="P77">
+        <v>-14.6924076</v>
+      </c>
+      <c r="Q77">
+        <v>-8.822407600000002</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1861131318657546</v>
+      </c>
+      <c r="T77">
+        <v>2.490820868296918</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.08078230435504168</v>
+      </c>
+      <c r="W77">
+        <v>0.2195091857200161</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3671922925229167</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2131601722564507</v>
+      </c>
+      <c r="C78">
+        <v>-89.6551909741361</v>
+      </c>
+      <c r="D78">
+        <v>32.90680902586389</v>
+      </c>
+      <c r="E78">
+        <v>65.012</v>
+      </c>
+      <c r="F78">
+        <v>126.312</v>
+      </c>
+      <c r="G78">
+        <v>3.75</v>
+      </c>
+      <c r="H78">
+        <v>104.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>16.8</v>
+      </c>
+      <c r="K78">
+        <v>5.87</v>
+      </c>
+      <c r="L78">
+        <v>10.93</v>
+      </c>
+      <c r="M78">
+        <v>30.1633056</v>
+      </c>
+      <c r="N78">
+        <v>-19.2333056</v>
+      </c>
+      <c r="O78">
+        <v>-4.231327232</v>
+      </c>
+      <c r="P78">
+        <v>-15.001978368</v>
+      </c>
+      <c r="Q78">
+        <v>-9.131978368000002</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1922511790268277</v>
+      </c>
+      <c r="T78">
+        <v>2.594605071142623</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.07971937929773849</v>
+      </c>
+      <c r="W78">
+        <v>0.2197630122237</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3623608149897205</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2151601722564507</v>
+      </c>
+      <c r="C79">
+        <v>-91.69036830328972</v>
+      </c>
+      <c r="D79">
+        <v>32.53363169671027</v>
+      </c>
+      <c r="E79">
+        <v>66.67399999999999</v>
+      </c>
+      <c r="F79">
+        <v>127.974</v>
+      </c>
+      <c r="G79">
+        <v>3.75</v>
+      </c>
+      <c r="H79">
+        <v>104.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>16.8</v>
+      </c>
+      <c r="K79">
+        <v>5.87</v>
+      </c>
+      <c r="L79">
+        <v>10.93</v>
+      </c>
+      <c r="M79">
+        <v>30.5601912</v>
+      </c>
+      <c r="N79">
+        <v>-19.6301912</v>
+      </c>
+      <c r="O79">
+        <v>-4.318642064</v>
+      </c>
+      <c r="P79">
+        <v>-15.311549136</v>
+      </c>
+      <c r="Q79">
+        <v>-9.441549135999999</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.1989229694192985</v>
+      </c>
+      <c r="T79">
+        <v>2.707413987279259</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.07868406268348216</v>
+      </c>
+      <c r="W79">
+        <v>0.2200102458311845</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3576548303794644</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2171601722564507</v>
+      </c>
+      <c r="C80">
+        <v>-93.71717655936082</v>
+      </c>
+      <c r="D80">
+        <v>32.16882344063917</v>
+      </c>
+      <c r="E80">
+        <v>68.336</v>
+      </c>
+      <c r="F80">
+        <v>129.636</v>
+      </c>
+      <c r="G80">
+        <v>3.75</v>
+      </c>
+      <c r="H80">
+        <v>104.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>16.8</v>
+      </c>
+      <c r="K80">
+        <v>5.87</v>
+      </c>
+      <c r="L80">
+        <v>10.93</v>
+      </c>
+      <c r="M80">
+        <v>30.9570768</v>
+      </c>
+      <c r="N80">
+        <v>-20.0270768</v>
+      </c>
+      <c r="O80">
+        <v>-4.405956895999999</v>
+      </c>
+      <c r="P80">
+        <v>-15.621119904</v>
+      </c>
+      <c r="Q80">
+        <v>-9.751119903999999</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2062012862110848</v>
+      </c>
+      <c r="T80">
+        <v>2.830478259428316</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.07767529264907853</v>
+      </c>
+      <c r="W80">
+        <v>0.2202511401154</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3530695120412661</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2191601722564507</v>
+      </c>
+      <c r="C81">
+        <v>-95.7358941543618</v>
+      </c>
+      <c r="D81">
+        <v>31.81210584563819</v>
+      </c>
+      <c r="E81">
+        <v>69.998</v>
+      </c>
+      <c r="F81">
+        <v>131.298</v>
+      </c>
+      <c r="G81">
+        <v>3.75</v>
+      </c>
+      <c r="H81">
+        <v>104.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>16.8</v>
+      </c>
+      <c r="K81">
+        <v>5.87</v>
+      </c>
+      <c r="L81">
+        <v>10.93</v>
+      </c>
+      <c r="M81">
+        <v>31.3539624</v>
+      </c>
+      <c r="N81">
+        <v>-20.4239624</v>
+      </c>
+      <c r="O81">
+        <v>-4.493271728</v>
+      </c>
+      <c r="P81">
+        <v>-15.930690672</v>
+      </c>
+      <c r="Q81">
+        <v>-10.060690672</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2141727760306603</v>
+      </c>
+      <c r="T81">
+        <v>2.965262938448712</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.07669206109655856</v>
+      </c>
+      <c r="W81">
+        <v>0.2204859358101418</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3486002777116298</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2211601722564507</v>
+      </c>
+      <c r="C82">
+        <v>-97.74678728658478</v>
+      </c>
+      <c r="D82">
+        <v>31.46321271341523</v>
+      </c>
+      <c r="E82">
+        <v>71.66000000000001</v>
+      </c>
+      <c r="F82">
+        <v>132.96</v>
+      </c>
+      <c r="G82">
+        <v>3.75</v>
+      </c>
+      <c r="H82">
+        <v>104.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>16.8</v>
+      </c>
+      <c r="K82">
+        <v>5.87</v>
+      </c>
+      <c r="L82">
+        <v>10.93</v>
+      </c>
+      <c r="M82">
+        <v>31.750848</v>
+      </c>
+      <c r="N82">
+        <v>-20.82084800000001</v>
+      </c>
+      <c r="O82">
+        <v>-4.58058656</v>
+      </c>
+      <c r="P82">
+        <v>-16.24026144</v>
+      </c>
+      <c r="Q82">
+        <v>-10.37026144</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2229414148321933</v>
+      </c>
+      <c r="T82">
+        <v>3.113526085371148</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.07573341033285157</v>
+      </c>
+      <c r="W82">
+        <v>0.2207148616125151</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3442427742402344</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2231601722564507</v>
+      </c>
+      <c r="C83">
+        <v>-99.75011060309424</v>
+      </c>
+      <c r="D83">
+        <v>31.12188939690574</v>
+      </c>
+      <c r="E83">
+        <v>73.32199999999999</v>
+      </c>
+      <c r="F83">
+        <v>134.622</v>
+      </c>
+      <c r="G83">
+        <v>3.75</v>
+      </c>
+      <c r="H83">
+        <v>104.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>16.8</v>
+      </c>
+      <c r="K83">
+        <v>5.87</v>
+      </c>
+      <c r="L83">
+        <v>10.93</v>
+      </c>
+      <c r="M83">
+        <v>32.1477336</v>
+      </c>
+      <c r="N83">
+        <v>-21.2177336</v>
+      </c>
+      <c r="O83">
+        <v>-4.667901391999998</v>
+      </c>
+      <c r="P83">
+        <v>-16.549832208</v>
+      </c>
+      <c r="Q83">
+        <v>-10.679832208</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.232633068244414</v>
+      </c>
+      <c r="T83">
+        <v>3.27739587933805</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.07479842995837194</v>
+      </c>
+      <c r="W83">
+        <v>0.2209381349259408</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3399928634471452</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2251601722564507</v>
+      </c>
+      <c r="C84">
+        <v>-101.7461078195604</v>
+      </c>
+      <c r="D84">
+        <v>30.78789218043955</v>
+      </c>
+      <c r="E84">
+        <v>74.98399999999999</v>
+      </c>
+      <c r="F84">
+        <v>136.284</v>
+      </c>
+      <c r="G84">
+        <v>3.75</v>
+      </c>
+      <c r="H84">
+        <v>104.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>16.8</v>
+      </c>
+      <c r="K84">
+        <v>5.87</v>
+      </c>
+      <c r="L84">
+        <v>10.93</v>
+      </c>
+      <c r="M84">
+        <v>32.5446192</v>
+      </c>
+      <c r="N84">
+        <v>-21.6146192</v>
+      </c>
+      <c r="O84">
+        <v>-4.755216224</v>
+      </c>
+      <c r="P84">
+        <v>-16.859402976</v>
+      </c>
+      <c r="Q84">
+        <v>-10.989402976</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2434015720357704</v>
+      </c>
+      <c r="T84">
+        <v>3.459473428190164</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.07388625398326983</v>
+      </c>
+      <c r="W84">
+        <v>0.2211559625487952</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3358466090148629</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2271601722564507</v>
+      </c>
+      <c r="C85">
+        <v>-103.7350123006046</v>
+      </c>
+      <c r="D85">
+        <v>30.46098769939541</v>
+      </c>
+      <c r="E85">
+        <v>76.646</v>
+      </c>
+      <c r="F85">
+        <v>137.946</v>
+      </c>
+      <c r="G85">
+        <v>3.75</v>
+      </c>
+      <c r="H85">
+        <v>104.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>16.8</v>
+      </c>
+      <c r="K85">
+        <v>5.87</v>
+      </c>
+      <c r="L85">
+        <v>10.93</v>
+      </c>
+      <c r="M85">
+        <v>32.9415048</v>
+      </c>
+      <c r="N85">
+        <v>-22.0115048</v>
+      </c>
+      <c r="O85">
+        <v>-4.842531056</v>
+      </c>
+      <c r="P85">
+        <v>-17.16897374400001</v>
+      </c>
+      <c r="Q85">
+        <v>-11.298973744</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2554369586261098</v>
+      </c>
+      <c r="T85">
+        <v>3.662971865142527</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.07299605815214609</v>
+      </c>
+      <c r="W85">
+        <v>0.2213685413132675</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3318002643279367</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2291601722564507</v>
+      </c>
+      <c r="C86">
+        <v>-105.7170476035602</v>
+      </c>
+      <c r="D86">
+        <v>30.14095239643975</v>
+      </c>
+      <c r="E86">
+        <v>78.30799999999998</v>
+      </c>
+      <c r="F86">
+        <v>139.608</v>
+      </c>
+      <c r="G86">
+        <v>3.75</v>
+      </c>
+      <c r="H86">
+        <v>104.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>16.8</v>
+      </c>
+      <c r="K86">
+        <v>5.87</v>
+      </c>
+      <c r="L86">
+        <v>10.93</v>
+      </c>
+      <c r="M86">
+        <v>33.33839039999999</v>
+      </c>
+      <c r="N86">
+        <v>-22.40839039999999</v>
+      </c>
+      <c r="O86">
+        <v>-4.929845887999998</v>
+      </c>
+      <c r="P86">
+        <v>-17.478544512</v>
+      </c>
+      <c r="Q86">
+        <v>-11.60854451199999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2689767685402416</v>
+      </c>
+      <c r="T86">
+        <v>3.891907606713933</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.07212705745985865</v>
+      </c>
+      <c r="W86">
+        <v>0.2215760586785858</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3278502611811758</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2311601722564507</v>
+      </c>
+      <c r="C87">
+        <v>-107.6924279883132</v>
+      </c>
+      <c r="D87">
+        <v>29.82757201168675</v>
+      </c>
+      <c r="E87">
+        <v>79.96999999999998</v>
+      </c>
+      <c r="F87">
+        <v>141.27</v>
+      </c>
+      <c r="G87">
+        <v>3.75</v>
+      </c>
+      <c r="H87">
+        <v>104.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>16.8</v>
+      </c>
+      <c r="K87">
+        <v>5.87</v>
+      </c>
+      <c r="L87">
+        <v>10.93</v>
+      </c>
+      <c r="M87">
+        <v>33.735276</v>
+      </c>
+      <c r="N87">
+        <v>-22.805276</v>
+      </c>
+      <c r="O87">
+        <v>-5.017160719999999</v>
+      </c>
+      <c r="P87">
+        <v>-17.78811528</v>
+      </c>
+      <c r="Q87">
+        <v>-11.91811528</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.2843218864429243</v>
+      </c>
+      <c r="T87">
+        <v>4.151368113828195</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.07127850384268383</v>
+      </c>
+      <c r="W87">
+        <v>0.2217786932823671</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3239931992849265</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2331601722564507</v>
+      </c>
+      <c r="C88">
+        <v>-109.6613588956632</v>
+      </c>
+      <c r="D88">
+        <v>29.52064110433676</v>
+      </c>
+      <c r="E88">
+        <v>81.63199999999999</v>
+      </c>
+      <c r="F88">
+        <v>142.932</v>
+      </c>
+      <c r="G88">
+        <v>3.75</v>
+      </c>
+      <c r="H88">
+        <v>104.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>16.8</v>
+      </c>
+      <c r="K88">
+        <v>5.87</v>
+      </c>
+      <c r="L88">
+        <v>10.93</v>
+      </c>
+      <c r="M88">
+        <v>34.1321616</v>
+      </c>
+      <c r="N88">
+        <v>-23.2021616</v>
+      </c>
+      <c r="O88">
+        <v>-5.104475551999998</v>
+      </c>
+      <c r="P88">
+        <v>-18.097686048</v>
+      </c>
+      <c r="Q88">
+        <v>-12.227686048</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3018591640459904</v>
+      </c>
+      <c r="T88">
+        <v>4.447894407673067</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.07044968403055961</v>
+      </c>
+      <c r="W88">
+        <v>0.2219766154535024</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3202258365025438</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2351601722564507</v>
+      </c>
+      <c r="C89">
+        <v>-111.6240373964519</v>
+      </c>
+      <c r="D89">
+        <v>29.21996260354808</v>
+      </c>
+      <c r="E89">
+        <v>83.294</v>
+      </c>
+      <c r="F89">
+        <v>144.594</v>
+      </c>
+      <c r="G89">
+        <v>3.75</v>
+      </c>
+      <c r="H89">
+        <v>104.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>16.8</v>
+      </c>
+      <c r="K89">
+        <v>5.87</v>
+      </c>
+      <c r="L89">
+        <v>10.93</v>
+      </c>
+      <c r="M89">
+        <v>34.5290472</v>
+      </c>
+      <c r="N89">
+        <v>-23.5990472</v>
+      </c>
+      <c r="O89">
+        <v>-5.191790384</v>
+      </c>
+      <c r="P89">
+        <v>-18.407256816</v>
+      </c>
+      <c r="Q89">
+        <v>-12.537256816</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3220944843572204</v>
+      </c>
+      <c r="T89">
+        <v>4.790040131340226</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.06963991754744972</v>
+      </c>
+      <c r="W89">
+        <v>0.222169987689669</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3165450797611351</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2371601722564507</v>
+      </c>
+      <c r="C90">
+        <v>-113.5806526135205</v>
+      </c>
+      <c r="D90">
+        <v>28.92534738647949</v>
+      </c>
+      <c r="E90">
+        <v>84.956</v>
+      </c>
+      <c r="F90">
+        <v>146.256</v>
+      </c>
+      <c r="G90">
+        <v>3.75</v>
+      </c>
+      <c r="H90">
+        <v>104.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>16.8</v>
+      </c>
+      <c r="K90">
+        <v>5.87</v>
+      </c>
+      <c r="L90">
+        <v>10.93</v>
+      </c>
+      <c r="M90">
+        <v>34.92593280000001</v>
+      </c>
+      <c r="N90">
+        <v>-23.99593280000001</v>
+      </c>
+      <c r="O90">
+        <v>-5.279105216</v>
+      </c>
+      <c r="P90">
+        <v>-18.716827584</v>
+      </c>
+      <c r="Q90">
+        <v>-12.846827584</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3457023580536555</v>
+      </c>
+      <c r="T90">
+        <v>5.189210142285245</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.06884855484804688</v>
+      </c>
+      <c r="W90">
+        <v>0.2223589651022864</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3129479765820313</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2391601722564507</v>
+      </c>
+      <c r="C91">
+        <v>-115.5313861183954</v>
+      </c>
+      <c r="D91">
+        <v>28.63661388160454</v>
+      </c>
+      <c r="E91">
+        <v>86.61799999999998</v>
+      </c>
+      <c r="F91">
+        <v>147.918</v>
+      </c>
+      <c r="G91">
+        <v>3.75</v>
+      </c>
+      <c r="H91">
+        <v>104.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>16.8</v>
+      </c>
+      <c r="K91">
+        <v>5.87</v>
+      </c>
+      <c r="L91">
+        <v>10.93</v>
+      </c>
+      <c r="M91">
+        <v>35.3228184</v>
+      </c>
+      <c r="N91">
+        <v>-24.3928184</v>
+      </c>
+      <c r="O91">
+        <v>-5.366420047999998</v>
+      </c>
+      <c r="P91">
+        <v>-19.026398352</v>
+      </c>
+      <c r="Q91">
+        <v>-13.156398352</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.3736025724221696</v>
+      </c>
+      <c r="T91">
+        <v>5.660956518856631</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.06807497558009132</v>
+      </c>
+      <c r="W91">
+        <v>0.2225436958314742</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3094317071822332</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2411601722564507</v>
+      </c>
+      <c r="C92">
+        <v>-117.4764123044506</v>
+      </c>
+      <c r="D92">
+        <v>28.35358769554936</v>
+      </c>
+      <c r="E92">
+        <v>88.27999999999999</v>
+      </c>
+      <c r="F92">
+        <v>149.58</v>
+      </c>
+      <c r="G92">
+        <v>3.75</v>
+      </c>
+      <c r="H92">
+        <v>104.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>16.8</v>
+      </c>
+      <c r="K92">
+        <v>5.87</v>
+      </c>
+      <c r="L92">
+        <v>10.93</v>
+      </c>
+      <c r="M92">
+        <v>35.719704</v>
+      </c>
+      <c r="N92">
+        <v>-24.789704</v>
+      </c>
+      <c r="O92">
+        <v>-5.45373488</v>
+      </c>
+      <c r="P92">
+        <v>-19.33596912</v>
+      </c>
+      <c r="Q92">
+        <v>-13.46596912</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4070828296643866</v>
+      </c>
+      <c r="T92">
+        <v>6.227052170742294</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.06731858696253473</v>
+      </c>
+      <c r="W92">
+        <v>0.2227243214333467</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3059935771024306</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2431601722564507</v>
+      </c>
+      <c r="C93">
+        <v>-119.4158987381572</v>
+      </c>
+      <c r="D93">
+        <v>28.07610126184282</v>
+      </c>
+      <c r="E93">
+        <v>89.94199999999999</v>
+      </c>
+      <c r="F93">
+        <v>151.242</v>
+      </c>
+      <c r="G93">
+        <v>3.75</v>
+      </c>
+      <c r="H93">
+        <v>104.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>16.8</v>
+      </c>
+      <c r="K93">
+        <v>5.87</v>
+      </c>
+      <c r="L93">
+        <v>10.93</v>
+      </c>
+      <c r="M93">
+        <v>36.1165896</v>
+      </c>
+      <c r="N93">
+        <v>-25.1865896</v>
+      </c>
+      <c r="O93">
+        <v>-5.541049711999999</v>
+      </c>
+      <c r="P93">
+        <v>-19.645539888</v>
+      </c>
+      <c r="Q93">
+        <v>-13.775539888</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4480031440715407</v>
+      </c>
+      <c r="T93">
+        <v>6.918946856380328</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.06657882227063874</v>
+      </c>
+      <c r="W93">
+        <v>0.2229009772417715</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3026310103210853</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2451601722564507</v>
+      </c>
+      <c r="C94">
+        <v>-121.3500064899083</v>
+      </c>
+      <c r="D94">
+        <v>27.80399351009166</v>
+      </c>
+      <c r="E94">
+        <v>91.604</v>
+      </c>
+      <c r="F94">
+        <v>152.904</v>
+      </c>
+      <c r="G94">
+        <v>3.75</v>
+      </c>
+      <c r="H94">
+        <v>104.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>16.8</v>
+      </c>
+      <c r="K94">
+        <v>5.87</v>
+      </c>
+      <c r="L94">
+        <v>10.93</v>
+      </c>
+      <c r="M94">
+        <v>36.5134752</v>
+      </c>
+      <c r="N94">
+        <v>-25.5834752</v>
+      </c>
+      <c r="O94">
+        <v>-5.628364544</v>
+      </c>
+      <c r="P94">
+        <v>-19.955110656</v>
+      </c>
+      <c r="Q94">
+        <v>-14.085110656</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.4991535370804834</v>
+      </c>
+      <c r="T94">
+        <v>7.783815213427871</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.06585513941987094</v>
+      </c>
+      <c r="W94">
+        <v>0.2230737927065348</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2993415428175952</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2471601722564507</v>
+      </c>
+      <c r="C95">
+        <v>-123.2788904457909</v>
+      </c>
+      <c r="D95">
+        <v>27.53710955420905</v>
+      </c>
+      <c r="E95">
+        <v>93.26600000000001</v>
+      </c>
+      <c r="F95">
+        <v>154.566</v>
+      </c>
+      <c r="G95">
+        <v>3.75</v>
+      </c>
+      <c r="H95">
+        <v>104.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>16.8</v>
+      </c>
+      <c r="K95">
+        <v>5.87</v>
+      </c>
+      <c r="L95">
+        <v>10.93</v>
+      </c>
+      <c r="M95">
+        <v>36.9103608</v>
+      </c>
+      <c r="N95">
+        <v>-25.9803608</v>
+      </c>
+      <c r="O95">
+        <v>-5.715679375999999</v>
+      </c>
+      <c r="P95">
+        <v>-20.264681424</v>
+      </c>
+      <c r="Q95">
+        <v>-14.394681424</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.5649183280919812</v>
+      </c>
+      <c r="T95">
+        <v>8.89578881534614</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.06514701964116264</v>
+      </c>
+      <c r="W95">
+        <v>0.2232428917096904</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2961228165507394</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2491601722564507</v>
+      </c>
+      <c r="C96">
+        <v>-125.202699601572</v>
+      </c>
+      <c r="D96">
+        <v>27.27530039842797</v>
+      </c>
+      <c r="E96">
+        <v>94.92800000000001</v>
+      </c>
+      <c r="F96">
+        <v>156.228</v>
+      </c>
+      <c r="G96">
+        <v>3.75</v>
+      </c>
+      <c r="H96">
+        <v>104.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>16.8</v>
+      </c>
+      <c r="K96">
+        <v>5.87</v>
+      </c>
+      <c r="L96">
+        <v>10.93</v>
+      </c>
+      <c r="M96">
+        <v>37.3072464</v>
+      </c>
+      <c r="N96">
+        <v>-26.3772464</v>
+      </c>
+      <c r="O96">
+        <v>-5.802994208</v>
+      </c>
+      <c r="P96">
+        <v>-20.574252192</v>
+      </c>
+      <c r="Q96">
+        <v>-14.704252192</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.6526047161073114</v>
+      </c>
+      <c r="T96">
+        <v>10.3784202845705</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.06445396624072473</v>
+      </c>
+      <c r="W96">
+        <v>0.2234083928617149</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2929725738214761</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2511601722564507</v>
+      </c>
+      <c r="C97">
+        <v>-127.1215773400727</v>
+      </c>
+      <c r="D97">
+        <v>27.01842265992729</v>
+      </c>
+      <c r="E97">
+        <v>96.58999999999999</v>
+      </c>
+      <c r="F97">
+        <v>157.89</v>
+      </c>
+      <c r="G97">
+        <v>3.75</v>
+      </c>
+      <c r="H97">
+        <v>104.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>16.8</v>
+      </c>
+      <c r="K97">
+        <v>5.87</v>
+      </c>
+      <c r="L97">
+        <v>10.93</v>
+      </c>
+      <c r="M97">
+        <v>37.704132</v>
+      </c>
+      <c r="N97">
+        <v>-26.774132</v>
+      </c>
+      <c r="O97">
+        <v>-5.89030904</v>
+      </c>
+      <c r="P97">
+        <v>-20.88382296</v>
+      </c>
+      <c r="Q97">
+        <v>-15.01382296</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.7753656593287741</v>
+      </c>
+      <c r="T97">
+        <v>12.45410434148461</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.0637755034381908</v>
+      </c>
+      <c r="W97">
+        <v>0.22357040977896</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2898886519917764</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2531601722564507</v>
+      </c>
+      <c r="C98">
+        <v>-129.0356616930149</v>
+      </c>
+      <c r="D98">
+        <v>26.76633830698506</v>
+      </c>
+      <c r="E98">
+        <v>98.252</v>
+      </c>
+      <c r="F98">
+        <v>159.552</v>
+      </c>
+      <c r="G98">
+        <v>3.75</v>
+      </c>
+      <c r="H98">
+        <v>104.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>16.8</v>
+      </c>
+      <c r="K98">
+        <v>5.87</v>
+      </c>
+      <c r="L98">
+        <v>10.93</v>
+      </c>
+      <c r="M98">
+        <v>38.1010176</v>
+      </c>
+      <c r="N98">
+        <v>-27.1710176</v>
+      </c>
+      <c r="O98">
+        <v>-5.977623871999999</v>
+      </c>
+      <c r="P98">
+        <v>-21.193393728</v>
+      </c>
+      <c r="Q98">
+        <v>-15.323393728</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.9595070741609655</v>
+      </c>
+      <c r="T98">
+        <v>15.56763042685572</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.06311117527737631</v>
+      </c>
+      <c r="W98">
+        <v>0.2237290513437626</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2868689785335288</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2551601722564507</v>
+      </c>
+      <c r="C99">
+        <v>-130.945085588345</v>
+      </c>
+      <c r="D99">
+        <v>26.51891441165501</v>
+      </c>
+      <c r="E99">
+        <v>99.914</v>
+      </c>
+      <c r="F99">
+        <v>161.214</v>
+      </c>
+      <c r="G99">
+        <v>3.75</v>
+      </c>
+      <c r="H99">
+        <v>104.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>16.8</v>
+      </c>
+      <c r="K99">
+        <v>5.87</v>
+      </c>
+      <c r="L99">
+        <v>10.93</v>
+      </c>
+      <c r="M99">
+        <v>38.4979032</v>
+      </c>
+      <c r="N99">
+        <v>-27.5679032</v>
+      </c>
+      <c r="O99">
+        <v>-6.064938704</v>
+      </c>
+      <c r="P99">
+        <v>-21.502964496</v>
+      </c>
+      <c r="Q99">
+        <v>-15.632964496</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.266409432214621</v>
+      </c>
+      <c r="T99">
+        <v>20.75684056914097</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.06246054460441366</v>
+      </c>
+      <c r="W99">
+        <v>0.223884421948466</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2839115663836985</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2571601722564507</v>
+      </c>
+      <c r="C100">
+        <v>-132.8499770839654</v>
+      </c>
+      <c r="D100">
+        <v>26.27602291603456</v>
+      </c>
+      <c r="E100">
+        <v>101.576</v>
+      </c>
+      <c r="F100">
+        <v>162.876</v>
+      </c>
+      <c r="G100">
+        <v>3.75</v>
+      </c>
+      <c r="H100">
+        <v>104.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>16.8</v>
+      </c>
+      <c r="K100">
+        <v>5.87</v>
+      </c>
+      <c r="L100">
+        <v>10.93</v>
+      </c>
+      <c r="M100">
+        <v>38.89478879999999</v>
+      </c>
+      <c r="N100">
+        <v>-27.96478879999999</v>
+      </c>
+      <c r="O100">
+        <v>-6.152253535999998</v>
+      </c>
+      <c r="P100">
+        <v>-21.812535264</v>
+      </c>
+      <c r="Q100">
+        <v>-15.942535264</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.880214148321931</v>
+      </c>
+      <c r="T100">
+        <v>31.13526085371145</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.06182319210845028</v>
+      </c>
+      <c r="W100">
+        <v>0.2240366217245021</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2810145095838649</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2591601722564507</v>
+      </c>
+      <c r="C101">
+        <v>-134.7504595887391</v>
+      </c>
+      <c r="D101">
+        <v>26.03754041126091</v>
+      </c>
+      <c r="E101">
+        <v>103.238</v>
+      </c>
+      <c r="F101">
+        <v>164.538</v>
+      </c>
+      <c r="G101">
+        <v>3.75</v>
+      </c>
+      <c r="H101">
+        <v>104.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>16.8</v>
+      </c>
+      <c r="K101">
+        <v>5.87</v>
+      </c>
+      <c r="L101">
+        <v>10.93</v>
+      </c>
+      <c r="M101">
+        <v>39.2916744</v>
+      </c>
+      <c r="N101">
+        <v>-28.3616744</v>
+      </c>
+      <c r="O101">
+        <v>-6.239568367999999</v>
+      </c>
+      <c r="P101">
+        <v>-22.122106032</v>
+      </c>
+      <c r="Q101">
+        <v>-16.252106032</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>3.721628296643862</v>
+      </c>
+      <c r="T101">
+        <v>62.27052170742288</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.06119871542048613</v>
+      </c>
+      <c r="W101">
+        <v>0.2241857467575879</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2781759791840278</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/denmark/denmark_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_farming_agriculture.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07129124021041604</v>
+        <v>0.07116949948195311</v>
       </c>
       <c r="C2">
-        <v>174.369494735668</v>
+        <v>172.9474325828151</v>
       </c>
       <c r="D2">
-        <v>151.069494735668</v>
+        <v>151.7944325828151</v>
       </c>
       <c r="E2">
-        <v>-104.8</v>
+        <v>-102.653</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.147</v>
       </c>
       <c r="G2">
         <v>23.3</v>
@@ -1451,28 +1451,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1079941</v>
       </c>
       <c r="N2">
-        <v>14.29666666666667</v>
+        <v>14.18867256666667</v>
       </c>
       <c r="O2">
-        <v>3.145266666666667</v>
+        <v>3.121507964666667</v>
       </c>
       <c r="P2">
-        <v>11.1514</v>
+        <v>11.067164602</v>
       </c>
       <c r="Q2">
-        <v>20.0214</v>
+        <v>19.937164602</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07129124021041604</v>
+        <v>0.07149208028480113</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5933505839445989</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>132.3837752864895</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07116949948195311</v>
+        <v>0.07104775875349019</v>
       </c>
       <c r="C3">
-        <v>172.9474325828151</v>
+        <v>171.5323615029095</v>
       </c>
       <c r="D3">
-        <v>151.7944325828151</v>
+        <v>152.5263615029095</v>
       </c>
       <c r="E3">
-        <v>-102.653</v>
+        <v>-100.506</v>
       </c>
       <c r="F3">
-        <v>2.147</v>
+        <v>4.294</v>
       </c>
       <c r="G3">
         <v>23.3</v>
@@ -1533,28 +1533,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M3">
-        <v>0.1079941</v>
+        <v>0.2159882</v>
       </c>
       <c r="N3">
-        <v>14.18867256666667</v>
+        <v>14.08067846666667</v>
       </c>
       <c r="O3">
-        <v>3.121507964666667</v>
+        <v>3.097749262666667</v>
       </c>
       <c r="P3">
-        <v>11.067164602</v>
+        <v>10.982929204</v>
       </c>
       <c r="Q3">
-        <v>19.937164602</v>
+        <v>19.852929204</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07149208028480113</v>
+        <v>0.07169701913621448</v>
       </c>
       <c r="T3">
-        <v>0.5933505839445989</v>
+        <v>0.5980835828225057</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>132.3837752864895</v>
+        <v>66.19188764324473</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07104775875349019</v>
+        <v>0.07092601802502729</v>
       </c>
       <c r="C4">
-        <v>171.5323615029095</v>
+        <v>170.124383115513</v>
       </c>
       <c r="D4">
-        <v>152.5263615029095</v>
+        <v>153.265383115513</v>
       </c>
       <c r="E4">
-        <v>-100.506</v>
+        <v>-98.35899999999999</v>
       </c>
       <c r="F4">
-        <v>4.294</v>
+        <v>6.441</v>
       </c>
       <c r="G4">
         <v>23.3</v>
@@ -1615,28 +1615,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M4">
-        <v>0.2159882</v>
+        <v>0.3239823</v>
       </c>
       <c r="N4">
-        <v>14.08067846666667</v>
+        <v>13.97268436666667</v>
       </c>
       <c r="O4">
-        <v>3.097749262666667</v>
+        <v>3.073990560666667</v>
       </c>
       <c r="P4">
-        <v>10.982929204</v>
+        <v>10.898693806</v>
       </c>
       <c r="Q4">
-        <v>19.852929204</v>
+        <v>19.768693806</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07169701913621448</v>
+        <v>0.07190618353095597</v>
       </c>
       <c r="T4">
-        <v>0.5980835828225057</v>
+        <v>0.6029141693061426</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>66.19188764324473</v>
+        <v>44.12792509549647</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07092601802502729</v>
+        <v>0.07080427729656437</v>
       </c>
       <c r="C5">
-        <v>170.124383115513</v>
+        <v>168.7236010192473</v>
       </c>
       <c r="D5">
-        <v>153.265383115513</v>
+        <v>154.0116010192473</v>
       </c>
       <c r="E5">
-        <v>-98.35899999999999</v>
+        <v>-96.212</v>
       </c>
       <c r="F5">
-        <v>6.441</v>
+        <v>8.587999999999999</v>
       </c>
       <c r="G5">
         <v>23.3</v>
@@ -1697,28 +1697,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M5">
-        <v>0.3239823</v>
+        <v>0.4319763999999999</v>
       </c>
       <c r="N5">
-        <v>13.97268436666667</v>
+        <v>13.86469026666667</v>
       </c>
       <c r="O5">
-        <v>3.073990560666667</v>
+        <v>3.050231858666667</v>
       </c>
       <c r="P5">
-        <v>10.898693806</v>
+        <v>10.814458408</v>
       </c>
       <c r="Q5">
-        <v>19.768693806</v>
+        <v>19.684458408</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07190618353095597</v>
+        <v>0.07211970551725455</v>
       </c>
       <c r="T5">
-        <v>0.6029141693061426</v>
+        <v>0.6078453930081885</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>44.12792509549647</v>
+        <v>33.09594382162236</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07080427729656437</v>
+        <v>0.07068253656810145</v>
       </c>
       <c r="C6">
-        <v>168.7236010192473</v>
+        <v>167.3301208402072</v>
       </c>
       <c r="D6">
-        <v>154.0116010192473</v>
+        <v>154.7651208402072</v>
       </c>
       <c r="E6">
-        <v>-96.212</v>
+        <v>-94.065</v>
       </c>
       <c r="F6">
-        <v>8.587999999999999</v>
+        <v>10.735</v>
       </c>
       <c r="G6">
         <v>23.3</v>
@@ -1779,28 +1779,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M6">
-        <v>0.4319763999999999</v>
+        <v>0.5399704999999999</v>
       </c>
       <c r="N6">
-        <v>13.86469026666667</v>
+        <v>13.75669616666667</v>
       </c>
       <c r="O6">
-        <v>3.050231858666667</v>
+        <v>3.026473156666667</v>
       </c>
       <c r="P6">
-        <v>10.814458408</v>
+        <v>10.73022301</v>
       </c>
       <c r="Q6">
-        <v>19.684458408</v>
+        <v>19.60022301</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07211970551725455</v>
+        <v>0.07233772270326469</v>
       </c>
       <c r="T6">
-        <v>0.6078453930081885</v>
+        <v>0.612880431946067</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.09594382162236</v>
+        <v>26.47675505729789</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07068253656810145</v>
+        <v>0.07056079583963855</v>
       </c>
       <c r="C7">
-        <v>167.3301208402072</v>
+        <v>165.9440502818034</v>
       </c>
       <c r="D7">
-        <v>154.7651208402072</v>
+        <v>155.5260502818034</v>
       </c>
       <c r="E7">
-        <v>-94.065</v>
+        <v>-91.91799999999999</v>
       </c>
       <c r="F7">
-        <v>10.735</v>
+        <v>12.882</v>
       </c>
       <c r="G7">
         <v>23.3</v>
@@ -1861,28 +1861,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M7">
-        <v>0.5399704999999999</v>
+        <v>0.6479646</v>
       </c>
       <c r="N7">
-        <v>13.75669616666667</v>
+        <v>13.64870206666667</v>
       </c>
       <c r="O7">
-        <v>3.026473156666667</v>
+        <v>3.002714454666667</v>
       </c>
       <c r="P7">
-        <v>10.73022301</v>
+        <v>10.645987612</v>
       </c>
       <c r="Q7">
-        <v>19.60022301</v>
+        <v>19.515987612</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07233772270326469</v>
+        <v>0.07256037855280696</v>
       </c>
       <c r="T7">
-        <v>0.612880431946067</v>
+        <v>0.6180225993719853</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.47675505729789</v>
+        <v>22.06396254774824</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07056079583963855</v>
+        <v>0.07043905511117562</v>
       </c>
       <c r="C8">
-        <v>165.9440502818034</v>
+        <v>164.5654991760827</v>
       </c>
       <c r="D8">
-        <v>155.5260502818034</v>
+        <v>156.2944991760826</v>
       </c>
       <c r="E8">
-        <v>-91.91799999999999</v>
+        <v>-89.771</v>
       </c>
       <c r="F8">
-        <v>12.882</v>
+        <v>15.029</v>
       </c>
       <c r="G8">
         <v>23.3</v>
@@ -1943,28 +1943,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M8">
-        <v>0.6479646</v>
+        <v>0.7559586999999999</v>
       </c>
       <c r="N8">
-        <v>13.64870206666667</v>
+        <v>13.54070796666667</v>
       </c>
       <c r="O8">
-        <v>3.002714454666667</v>
+        <v>2.978955752666667</v>
       </c>
       <c r="P8">
-        <v>10.645987612</v>
+        <v>10.561752214</v>
       </c>
       <c r="Q8">
-        <v>19.515987612</v>
+        <v>19.431752214</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07256037855280696</v>
+        <v>0.07278782270018885</v>
       </c>
       <c r="T8">
-        <v>0.6180225993719853</v>
+        <v>0.6232753510436224</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.06396254774824</v>
+        <v>18.91196789806992</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07043905511117564</v>
+        <v>0.07031731438271271</v>
       </c>
       <c r="C9">
-        <v>164.5654991760826</v>
+        <v>163.1945795365751</v>
       </c>
       <c r="D9">
-        <v>156.2944991760826</v>
+        <v>157.0705795365751</v>
       </c>
       <c r="E9">
-        <v>-89.771</v>
+        <v>-87.624</v>
       </c>
       <c r="F9">
-        <v>15.029</v>
+        <v>17.176</v>
       </c>
       <c r="G9">
         <v>23.3</v>
@@ -2025,28 +2025,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M9">
-        <v>0.7559587</v>
+        <v>0.8639527999999999</v>
       </c>
       <c r="N9">
-        <v>13.54070796666667</v>
+        <v>13.43271386666667</v>
       </c>
       <c r="O9">
-        <v>2.978955752666667</v>
+        <v>2.955197050666667</v>
       </c>
       <c r="P9">
-        <v>10.561752214</v>
+        <v>10.477516816</v>
       </c>
       <c r="Q9">
-        <v>19.431752214</v>
+        <v>19.347516816</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07278782270018885</v>
+        <v>0.0730202112855573</v>
       </c>
       <c r="T9">
-        <v>0.6232753510436225</v>
+        <v>0.6286422929689908</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.91196789806992</v>
+        <v>16.54797191081118</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07031731438271271</v>
+        <v>0.0701955736542498</v>
       </c>
       <c r="C10">
-        <v>163.1945795365751</v>
+        <v>161.8314056127265</v>
       </c>
       <c r="D10">
-        <v>157.0705795365751</v>
+        <v>157.8544056127265</v>
       </c>
       <c r="E10">
-        <v>-87.624</v>
+        <v>-85.477</v>
       </c>
       <c r="F10">
-        <v>17.176</v>
+        <v>19.323</v>
       </c>
       <c r="G10">
         <v>23.3</v>
@@ -2107,28 +2107,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M10">
-        <v>0.8639527999999999</v>
+        <v>0.9719468999999998</v>
       </c>
       <c r="N10">
-        <v>13.43271386666667</v>
+        <v>13.32471976666667</v>
       </c>
       <c r="O10">
-        <v>2.955197050666667</v>
+        <v>2.931438348666667</v>
       </c>
       <c r="P10">
-        <v>10.477516816</v>
+        <v>10.393281418</v>
       </c>
       <c r="Q10">
-        <v>19.347516816</v>
+        <v>19.263281418</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0730202112855573</v>
+        <v>0.07325770731236242</v>
       </c>
       <c r="T10">
-        <v>0.6286422929689908</v>
+        <v>0.6341271896619497</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.54797191081118</v>
+        <v>14.70930836516549</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0701955736542498</v>
+        <v>0.07007383292578688</v>
       </c>
       <c r="C11">
-        <v>161.8314056127265</v>
+        <v>160.4760939459671</v>
       </c>
       <c r="D11">
-        <v>157.8544056127265</v>
+        <v>158.6460939459671</v>
       </c>
       <c r="E11">
-        <v>-85.477</v>
+        <v>-83.33</v>
       </c>
       <c r="F11">
-        <v>19.323</v>
+        <v>21.47</v>
       </c>
       <c r="G11">
         <v>23.3</v>
@@ -2189,28 +2189,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M11">
-        <v>0.9719468999999998</v>
+        <v>1.079941</v>
       </c>
       <c r="N11">
-        <v>13.32471976666667</v>
+        <v>13.21672566666667</v>
       </c>
       <c r="O11">
-        <v>2.931438348666667</v>
+        <v>2.907679646666667</v>
       </c>
       <c r="P11">
-        <v>10.393281418</v>
+        <v>10.30904602</v>
       </c>
       <c r="Q11">
-        <v>19.263281418</v>
+        <v>19.17904602</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07325770731236242</v>
+        <v>0.07350048102865209</v>
       </c>
       <c r="T11">
-        <v>0.6341271896619497</v>
+        <v>0.6397339729480854</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.70930836516549</v>
+        <v>13.23837752864894</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07007383292578688</v>
+        <v>0.07008079219732397</v>
       </c>
       <c r="C12">
-        <v>160.4760939459671</v>
+        <v>158.2836233848299</v>
       </c>
       <c r="D12">
-        <v>158.6460939459671</v>
+        <v>158.6006233848298</v>
       </c>
       <c r="E12">
-        <v>-83.33</v>
+        <v>-81.18299999999999</v>
       </c>
       <c r="F12">
-        <v>21.47</v>
+        <v>23.617</v>
       </c>
       <c r="G12">
         <v>23.3</v>
@@ -2271,45 +2271,45 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M12">
-        <v>1.079941</v>
+        <v>1.2233606</v>
       </c>
       <c r="N12">
-        <v>13.21672566666667</v>
+        <v>13.07330606666667</v>
       </c>
       <c r="O12">
-        <v>2.907679646666667</v>
+        <v>2.876127334666667</v>
       </c>
       <c r="P12">
-        <v>10.30904602</v>
+        <v>10.197178732</v>
       </c>
       <c r="Q12">
-        <v>19.17904602</v>
+        <v>19.067178732</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07350048102865209</v>
+        <v>0.07374871033407188</v>
       </c>
       <c r="T12">
-        <v>0.6397339729480854</v>
+        <v>0.6454667513642467</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.23837752864894</v>
+        <v>11.68638802546581</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07008079219732397</v>
+        <v>0.06997075146886106</v>
       </c>
       <c r="C13">
-        <v>158.2836233848299</v>
+        <v>156.8586749170059</v>
       </c>
       <c r="D13">
-        <v>158.6006233848298</v>
+        <v>159.3226749170059</v>
       </c>
       <c r="E13">
-        <v>-81.18299999999999</v>
+        <v>-79.036</v>
       </c>
       <c r="F13">
-        <v>23.617</v>
+        <v>25.764</v>
       </c>
       <c r="G13">
         <v>23.3</v>
@@ -2353,28 +2353,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M13">
-        <v>1.2233606</v>
+        <v>1.3345752</v>
       </c>
       <c r="N13">
-        <v>13.07330606666667</v>
+        <v>12.96209146666667</v>
       </c>
       <c r="O13">
-        <v>2.876127334666667</v>
+        <v>2.851660122666667</v>
       </c>
       <c r="P13">
-        <v>10.197178732</v>
+        <v>10.110431344</v>
       </c>
       <c r="Q13">
-        <v>19.067178732</v>
+        <v>18.980431344</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07374871033407188</v>
+        <v>0.07400258121461484</v>
       </c>
       <c r="T13">
-        <v>0.6454667513642467</v>
+        <v>0.651329820198957</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.68638802546581</v>
+        <v>10.71252235667699</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06997075146886106</v>
+        <v>0.06986071074039814</v>
       </c>
       <c r="C14">
-        <v>156.8586749170059</v>
+        <v>155.4403309986025</v>
       </c>
       <c r="D14">
-        <v>159.3226749170059</v>
+        <v>160.0513309986025</v>
       </c>
       <c r="E14">
-        <v>-79.036</v>
+        <v>-76.889</v>
       </c>
       <c r="F14">
-        <v>25.764</v>
+        <v>27.911</v>
       </c>
       <c r="G14">
         <v>23.3</v>
@@ -2435,28 +2435,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M14">
-        <v>1.3345752</v>
+        <v>1.4457898</v>
       </c>
       <c r="N14">
-        <v>12.96209146666667</v>
+        <v>12.85087686666667</v>
       </c>
       <c r="O14">
-        <v>2.851660122666667</v>
+        <v>2.827192910666667</v>
       </c>
       <c r="P14">
-        <v>10.110431344</v>
+        <v>10.023683956</v>
       </c>
       <c r="Q14">
-        <v>18.980431344</v>
+        <v>18.893683956</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07400258121461484</v>
+        <v>0.07426228820735419</v>
       </c>
       <c r="T14">
-        <v>0.651329820198957</v>
+        <v>0.6573276722252699</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.71252235667699</v>
+        <v>9.888482175394149</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06986071074039814</v>
+        <v>0.06993631001193523</v>
       </c>
       <c r="C15">
-        <v>155.4403309986025</v>
+        <v>152.7920213938596</v>
       </c>
       <c r="D15">
-        <v>160.0513309986025</v>
+        <v>159.5500213938596</v>
       </c>
       <c r="E15">
-        <v>-76.889</v>
+        <v>-74.74199999999999</v>
       </c>
       <c r="F15">
-        <v>27.911</v>
+        <v>30.058</v>
       </c>
       <c r="G15">
         <v>23.3</v>
@@ -2517,45 +2517,45 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M15">
-        <v>1.4457898</v>
+        <v>1.608103</v>
       </c>
       <c r="N15">
-        <v>12.85087686666667</v>
+        <v>12.68856366666667</v>
       </c>
       <c r="O15">
-        <v>2.827192910666667</v>
+        <v>2.791484006666667</v>
       </c>
       <c r="P15">
-        <v>10.023683956</v>
+        <v>9.897079660000001</v>
       </c>
       <c r="Q15">
-        <v>18.893683956</v>
+        <v>18.76707966</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07426228820735419</v>
+        <v>0.0745280348975991</v>
       </c>
       <c r="T15">
-        <v>0.6573276722252699</v>
+        <v>0.6634650091824272</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>9.888482175394149</v>
+        <v>8.890392385728195</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06993631001193523</v>
+        <v>0.0698395292834723</v>
       </c>
       <c r="C16">
-        <v>152.7920213938596</v>
+        <v>151.2873537421636</v>
       </c>
       <c r="D16">
-        <v>159.5500213938596</v>
+        <v>160.1923537421636</v>
       </c>
       <c r="E16">
-        <v>-74.74199999999999</v>
+        <v>-72.595</v>
       </c>
       <c r="F16">
-        <v>30.058</v>
+        <v>32.20500000000001</v>
       </c>
       <c r="G16">
         <v>23.3</v>
@@ -2599,28 +2599,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M16">
-        <v>1.608103</v>
+        <v>1.7229675</v>
       </c>
       <c r="N16">
-        <v>12.68856366666667</v>
+        <v>12.57369916666667</v>
       </c>
       <c r="O16">
-        <v>2.791484006666667</v>
+        <v>2.766213816666667</v>
       </c>
       <c r="P16">
-        <v>9.897079660000001</v>
+        <v>9.80748535</v>
       </c>
       <c r="Q16">
-        <v>18.76707966</v>
+        <v>18.67748535</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0745280348975991</v>
+        <v>0.07480003445114389</v>
       </c>
       <c r="T16">
-        <v>0.6634650091824272</v>
+        <v>0.6697467540679883</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.890392385728195</v>
+        <v>8.297699560012981</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0698395292834723</v>
+        <v>0.06974274855500938</v>
       </c>
       <c r="C17">
-        <v>151.2873537421636</v>
+        <v>149.7878789272415</v>
       </c>
       <c r="D17">
-        <v>160.1923537421636</v>
+        <v>160.8398789272414</v>
       </c>
       <c r="E17">
-        <v>-72.595</v>
+        <v>-70.44800000000001</v>
       </c>
       <c r="F17">
-        <v>32.205</v>
+        <v>34.352</v>
       </c>
       <c r="G17">
         <v>23.3</v>
@@ -2681,28 +2681,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M17">
-        <v>1.7229675</v>
+        <v>1.837832</v>
       </c>
       <c r="N17">
-        <v>12.57369916666667</v>
+        <v>12.45883466666667</v>
       </c>
       <c r="O17">
-        <v>2.766213816666667</v>
+        <v>2.740943626666667</v>
       </c>
       <c r="P17">
-        <v>9.807485350000002</v>
+        <v>9.717891040000001</v>
       </c>
       <c r="Q17">
-        <v>18.67748535</v>
+        <v>18.58789104</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07480003445114389</v>
+        <v>0.07507851018453499</v>
       </c>
       <c r="T17">
-        <v>0.6697467540679883</v>
+        <v>0.6761780643079676</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.297699560012983</v>
+        <v>7.779093337512172</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06974274855500938</v>
+        <v>0.06975204782654648</v>
       </c>
       <c r="C18">
-        <v>149.7878789272415</v>
+        <v>147.5784335898336</v>
       </c>
       <c r="D18">
-        <v>160.8398789272414</v>
+        <v>160.7774335898335</v>
       </c>
       <c r="E18">
-        <v>-70.44800000000001</v>
+        <v>-68.30099999999999</v>
       </c>
       <c r="F18">
-        <v>34.352</v>
+        <v>36.499</v>
       </c>
       <c r="G18">
         <v>23.3</v>
@@ -2763,45 +2763,45 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M18">
-        <v>1.837832</v>
+        <v>1.9818957</v>
       </c>
       <c r="N18">
-        <v>12.45883466666667</v>
+        <v>12.31477096666667</v>
       </c>
       <c r="O18">
-        <v>2.740943626666667</v>
+        <v>2.709249612666667</v>
       </c>
       <c r="P18">
-        <v>9.717891040000001</v>
+        <v>9.605521354</v>
       </c>
       <c r="Q18">
-        <v>18.58789104</v>
+        <v>18.475521354</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07507851018453499</v>
+        <v>0.07536369617656202</v>
       </c>
       <c r="T18">
-        <v>0.6761780643079676</v>
+        <v>0.6827643458790307</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.779093337512172</v>
+        <v>7.213632214180931</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06975204782654648</v>
+        <v>0.06966150709808357</v>
       </c>
       <c r="C19">
-        <v>147.5784335898336</v>
+        <v>146.041491701326</v>
       </c>
       <c r="D19">
-        <v>160.7774335898335</v>
+        <v>161.387491701326</v>
       </c>
       <c r="E19">
-        <v>-68.30099999999999</v>
+        <v>-66.154</v>
       </c>
       <c r="F19">
-        <v>36.499</v>
+        <v>38.646</v>
       </c>
       <c r="G19">
         <v>23.3</v>
@@ -2845,28 +2845,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M19">
-        <v>1.9818957</v>
+        <v>2.0984778</v>
       </c>
       <c r="N19">
-        <v>12.31477096666667</v>
+        <v>12.19818886666667</v>
       </c>
       <c r="O19">
-        <v>2.709249612666667</v>
+        <v>2.683601550666667</v>
       </c>
       <c r="P19">
-        <v>9.605521354</v>
+        <v>9.514587316000002</v>
       </c>
       <c r="Q19">
-        <v>18.475521354</v>
+        <v>18.384587316</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07536369617656202</v>
+        <v>0.07565583792449215</v>
       </c>
       <c r="T19">
-        <v>0.6827643458790307</v>
+        <v>0.6895112684640221</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.213632214180931</v>
+        <v>6.812874868948659</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06966150709808358</v>
+        <v>0.06957096636962065</v>
       </c>
       <c r="C20">
-        <v>146.041491701326</v>
+        <v>144.5091970875621</v>
       </c>
       <c r="D20">
-        <v>161.3874917013259</v>
+        <v>162.0021970875621</v>
       </c>
       <c r="E20">
-        <v>-66.154</v>
+        <v>-64.00700000000001</v>
       </c>
       <c r="F20">
-        <v>38.64599999999999</v>
+        <v>40.793</v>
       </c>
       <c r="G20">
         <v>23.3</v>
@@ -2927,28 +2927,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M20">
-        <v>2.0984778</v>
+        <v>2.2150599</v>
       </c>
       <c r="N20">
-        <v>12.19818886666667</v>
+        <v>12.08160676666667</v>
       </c>
       <c r="O20">
-        <v>2.683601550666667</v>
+        <v>2.657953488666667</v>
       </c>
       <c r="P20">
-        <v>9.514587316000002</v>
+        <v>9.423653278000002</v>
       </c>
       <c r="Q20">
-        <v>18.384587316</v>
+        <v>18.293653278</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07565583792449215</v>
+        <v>0.07595519304891438</v>
       </c>
       <c r="T20">
-        <v>0.689511268464022</v>
+        <v>0.6964247817301243</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.81287486894866</v>
+        <v>6.454302507425044</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06957096636962065</v>
+        <v>0.06948042564115772</v>
       </c>
       <c r="C21">
-        <v>144.5091970875621</v>
+        <v>142.9816030542947</v>
       </c>
       <c r="D21">
-        <v>162.0021970875621</v>
+        <v>162.6216030542947</v>
       </c>
       <c r="E21">
-        <v>-64.00700000000001</v>
+        <v>-61.86</v>
       </c>
       <c r="F21">
-        <v>40.793</v>
+        <v>42.94</v>
       </c>
       <c r="G21">
         <v>23.3</v>
@@ -3009,28 +3009,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M21">
-        <v>2.2150599</v>
+        <v>2.331642</v>
       </c>
       <c r="N21">
-        <v>12.08160676666667</v>
+        <v>11.96502466666667</v>
       </c>
       <c r="O21">
-        <v>2.657953488666667</v>
+        <v>2.632305426666667</v>
       </c>
       <c r="P21">
-        <v>9.423653278000002</v>
+        <v>9.332719240000001</v>
       </c>
       <c r="Q21">
-        <v>18.293653278</v>
+        <v>18.20271924</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07595519304891438</v>
+        <v>0.07626203205144716</v>
       </c>
       <c r="T21">
-        <v>0.6964247817301243</v>
+        <v>0.7035111328278792</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.454302507425044</v>
+        <v>6.131587382053792</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06948042564115772</v>
+        <v>0.06955368491269481</v>
       </c>
       <c r="C22">
-        <v>142.9816030542947</v>
+        <v>140.3330581268555</v>
       </c>
       <c r="D22">
-        <v>162.6216030542947</v>
+        <v>162.1200581268555</v>
       </c>
       <c r="E22">
-        <v>-61.86</v>
+        <v>-59.71299999999999</v>
       </c>
       <c r="F22">
-        <v>42.94</v>
+        <v>45.087</v>
       </c>
       <c r="G22">
         <v>23.3</v>
@@ -3091,45 +3091,45 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M22">
-        <v>2.331642</v>
+        <v>2.4933111</v>
       </c>
       <c r="N22">
-        <v>11.96502466666667</v>
+        <v>11.80335556666667</v>
       </c>
       <c r="O22">
-        <v>2.632305426666667</v>
+        <v>2.596738224666667</v>
       </c>
       <c r="P22">
-        <v>9.332719240000001</v>
+        <v>9.206617342000001</v>
       </c>
       <c r="Q22">
-        <v>18.20271924</v>
+        <v>18.076617342</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07626203205144716</v>
+        <v>0.07657663912999343</v>
       </c>
       <c r="T22">
-        <v>0.7035111328278792</v>
+        <v>0.7107768852192482</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.131587382053792</v>
+        <v>5.734008350047721</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06955368491269481</v>
+        <v>0.06947094418423191</v>
       </c>
       <c r="C23">
-        <v>140.3330581268555</v>
+        <v>138.7527415512032</v>
       </c>
       <c r="D23">
-        <v>162.1200581268555</v>
+        <v>162.6867415512032</v>
       </c>
       <c r="E23">
-        <v>-59.713</v>
+        <v>-57.566</v>
       </c>
       <c r="F23">
-        <v>45.087</v>
+        <v>47.23399999999999</v>
       </c>
       <c r="G23">
         <v>23.3</v>
@@ -3173,28 +3173,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M23">
-        <v>2.4933111</v>
+        <v>2.6120402</v>
       </c>
       <c r="N23">
-        <v>11.80335556666667</v>
+        <v>11.68462646666667</v>
       </c>
       <c r="O23">
-        <v>2.596738224666667</v>
+        <v>2.570617822666667</v>
       </c>
       <c r="P23">
-        <v>9.206617342000001</v>
+        <v>9.114008644000002</v>
       </c>
       <c r="Q23">
-        <v>18.076617342</v>
+        <v>17.984008644</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07657663912999343</v>
+        <v>0.07689931305670757</v>
       </c>
       <c r="T23">
-        <v>0.710776885219248</v>
+        <v>0.7182289389539854</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.734008350047722</v>
+        <v>5.473371606863735</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06947094418423191</v>
+        <v>0.06938820345576899</v>
       </c>
       <c r="C24">
-        <v>138.7527415512032</v>
+        <v>137.1764005050505</v>
       </c>
       <c r="D24">
-        <v>162.6867415512032</v>
+        <v>163.2574005050505</v>
       </c>
       <c r="E24">
-        <v>-57.566</v>
+        <v>-55.419</v>
       </c>
       <c r="F24">
-        <v>47.23399999999999</v>
+        <v>49.381</v>
       </c>
       <c r="G24">
         <v>23.3</v>
@@ -3255,28 +3255,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M24">
-        <v>2.6120402</v>
+        <v>2.7307693</v>
       </c>
       <c r="N24">
-        <v>11.68462646666667</v>
+        <v>11.56589736666667</v>
       </c>
       <c r="O24">
-        <v>2.570617822666667</v>
+        <v>2.544497420666667</v>
       </c>
       <c r="P24">
-        <v>9.114008644000002</v>
+        <v>9.021399946000001</v>
       </c>
       <c r="Q24">
-        <v>17.984008644</v>
+        <v>17.891399946</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07689931305670757</v>
+        <v>0.07723036812437531</v>
       </c>
       <c r="T24">
-        <v>0.7182289389539854</v>
+        <v>0.7258745525259888</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.473371606863735</v>
+        <v>5.235398928304441</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06938820345576899</v>
+        <v>0.06930546272730607</v>
       </c>
       <c r="C25">
-        <v>137.1764005050505</v>
+        <v>135.6040769707496</v>
       </c>
       <c r="D25">
-        <v>163.2574005050505</v>
+        <v>163.8320769707496</v>
       </c>
       <c r="E25">
-        <v>-55.419</v>
+        <v>-53.272</v>
       </c>
       <c r="F25">
-        <v>49.381</v>
+        <v>51.528</v>
       </c>
       <c r="G25">
         <v>23.3</v>
@@ -3337,28 +3337,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M25">
-        <v>2.7307693</v>
+        <v>2.8494984</v>
       </c>
       <c r="N25">
-        <v>11.56589736666667</v>
+        <v>11.44716826666667</v>
       </c>
       <c r="O25">
-        <v>2.544497420666667</v>
+        <v>2.518377018666667</v>
       </c>
       <c r="P25">
-        <v>9.021399946000001</v>
+        <v>8.928791248000001</v>
       </c>
       <c r="Q25">
-        <v>17.891399946</v>
+        <v>17.798791248</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07723036812437531</v>
+        <v>0.07757013516750799</v>
       </c>
       <c r="T25">
-        <v>0.7258745525259888</v>
+        <v>0.73372136645515</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.235398928304441</v>
+        <v>5.017257306291756</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06930546272730607</v>
+        <v>0.06922272199884316</v>
       </c>
       <c r="C26">
-        <v>135.6040769707496</v>
+        <v>134.0358135238633</v>
       </c>
       <c r="D26">
-        <v>163.8320769707496</v>
+        <v>164.4108135238633</v>
       </c>
       <c r="E26">
-        <v>-53.272</v>
+        <v>-51.125</v>
       </c>
       <c r="F26">
-        <v>51.528</v>
+        <v>53.675</v>
       </c>
       <c r="G26">
         <v>23.3</v>
@@ -3419,28 +3419,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M26">
-        <v>2.8494984</v>
+        <v>2.9682275</v>
       </c>
       <c r="N26">
-        <v>11.44716826666667</v>
+        <v>11.32843916666667</v>
       </c>
       <c r="O26">
-        <v>2.518377018666667</v>
+        <v>2.492256616666667</v>
       </c>
       <c r="P26">
-        <v>8.928791248000001</v>
+        <v>8.836182550000002</v>
       </c>
       <c r="Q26">
-        <v>17.798791248</v>
+        <v>17.70618255</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07757013516750799</v>
+        <v>0.07791896266512421</v>
       </c>
       <c r="T26">
-        <v>0.73372136645515</v>
+        <v>0.7417774287557555</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.017257306291756</v>
+        <v>4.816567014040086</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06922272199884316</v>
+        <v>0.06913998127038024</v>
       </c>
       <c r="C27">
-        <v>134.0358135238633</v>
+        <v>132.4716533436797</v>
       </c>
       <c r="D27">
-        <v>164.4108135238633</v>
+        <v>164.9936533436797</v>
       </c>
       <c r="E27">
-        <v>-51.125</v>
+        <v>-48.978</v>
       </c>
       <c r="F27">
-        <v>53.675</v>
+        <v>55.822</v>
       </c>
       <c r="G27">
         <v>23.3</v>
@@ -3501,28 +3501,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M27">
-        <v>2.9682275</v>
+        <v>3.0869566</v>
       </c>
       <c r="N27">
-        <v>11.32843916666667</v>
+        <v>11.20971006666667</v>
       </c>
       <c r="O27">
-        <v>2.492256616666667</v>
+        <v>2.466136214666667</v>
       </c>
       <c r="P27">
-        <v>8.836182550000002</v>
+        <v>8.743573852000003</v>
       </c>
       <c r="Q27">
-        <v>17.70618255</v>
+        <v>17.613573852</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07791896266512421</v>
+        <v>0.07827721793294626</v>
       </c>
       <c r="T27">
-        <v>0.7417774287557555</v>
+        <v>0.7500512224698909</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.816567014040086</v>
+        <v>4.631314436577006</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06913998127038024</v>
+        <v>0.06958374054191732</v>
       </c>
       <c r="C28">
-        <v>132.4716533436797</v>
+        <v>127.2461862166527</v>
       </c>
       <c r="D28">
-        <v>164.9936533436797</v>
+        <v>161.9151862166526</v>
       </c>
       <c r="E28">
-        <v>-48.978</v>
+        <v>-46.831</v>
       </c>
       <c r="F28">
-        <v>55.822</v>
+        <v>57.969</v>
       </c>
       <c r="G28">
         <v>23.3</v>
@@ -3583,45 +3583,45 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M28">
-        <v>3.0869566</v>
+        <v>3.3506082</v>
       </c>
       <c r="N28">
-        <v>11.20971006666667</v>
+        <v>10.94605846666667</v>
       </c>
       <c r="O28">
-        <v>2.466136214666667</v>
+        <v>2.408132862666667</v>
       </c>
       <c r="P28">
-        <v>8.743573852000003</v>
+        <v>8.537925604000002</v>
       </c>
       <c r="Q28">
-        <v>17.613573852</v>
+        <v>17.407925604</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07827721793294626</v>
+        <v>0.07864528841358537</v>
       </c>
       <c r="T28">
-        <v>0.7500512224698909</v>
+        <v>0.7585516954638656</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.22</v>
       </c>
       <c r="W28">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.631314436577006</v>
+        <v>4.266887028649506</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06958374054191732</v>
+        <v>0.0695204998134544</v>
       </c>
       <c r="C29">
-        <v>127.2461862166527</v>
+        <v>125.5308649083361</v>
       </c>
       <c r="D29">
-        <v>161.9151862166526</v>
+        <v>162.3468649083361</v>
       </c>
       <c r="E29">
-        <v>-46.831</v>
+        <v>-44.684</v>
       </c>
       <c r="F29">
-        <v>57.969</v>
+        <v>60.116</v>
       </c>
       <c r="G29">
         <v>23.3</v>
@@ -3665,28 +3665,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M29">
-        <v>3.3506082</v>
+        <v>3.4747048</v>
       </c>
       <c r="N29">
-        <v>10.94605846666667</v>
+        <v>10.82196186666667</v>
       </c>
       <c r="O29">
-        <v>2.408132862666667</v>
+        <v>2.380831610666667</v>
       </c>
       <c r="P29">
-        <v>8.537925604000002</v>
+        <v>8.441130256000001</v>
       </c>
       <c r="Q29">
-        <v>17.407925604</v>
+        <v>17.311130256</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07864528841358537</v>
+        <v>0.07902358307424223</v>
       </c>
       <c r="T29">
-        <v>0.7585516954638656</v>
+        <v>0.7672882927076731</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.266887028649506</v>
+        <v>4.114498206197737</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0695204998134544</v>
+        <v>0.0702489590849915</v>
       </c>
       <c r="C30">
-        <v>125.5308649083361</v>
+        <v>118.5467232314107</v>
       </c>
       <c r="D30">
-        <v>162.3468649083361</v>
+        <v>157.5097232314106</v>
       </c>
       <c r="E30">
-        <v>-44.684</v>
+        <v>-42.53699999999999</v>
       </c>
       <c r="F30">
-        <v>60.116</v>
+        <v>62.26300000000001</v>
       </c>
       <c r="G30">
         <v>23.3</v>
@@ -3747,45 +3747,45 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M30">
-        <v>3.4747048</v>
+        <v>3.816721900000001</v>
       </c>
       <c r="N30">
-        <v>10.82196186666667</v>
+        <v>10.47994476666667</v>
       </c>
       <c r="O30">
-        <v>2.380831610666667</v>
+        <v>2.305587848666667</v>
       </c>
       <c r="P30">
-        <v>8.441130256000001</v>
+        <v>8.174356918000001</v>
       </c>
       <c r="Q30">
-        <v>17.311130256</v>
+        <v>17.044356918</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07902358307424223</v>
+        <v>0.07941253392252323</v>
       </c>
       <c r="T30">
-        <v>0.7672882927076731</v>
+        <v>0.7762709912822918</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.22</v>
       </c>
       <c r="W30">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.114498206197737</v>
+        <v>3.745797320644888</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07024895908499149</v>
+        <v>0.07021301835652857</v>
       </c>
       <c r="C31">
-        <v>118.5467232314108</v>
+        <v>116.6316082900403</v>
       </c>
       <c r="D31">
-        <v>157.5097232314107</v>
+        <v>157.7416082900403</v>
       </c>
       <c r="E31">
-        <v>-42.53700000000001</v>
+        <v>-40.39</v>
       </c>
       <c r="F31">
-        <v>62.26299999999999</v>
+        <v>64.41</v>
       </c>
       <c r="G31">
         <v>23.3</v>
@@ -3829,28 +3829,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M31">
-        <v>3.8167219</v>
+        <v>3.948333</v>
       </c>
       <c r="N31">
-        <v>10.47994476666667</v>
+        <v>10.34833366666667</v>
       </c>
       <c r="O31">
-        <v>2.305587848666667</v>
+        <v>2.276633406666667</v>
       </c>
       <c r="P31">
-        <v>8.174356918000003</v>
+        <v>8.071700260000002</v>
       </c>
       <c r="Q31">
-        <v>17.044356918</v>
+        <v>16.94170026</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07941253392252323</v>
+        <v>0.07981259765218368</v>
       </c>
       <c r="T31">
-        <v>0.7762709912822918</v>
+        <v>0.7855103383876141</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.745797320644889</v>
+        <v>3.620937409956726</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07021301835652857</v>
+        <v>0.07017707762806566</v>
       </c>
       <c r="C32">
-        <v>116.6316082900403</v>
+        <v>114.717177115449</v>
       </c>
       <c r="D32">
-        <v>157.7416082900403</v>
+        <v>157.974177115449</v>
       </c>
       <c r="E32">
-        <v>-40.39</v>
+        <v>-38.24299999999999</v>
       </c>
       <c r="F32">
-        <v>64.41</v>
+        <v>66.557</v>
       </c>
       <c r="G32">
         <v>23.3</v>
@@ -3911,28 +3911,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M32">
-        <v>3.948333</v>
+        <v>4.079944100000001</v>
       </c>
       <c r="N32">
-        <v>10.34833366666667</v>
+        <v>10.21672256666667</v>
       </c>
       <c r="O32">
-        <v>2.276633406666667</v>
+        <v>2.247678964666667</v>
       </c>
       <c r="P32">
-        <v>8.071700260000002</v>
+        <v>7.969043602000001</v>
       </c>
       <c r="Q32">
-        <v>16.94170026</v>
+        <v>16.839043602</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07981259765218368</v>
+        <v>0.08022425743197922</v>
       </c>
       <c r="T32">
-        <v>0.7855103383876141</v>
+        <v>0.7950174926554094</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.620937409956726</v>
+        <v>3.504132977377476</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07017707762806566</v>
+        <v>0.07084001689960275</v>
       </c>
       <c r="C33">
-        <v>114.717177115449</v>
+        <v>108.3877803415775</v>
       </c>
       <c r="D33">
-        <v>157.974177115449</v>
+        <v>153.7917803415775</v>
       </c>
       <c r="E33">
-        <v>-38.24299999999999</v>
+        <v>-36.096</v>
       </c>
       <c r="F33">
-        <v>66.557</v>
+        <v>68.70399999999999</v>
       </c>
       <c r="G33">
         <v>23.3</v>
@@ -3993,45 +3993,45 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M33">
-        <v>4.079944100000001</v>
+        <v>4.4039264</v>
       </c>
       <c r="N33">
-        <v>10.21672256666667</v>
+        <v>9.892740266666669</v>
       </c>
       <c r="O33">
-        <v>2.247678964666667</v>
+        <v>2.176402858666667</v>
       </c>
       <c r="P33">
-        <v>7.969043602000001</v>
+        <v>7.716337408000002</v>
       </c>
       <c r="Q33">
-        <v>16.839043602</v>
+        <v>16.586337408</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08022425743197922</v>
+        <v>0.08064802485235698</v>
       </c>
       <c r="T33">
-        <v>0.7950174926554094</v>
+        <v>0.8048042691075518</v>
       </c>
       <c r="U33">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.504132977377476</v>
+        <v>3.246345503563972</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07084001689960275</v>
+        <v>0.07082591617113983</v>
       </c>
       <c r="C34">
-        <v>108.3877803415775</v>
+        <v>106.3274335581709</v>
       </c>
       <c r="D34">
-        <v>153.7917803415775</v>
+        <v>153.8784335581709</v>
       </c>
       <c r="E34">
-        <v>-36.096</v>
+        <v>-33.949</v>
       </c>
       <c r="F34">
-        <v>68.70399999999999</v>
+        <v>70.851</v>
       </c>
       <c r="G34">
         <v>23.3</v>
@@ -4075,28 +4075,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M34">
-        <v>4.4039264</v>
+        <v>4.5415491</v>
       </c>
       <c r="N34">
-        <v>9.892740266666669</v>
+        <v>9.755117566666669</v>
       </c>
       <c r="O34">
-        <v>2.176402858666667</v>
+        <v>2.146125864666667</v>
       </c>
       <c r="P34">
-        <v>7.716337408000002</v>
+        <v>7.608991702000003</v>
       </c>
       <c r="Q34">
-        <v>16.586337408</v>
+        <v>16.478991702</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08064802485235698</v>
+        <v>0.08108444204647736</v>
       </c>
       <c r="T34">
-        <v>0.8048042691075518</v>
+        <v>0.8148831881403549</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.246345503563972</v>
+        <v>3.147971397395366</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07082591617113983</v>
+        <v>0.07081181544267691</v>
       </c>
       <c r="C35">
-        <v>106.3274335581709</v>
+        <v>104.2671844784659</v>
       </c>
       <c r="D35">
-        <v>153.8784335581709</v>
+        <v>153.9651844784659</v>
       </c>
       <c r="E35">
-        <v>-33.949</v>
+        <v>-31.80199999999999</v>
       </c>
       <c r="F35">
-        <v>70.851</v>
+        <v>72.998</v>
       </c>
       <c r="G35">
         <v>23.3</v>
@@ -4157,28 +4157,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M35">
-        <v>4.5415491</v>
+        <v>4.679171800000001</v>
       </c>
       <c r="N35">
-        <v>9.755117566666669</v>
+        <v>9.617494866666668</v>
       </c>
       <c r="O35">
-        <v>2.146125864666667</v>
+        <v>2.115848870666667</v>
       </c>
       <c r="P35">
-        <v>7.608991702000003</v>
+        <v>7.501645996000001</v>
       </c>
       <c r="Q35">
-        <v>16.478991702</v>
+        <v>16.371645996</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08108444204647736</v>
+        <v>0.08153408400405593</v>
       </c>
       <c r="T35">
-        <v>0.8148831881403549</v>
+        <v>0.8252675289620309</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.147971397395366</v>
+        <v>3.055384003354326</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07081181544267691</v>
+        <v>0.07292711471421401</v>
       </c>
       <c r="C36">
-        <v>104.2671844784659</v>
+        <v>90.11439447829599</v>
       </c>
       <c r="D36">
-        <v>153.9651844784659</v>
+        <v>141.959394478296</v>
       </c>
       <c r="E36">
-        <v>-31.80199999999999</v>
+        <v>-29.65499999999999</v>
       </c>
       <c r="F36">
-        <v>72.998</v>
+        <v>75.14500000000001</v>
       </c>
       <c r="G36">
         <v>23.3</v>
@@ -4239,45 +4239,45 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M36">
-        <v>4.679171800000001</v>
+        <v>5.402925500000001</v>
       </c>
       <c r="N36">
-        <v>9.617494866666668</v>
+        <v>8.893741166666668</v>
       </c>
       <c r="O36">
-        <v>2.115848870666667</v>
+        <v>1.956623056666667</v>
       </c>
       <c r="P36">
-        <v>7.501645996000001</v>
+        <v>6.937118110000001</v>
       </c>
       <c r="Q36">
-        <v>16.371645996</v>
+        <v>15.80711811</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08153408400405593</v>
+        <v>0.08199756109879078</v>
       </c>
       <c r="T36">
-        <v>0.8252675289620309</v>
+        <v>0.8359713879628355</v>
       </c>
       <c r="U36">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V36">
         <v>0.22</v>
       </c>
       <c r="W36">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.055384003354326</v>
+        <v>2.646097316475429</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07292711471421401</v>
+        <v>0.07297385398575108</v>
       </c>
       <c r="C37">
-        <v>90.11439447829599</v>
+        <v>87.72322305199631</v>
       </c>
       <c r="D37">
-        <v>141.959394478296</v>
+        <v>141.7152230519963</v>
       </c>
       <c r="E37">
-        <v>-29.65499999999999</v>
+        <v>-27.508</v>
       </c>
       <c r="F37">
-        <v>75.14500000000001</v>
+        <v>77.292</v>
       </c>
       <c r="G37">
         <v>23.3</v>
@@ -4321,28 +4321,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M37">
-        <v>5.402925500000001</v>
+        <v>5.5572948</v>
       </c>
       <c r="N37">
-        <v>8.893741166666668</v>
+        <v>8.739371866666669</v>
       </c>
       <c r="O37">
-        <v>1.956623056666667</v>
+        <v>1.922661810666667</v>
       </c>
       <c r="P37">
-        <v>6.937118110000001</v>
+        <v>6.816710056000002</v>
       </c>
       <c r="Q37">
-        <v>15.80711811</v>
+        <v>15.686710056</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08199756109879078</v>
+        <v>0.08247552185273607</v>
       </c>
       <c r="T37">
-        <v>0.8359713879628355</v>
+        <v>0.8470097425574153</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.646097316475429</v>
+        <v>2.572594613240001</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0729738539857511</v>
+        <v>0.07302059325728817</v>
       </c>
       <c r="C38">
-        <v>87.72322305199627</v>
+        <v>85.3328901375165</v>
       </c>
       <c r="D38">
-        <v>141.7152230519962</v>
+        <v>141.4718901375165</v>
       </c>
       <c r="E38">
-        <v>-27.50800000000001</v>
+        <v>-25.361</v>
       </c>
       <c r="F38">
-        <v>77.29199999999999</v>
+        <v>79.43899999999999</v>
       </c>
       <c r="G38">
         <v>23.3</v>
@@ -4403,28 +4403,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M38">
-        <v>5.557294799999999</v>
+        <v>5.7116641</v>
       </c>
       <c r="N38">
-        <v>8.739371866666669</v>
+        <v>8.585002566666668</v>
       </c>
       <c r="O38">
-        <v>1.922661810666667</v>
+        <v>1.888700564666667</v>
       </c>
       <c r="P38">
-        <v>6.816710056000002</v>
+        <v>6.696302002000001</v>
       </c>
       <c r="Q38">
-        <v>15.686710056</v>
+        <v>15.566302002</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08247552185273607</v>
+        <v>0.08296865596394948</v>
       </c>
       <c r="T38">
-        <v>0.8470097425574151</v>
+        <v>0.8583985211073784</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.572594613240001</v>
+        <v>2.503065029098379</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07302059325728817</v>
+        <v>0.07422329252882526</v>
       </c>
       <c r="C39">
-        <v>85.3328901375165</v>
+        <v>77.19966813178611</v>
       </c>
       <c r="D39">
-        <v>141.4718901375165</v>
+        <v>135.4856681317861</v>
       </c>
       <c r="E39">
-        <v>-25.361</v>
+        <v>-23.214</v>
       </c>
       <c r="F39">
-        <v>79.43899999999999</v>
+        <v>81.586</v>
       </c>
       <c r="G39">
         <v>23.3</v>
@@ -4485,45 +4485,45 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M39">
-        <v>5.7116641</v>
+        <v>6.1842188</v>
       </c>
       <c r="N39">
-        <v>8.585002566666668</v>
+        <v>8.112447866666669</v>
       </c>
       <c r="O39">
-        <v>1.888700564666667</v>
+        <v>1.784738530666667</v>
       </c>
       <c r="P39">
-        <v>6.696302002000001</v>
+        <v>6.327709336000002</v>
       </c>
       <c r="Q39">
-        <v>15.566302002</v>
+        <v>15.197709336</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08296865596394948</v>
+        <v>0.0834776976271375</v>
       </c>
       <c r="T39">
-        <v>0.8583985211073784</v>
+        <v>0.8701546796105661</v>
       </c>
       <c r="U39">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V39">
         <v>0.22</v>
       </c>
       <c r="W39">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.503065029098379</v>
+        <v>2.31179832554868</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07422329252882526</v>
+        <v>0.07430045180036234</v>
       </c>
       <c r="C40">
-        <v>77.19966813178611</v>
+        <v>74.6858677901638</v>
       </c>
       <c r="D40">
-        <v>135.4856681317861</v>
+        <v>135.1188677901638</v>
       </c>
       <c r="E40">
-        <v>-23.214</v>
+        <v>-21.06699999999999</v>
       </c>
       <c r="F40">
-        <v>81.586</v>
+        <v>83.733</v>
       </c>
       <c r="G40">
         <v>23.3</v>
@@ -4567,28 +4567,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M40">
-        <v>6.1842188</v>
+        <v>6.346961400000001</v>
       </c>
       <c r="N40">
-        <v>8.112447866666669</v>
+        <v>7.949705266666668</v>
       </c>
       <c r="O40">
-        <v>1.784738530666667</v>
+        <v>1.748935158666667</v>
       </c>
       <c r="P40">
-        <v>6.327709336000002</v>
+        <v>6.200770108000001</v>
       </c>
       <c r="Q40">
-        <v>15.197709336</v>
+        <v>15.070770108</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.0834776976271375</v>
+        <v>0.08400342918092187</v>
       </c>
       <c r="T40">
-        <v>0.8701546796105661</v>
+        <v>0.8822962859335306</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.31179832554868</v>
+        <v>2.252521445406406</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07430045180036234</v>
+        <v>0.07437761107189944</v>
       </c>
       <c r="C41">
-        <v>74.6858677901638</v>
+        <v>72.17404816324057</v>
       </c>
       <c r="D41">
-        <v>135.1188677901638</v>
+        <v>134.7540481632406</v>
       </c>
       <c r="E41">
-        <v>-21.06699999999999</v>
+        <v>-18.92</v>
       </c>
       <c r="F41">
-        <v>83.733</v>
+        <v>85.88</v>
       </c>
       <c r="G41">
         <v>23.3</v>
@@ -4649,28 +4649,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M41">
-        <v>6.346961400000001</v>
+        <v>6.509704</v>
       </c>
       <c r="N41">
-        <v>7.949705266666668</v>
+        <v>7.786962666666668</v>
       </c>
       <c r="O41">
-        <v>1.748935158666667</v>
+        <v>1.713131786666667</v>
       </c>
       <c r="P41">
-        <v>6.200770108000001</v>
+        <v>6.073830880000001</v>
       </c>
       <c r="Q41">
-        <v>15.070770108</v>
+        <v>14.94383088</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08400342918092187</v>
+        <v>0.08454668511983238</v>
       </c>
       <c r="T41">
-        <v>0.8822962859335306</v>
+        <v>0.8948426124672605</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.252521445406406</v>
+        <v>2.196208409271246</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07437761107189944</v>
+        <v>0.0744547703434365</v>
       </c>
       <c r="C42">
-        <v>72.17404816324057</v>
+        <v>69.66419325048683</v>
       </c>
       <c r="D42">
-        <v>134.7540481632406</v>
+        <v>134.3911932504868</v>
       </c>
       <c r="E42">
-        <v>-18.92</v>
+        <v>-16.773</v>
       </c>
       <c r="F42">
-        <v>85.88</v>
+        <v>88.027</v>
       </c>
       <c r="G42">
         <v>23.3</v>
@@ -4731,28 +4731,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M42">
-        <v>6.509704</v>
+        <v>6.672446600000001</v>
       </c>
       <c r="N42">
-        <v>7.786962666666668</v>
+        <v>7.624220066666668</v>
       </c>
       <c r="O42">
-        <v>1.713131786666667</v>
+        <v>1.677328414666667</v>
       </c>
       <c r="P42">
-        <v>6.073830880000001</v>
+        <v>5.946891652000001</v>
       </c>
       <c r="Q42">
-        <v>14.94383088</v>
+        <v>14.816891652</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08454668511983238</v>
+        <v>0.08510835651429917</v>
       </c>
       <c r="T42">
-        <v>0.8948426124672605</v>
+        <v>0.9078142382055236</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.196208409271246</v>
+        <v>2.142642350508533</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0744547703434365</v>
+        <v>0.0745319296149736</v>
       </c>
       <c r="C43">
-        <v>69.66419325048683</v>
+        <v>67.15628722324931</v>
       </c>
       <c r="D43">
-        <v>134.3911932504868</v>
+        <v>134.0302872232493</v>
       </c>
       <c r="E43">
-        <v>-16.773</v>
+        <v>-14.62599999999999</v>
       </c>
       <c r="F43">
-        <v>88.027</v>
+        <v>90.17400000000001</v>
       </c>
       <c r="G43">
         <v>23.3</v>
@@ -4813,28 +4813,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M43">
-        <v>6.672446600000001</v>
+        <v>6.835189200000001</v>
       </c>
       <c r="N43">
-        <v>7.624220066666668</v>
+        <v>7.461477466666667</v>
       </c>
       <c r="O43">
-        <v>1.677328414666667</v>
+        <v>1.641525042666667</v>
       </c>
       <c r="P43">
-        <v>5.946891652000001</v>
+        <v>5.819952424</v>
       </c>
       <c r="Q43">
-        <v>14.816891652</v>
+        <v>14.689952424</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08510835651429917</v>
+        <v>0.0856893958878855</v>
       </c>
       <c r="T43">
-        <v>0.9078142382055236</v>
+        <v>0.9212331613830372</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.142642350508533</v>
+        <v>2.091627056448806</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0745319296149736</v>
+        <v>0.07460908888651069</v>
       </c>
       <c r="C44">
-        <v>67.15628722324932</v>
+        <v>64.65031442245049</v>
       </c>
       <c r="D44">
-        <v>134.0302872232493</v>
+        <v>133.6713144224505</v>
       </c>
       <c r="E44">
-        <v>-14.626</v>
+        <v>-12.479</v>
       </c>
       <c r="F44">
-        <v>90.17399999999999</v>
+        <v>92.321</v>
       </c>
       <c r="G44">
         <v>23.3</v>
@@ -4895,28 +4895,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M44">
-        <v>6.8351892</v>
+        <v>6.997931800000001</v>
       </c>
       <c r="N44">
-        <v>7.461477466666668</v>
+        <v>7.298734866666668</v>
       </c>
       <c r="O44">
-        <v>1.641525042666667</v>
+        <v>1.605721670666667</v>
       </c>
       <c r="P44">
-        <v>5.819952424000001</v>
+        <v>5.693013196000001</v>
       </c>
       <c r="Q44">
-        <v>14.689952424</v>
+        <v>14.563013196</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0856893958878855</v>
+        <v>0.08629082260791347</v>
       </c>
       <c r="T44">
-        <v>0.9212331613830372</v>
+        <v>0.9351229239702882</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.091627056448806</v>
+        <v>2.04298456676395</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07460908888651069</v>
+        <v>0.07955968815804776</v>
       </c>
       <c r="C45">
-        <v>64.65031442245049</v>
+        <v>42.90144165907799</v>
       </c>
       <c r="D45">
-        <v>133.6713144224505</v>
+        <v>114.069441659078</v>
       </c>
       <c r="E45">
-        <v>-12.479</v>
+        <v>-10.33200000000001</v>
       </c>
       <c r="F45">
-        <v>92.321</v>
+        <v>94.46799999999999</v>
       </c>
       <c r="G45">
         <v>23.3</v>
@@ -4977,45 +4977,45 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M45">
-        <v>6.997931800000001</v>
+        <v>8.502119999999998</v>
       </c>
       <c r="N45">
-        <v>7.298734866666668</v>
+        <v>5.794546666666671</v>
       </c>
       <c r="O45">
-        <v>1.605721670666667</v>
+        <v>1.274800266666668</v>
       </c>
       <c r="P45">
-        <v>5.693013196000001</v>
+        <v>4.519746400000003</v>
       </c>
       <c r="Q45">
-        <v>14.563013196</v>
+        <v>13.3897464</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08629082260791347</v>
+        <v>0.08691372885365672</v>
       </c>
       <c r="T45">
-        <v>0.9351229239702882</v>
+        <v>0.9495087495070839</v>
       </c>
       <c r="U45">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V45">
         <v>0.22</v>
       </c>
       <c r="W45">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.04298456676395</v>
+        <v>1.681541388108692</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07955968815804776</v>
+        <v>0.07974760742958487</v>
       </c>
       <c r="C46">
-        <v>42.90144165907799</v>
+        <v>40.12300256795258</v>
       </c>
       <c r="D46">
-        <v>114.069441659078</v>
+        <v>113.4380025679526</v>
       </c>
       <c r="E46">
-        <v>-10.33200000000001</v>
+        <v>-8.185000000000002</v>
       </c>
       <c r="F46">
-        <v>94.46799999999999</v>
+        <v>96.61499999999999</v>
       </c>
       <c r="G46">
         <v>23.3</v>
@@ -5059,28 +5059,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M46">
-        <v>8.502119999999998</v>
+        <v>8.695349999999999</v>
       </c>
       <c r="N46">
-        <v>5.794546666666671</v>
+        <v>5.601316666666669</v>
       </c>
       <c r="O46">
-        <v>1.274800266666668</v>
+        <v>1.232289666666667</v>
       </c>
       <c r="P46">
-        <v>4.519746400000003</v>
+        <v>4.369027000000002</v>
       </c>
       <c r="Q46">
-        <v>13.3897464</v>
+        <v>13.239027</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08691372885365672</v>
+        <v>0.08755928623560882</v>
       </c>
       <c r="T46">
-        <v>0.9495087495070839</v>
+        <v>0.9644176959724902</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.681541388108692</v>
+        <v>1.644173801706276</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07974760742958487</v>
+        <v>0.07993552670112195</v>
       </c>
       <c r="C47">
-        <v>40.12300256795258</v>
+        <v>37.35151573949855</v>
       </c>
       <c r="D47">
-        <v>113.4380025679526</v>
+        <v>112.8135157394986</v>
       </c>
       <c r="E47">
-        <v>-8.185000000000002</v>
+        <v>-6.037999999999997</v>
       </c>
       <c r="F47">
-        <v>96.61499999999999</v>
+        <v>98.762</v>
       </c>
       <c r="G47">
         <v>23.3</v>
@@ -5141,28 +5141,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M47">
-        <v>8.695349999999999</v>
+        <v>8.888579999999999</v>
       </c>
       <c r="N47">
-        <v>5.601316666666669</v>
+        <v>5.408086666666669</v>
       </c>
       <c r="O47">
-        <v>1.232289666666667</v>
+        <v>1.189779066666667</v>
       </c>
       <c r="P47">
-        <v>4.369027000000002</v>
+        <v>4.218307600000002</v>
       </c>
       <c r="Q47">
-        <v>13.239027</v>
+        <v>13.0883076</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08755928623560882</v>
+        <v>0.0882287531502258</v>
       </c>
       <c r="T47">
-        <v>0.9644176959724902</v>
+        <v>0.9798788256403189</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.644173801706276</v>
+        <v>1.608430892973531</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07993552670112195</v>
+        <v>0.08012344597265902</v>
       </c>
       <c r="C48">
-        <v>37.35151573949855</v>
+        <v>34.58686698377078</v>
       </c>
       <c r="D48">
-        <v>112.8135157394986</v>
+        <v>112.1958669837708</v>
       </c>
       <c r="E48">
-        <v>-6.037999999999997</v>
+        <v>-3.890999999999991</v>
       </c>
       <c r="F48">
-        <v>98.762</v>
+        <v>100.909</v>
       </c>
       <c r="G48">
         <v>23.3</v>
@@ -5223,28 +5223,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M48">
-        <v>8.888579999999999</v>
+        <v>9.081810000000001</v>
       </c>
       <c r="N48">
-        <v>5.408086666666669</v>
+        <v>5.214856666666668</v>
       </c>
       <c r="O48">
-        <v>1.189779066666667</v>
+        <v>1.147268466666667</v>
       </c>
       <c r="P48">
-        <v>4.218307600000002</v>
+        <v>4.067588200000001</v>
       </c>
       <c r="Q48">
-        <v>13.0883076</v>
+        <v>12.9375882</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0882287531502258</v>
+        <v>0.08892348296728117</v>
       </c>
       <c r="T48">
-        <v>0.9798788256403189</v>
+        <v>0.9959233941635375</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.608430892973531</v>
+        <v>1.574208959080477</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08012344597265902</v>
+        <v>0.0803113652441961</v>
       </c>
       <c r="C49">
-        <v>34.58686698377078</v>
+        <v>31.82894459794581</v>
       </c>
       <c r="D49">
-        <v>112.1958669837708</v>
+        <v>111.5849445979458</v>
       </c>
       <c r="E49">
-        <v>-3.890999999999991</v>
+        <v>-1.744</v>
       </c>
       <c r="F49">
-        <v>100.909</v>
+        <v>103.056</v>
       </c>
       <c r="G49">
         <v>23.3</v>
@@ -5305,28 +5305,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M49">
-        <v>9.081810000000001</v>
+        <v>9.275039999999999</v>
       </c>
       <c r="N49">
-        <v>5.214856666666668</v>
+        <v>5.02162666666667</v>
       </c>
       <c r="O49">
-        <v>1.147268466666667</v>
+        <v>1.104757866666667</v>
       </c>
       <c r="P49">
-        <v>4.067588200000001</v>
+        <v>3.916868800000002</v>
       </c>
       <c r="Q49">
-        <v>12.9375882</v>
+        <v>12.7868688</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08892348296728117</v>
+        <v>0.08964493316191559</v>
       </c>
       <c r="T49">
-        <v>0.9959233941635375</v>
+        <v>1.012585061476111</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.574208959080477</v>
+        <v>1.541412939099634</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0803113652441961</v>
+        <v>0.08049928451573318</v>
       </c>
       <c r="C50">
-        <v>31.82894459794581</v>
+        <v>29.07763929897506</v>
       </c>
       <c r="D50">
-        <v>111.5849445979458</v>
+        <v>110.980639298975</v>
       </c>
       <c r="E50">
-        <v>-1.744</v>
+        <v>0.4029999999999916</v>
       </c>
       <c r="F50">
-        <v>103.056</v>
+        <v>105.203</v>
       </c>
       <c r="G50">
         <v>23.3</v>
@@ -5387,28 +5387,28 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M50">
-        <v>9.275039999999999</v>
+        <v>9.468269999999999</v>
       </c>
       <c r="N50">
-        <v>5.02162666666667</v>
+        <v>4.82839666666667</v>
       </c>
       <c r="O50">
-        <v>1.104757866666667</v>
+        <v>1.062247266666667</v>
       </c>
       <c r="P50">
-        <v>3.916868800000002</v>
+        <v>3.766149400000002</v>
       </c>
       <c r="Q50">
-        <v>12.7868688</v>
+        <v>12.6361494</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08964493316191557</v>
+        <v>0.09039467552104546</v>
       </c>
       <c r="T50">
-        <v>1.01258506147611</v>
+        <v>1.029900127506824</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.541412939099634</v>
+        <v>1.509955532179233</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08049928451573318</v>
+        <v>0.1045978084403243</v>
       </c>
       <c r="C51">
-        <v>29.07763929897506</v>
+        <v>-18.55523274721129</v>
       </c>
       <c r="D51">
-        <v>110.980639298975</v>
+        <v>65.49476725278871</v>
       </c>
       <c r="E51">
-        <v>0.4029999999999916</v>
+        <v>2.549999999999997</v>
       </c>
       <c r="F51">
-        <v>105.203</v>
+        <v>107.35</v>
       </c>
       <c r="G51">
         <v>23.3</v>
@@ -5469,45 +5469,45 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M51">
-        <v>9.468269999999999</v>
+        <v>15.75898</v>
       </c>
       <c r="N51">
-        <v>4.82839666666667</v>
+        <v>-1.462313333333332</v>
       </c>
       <c r="O51">
-        <v>1.062247266666667</v>
+        <v>-0.3217089333333332</v>
       </c>
       <c r="P51">
-        <v>3.766149400000002</v>
+        <v>-1.140604399999999</v>
       </c>
       <c r="Q51">
-        <v>12.6361494</v>
+        <v>7.7293956</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09039467552104546</v>
+        <v>0.09169479402705438</v>
       </c>
       <c r="T51">
-        <v>1.029900127506824</v>
+        <v>1.059925959054374</v>
       </c>
       <c r="U51">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.22</v>
+        <v>0.199585675384236</v>
       </c>
       <c r="W51">
-        <v>0.0702</v>
+        <v>0.1175008228535942</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.509955532179233</v>
+        <v>0.9072076153828907</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1045978084403243</v>
+        <v>0.1056078084403243</v>
       </c>
       <c r="C52">
-        <v>-18.55523274721129</v>
+        <v>-21.80827084909761</v>
       </c>
       <c r="D52">
-        <v>65.49476725278871</v>
+        <v>64.38872915090239</v>
       </c>
       <c r="E52">
-        <v>2.549999999999997</v>
+        <v>4.697000000000003</v>
       </c>
       <c r="F52">
-        <v>107.35</v>
+        <v>109.497</v>
       </c>
       <c r="G52">
         <v>23.3</v>
@@ -5551,37 +5551,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M52">
-        <v>15.75898</v>
+        <v>16.0741596</v>
       </c>
       <c r="N52">
-        <v>-1.462313333333332</v>
+        <v>-1.777492933333333</v>
       </c>
       <c r="O52">
-        <v>-0.3217089333333332</v>
+        <v>-0.3910484453333332</v>
       </c>
       <c r="P52">
-        <v>-1.140604399999999</v>
+        <v>-1.386444488</v>
       </c>
       <c r="Q52">
-        <v>7.7293956</v>
+        <v>7.483555512</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09169479402705438</v>
+        <v>0.09263142247658612</v>
       </c>
       <c r="T52">
-        <v>1.059925959054374</v>
+        <v>1.081557101075892</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.199585675384236</v>
+        <v>0.1956722307688588</v>
       </c>
       <c r="W52">
-        <v>0.1175008228535942</v>
+        <v>0.1180753165231316</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.9072076153828907</v>
+        <v>0.8894192307675399</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1056078084403243</v>
+        <v>0.1066178084403243</v>
       </c>
       <c r="C53">
-        <v>-21.80827084909761</v>
+        <v>-25.02457305038004</v>
       </c>
       <c r="D53">
-        <v>64.38872915090239</v>
+        <v>63.31942694961995</v>
       </c>
       <c r="E53">
-        <v>4.697000000000003</v>
+        <v>6.843999999999994</v>
       </c>
       <c r="F53">
-        <v>109.497</v>
+        <v>111.644</v>
       </c>
       <c r="G53">
         <v>23.3</v>
@@ -5633,37 +5633,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M53">
-        <v>16.0741596</v>
+        <v>16.3893392</v>
       </c>
       <c r="N53">
-        <v>-1.777492933333333</v>
+        <v>-2.092672533333333</v>
       </c>
       <c r="O53">
-        <v>-0.3910484453333332</v>
+        <v>-0.4603879573333333</v>
       </c>
       <c r="P53">
-        <v>-1.386444488</v>
+        <v>-1.632284576</v>
       </c>
       <c r="Q53">
-        <v>7.483555512</v>
+        <v>7.237715423999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09263142247658612</v>
+        <v>0.093607077111515</v>
       </c>
       <c r="T53">
-        <v>1.081557101075892</v>
+        <v>1.10408954068164</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1956722307688588</v>
+        <v>0.191909303254073</v>
       </c>
       <c r="W53">
-        <v>0.1180753165231316</v>
+        <v>0.1186277142823021</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8894192307675399</v>
+        <v>0.8723150147912411</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1066178084403243</v>
+        <v>0.1076278084403243</v>
       </c>
       <c r="C54">
-        <v>-25.02457305038004</v>
+        <v>-28.20593967006774</v>
       </c>
       <c r="D54">
-        <v>63.31942694961995</v>
+        <v>62.28506032993226</v>
       </c>
       <c r="E54">
-        <v>6.843999999999994</v>
+        <v>8.991</v>
       </c>
       <c r="F54">
-        <v>111.644</v>
+        <v>113.791</v>
       </c>
       <c r="G54">
         <v>23.3</v>
@@ -5715,37 +5715,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M54">
-        <v>16.3893392</v>
+        <v>16.7045188</v>
       </c>
       <c r="N54">
-        <v>-2.092672533333333</v>
+        <v>-2.407852133333334</v>
       </c>
       <c r="O54">
-        <v>-0.4603879573333333</v>
+        <v>-0.5297274693333335</v>
       </c>
       <c r="P54">
-        <v>-1.632284576</v>
+        <v>-1.878124664</v>
       </c>
       <c r="Q54">
-        <v>7.237715423999999</v>
+        <v>6.991875335999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.093607077111515</v>
+        <v>0.0946242489649515</v>
       </c>
       <c r="T54">
-        <v>1.10408954068164</v>
+        <v>1.127580807504654</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.191909303254073</v>
+        <v>0.1882883730039962</v>
       </c>
       <c r="W54">
-        <v>0.1186277142823021</v>
+        <v>0.1191592668430134</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8723150147912411</v>
+        <v>0.8558562409272553</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1076278084403243</v>
+        <v>0.1086378084403243</v>
       </c>
       <c r="C55">
-        <v>-28.20593967006774</v>
+        <v>-31.3540552801542</v>
       </c>
       <c r="D55">
-        <v>62.28506032993226</v>
+        <v>61.2839447198458</v>
       </c>
       <c r="E55">
-        <v>8.991</v>
+        <v>11.13800000000001</v>
       </c>
       <c r="F55">
-        <v>113.791</v>
+        <v>115.938</v>
       </c>
       <c r="G55">
         <v>23.3</v>
@@ -5797,37 +5797,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M55">
-        <v>16.7045188</v>
+        <v>17.0196984</v>
       </c>
       <c r="N55">
-        <v>-2.407852133333334</v>
+        <v>-2.723031733333334</v>
       </c>
       <c r="O55">
-        <v>-0.5297274693333335</v>
+        <v>-0.5990669813333336</v>
       </c>
       <c r="P55">
-        <v>-1.878124664</v>
+        <v>-2.123964752000001</v>
       </c>
       <c r="Q55">
-        <v>6.991875335999999</v>
+        <v>6.746035247999998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.0946242489649515</v>
+        <v>0.09568564568158086</v>
       </c>
       <c r="T55">
-        <v>1.127580807504654</v>
+        <v>1.152093433754755</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1882883730039962</v>
+        <v>0.1848015512816999</v>
       </c>
       <c r="W55">
-        <v>0.1191592668430134</v>
+        <v>0.1196711322718465</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8558562409272553</v>
+        <v>0.8400070512804543</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1086378084403243</v>
+        <v>0.1096478084403243</v>
       </c>
       <c r="C56">
-        <v>-31.3540552801542</v>
+        <v>-34.47049786055064</v>
       </c>
       <c r="D56">
-        <v>61.2839447198458</v>
+        <v>60.31450213944937</v>
       </c>
       <c r="E56">
-        <v>11.13800000000001</v>
+        <v>13.28500000000001</v>
       </c>
       <c r="F56">
-        <v>115.938</v>
+        <v>118.085</v>
       </c>
       <c r="G56">
         <v>23.3</v>
@@ -5879,37 +5879,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M56">
-        <v>17.0196984</v>
+        <v>17.334878</v>
       </c>
       <c r="N56">
-        <v>-2.723031733333334</v>
+        <v>-3.038211333333335</v>
       </c>
       <c r="O56">
-        <v>-0.5990669813333336</v>
+        <v>-0.6684064933333337</v>
       </c>
       <c r="P56">
-        <v>-2.123964752000001</v>
+        <v>-2.369804840000001</v>
       </c>
       <c r="Q56">
-        <v>6.746035247999998</v>
+        <v>6.500195159999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09568564568158086</v>
+        <v>0.09679421558561599</v>
       </c>
       <c r="T56">
-        <v>1.152093433754755</v>
+        <v>1.177695510060416</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1848015512816999</v>
+        <v>0.1814415230765781</v>
       </c>
       <c r="W56">
-        <v>0.1196711322718465</v>
+        <v>0.1201643844123583</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8400070512804543</v>
+        <v>0.8247341958026279</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1096478084403243</v>
+        <v>0.1106578084403243</v>
       </c>
       <c r="C57">
-        <v>-34.47049786055064</v>
+        <v>-37.55674709862645</v>
       </c>
       <c r="D57">
-        <v>60.31450213944937</v>
+        <v>59.37525290137355</v>
       </c>
       <c r="E57">
-        <v>13.28500000000001</v>
+        <v>15.432</v>
       </c>
       <c r="F57">
-        <v>118.085</v>
+        <v>120.232</v>
       </c>
       <c r="G57">
         <v>23.3</v>
@@ -5961,37 +5961,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M57">
-        <v>17.334878</v>
+        <v>17.6500576</v>
       </c>
       <c r="N57">
-        <v>-3.038211333333335</v>
+        <v>-3.353390933333332</v>
       </c>
       <c r="O57">
-        <v>-0.6684064933333337</v>
+        <v>-0.737746005333333</v>
       </c>
       <c r="P57">
-        <v>-2.369804840000001</v>
+        <v>-2.615644927999999</v>
       </c>
       <c r="Q57">
-        <v>6.500195159999999</v>
+        <v>6.254355072000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09679421558561599</v>
+        <v>0.09795317503074363</v>
       </c>
       <c r="T57">
-        <v>1.177695510060416</v>
+        <v>1.204461317107243</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1814415230765781</v>
+        <v>0.1782014958787821</v>
       </c>
       <c r="W57">
-        <v>0.1201643844123583</v>
+        <v>0.1206400204049948</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8247341958026279</v>
+        <v>0.8100067994490097</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1106578084403243</v>
+        <v>0.1431319096984518</v>
       </c>
       <c r="C58">
-        <v>-37.55674709862645</v>
+        <v>-59.51387905760932</v>
       </c>
       <c r="D58">
-        <v>59.37525290137355</v>
+        <v>39.56512094239068</v>
       </c>
       <c r="E58">
-        <v>15.432</v>
+        <v>17.57900000000001</v>
       </c>
       <c r="F58">
-        <v>120.232</v>
+        <v>122.379</v>
       </c>
       <c r="G58">
         <v>23.3</v>
@@ -6043,45 +6043,45 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M58">
-        <v>17.6500576</v>
+        <v>24.5737032</v>
       </c>
       <c r="N58">
-        <v>-3.353390933333332</v>
+        <v>-10.27703653333333</v>
       </c>
       <c r="O58">
-        <v>-0.737746005333333</v>
+        <v>-2.260948037333333</v>
       </c>
       <c r="P58">
-        <v>-2.615644927999999</v>
+        <v>-8.016088495999998</v>
       </c>
       <c r="Q58">
-        <v>6.254355072000001</v>
+        <v>0.8539115040000009</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09795317503074363</v>
+        <v>0.1007569727247783</v>
       </c>
       <c r="T58">
-        <v>1.204461317107243</v>
+        <v>1.269214150687721</v>
       </c>
       <c r="U58">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1782014958787821</v>
+        <v>0.1279931901621839</v>
       </c>
       <c r="W58">
-        <v>0.1206400204049948</v>
+        <v>0.1750989674154335</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.8100067994490097</v>
+        <v>0.5817872280099268</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1431319096984518</v>
+        <v>0.1446819096984518</v>
       </c>
       <c r="C59">
-        <v>-59.51387905760932</v>
+        <v>-62.28107275782936</v>
       </c>
       <c r="D59">
-        <v>39.56512094239068</v>
+        <v>38.94492724217065</v>
       </c>
       <c r="E59">
-        <v>17.57900000000001</v>
+        <v>19.72600000000001</v>
       </c>
       <c r="F59">
-        <v>122.379</v>
+        <v>124.526</v>
       </c>
       <c r="G59">
         <v>23.3</v>
@@ -6125,37 +6125,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M59">
-        <v>24.5737032</v>
+        <v>25.0048208</v>
       </c>
       <c r="N59">
-        <v>-10.27703653333333</v>
+        <v>-10.70815413333334</v>
       </c>
       <c r="O59">
-        <v>-2.260948037333333</v>
+        <v>-2.355793909333334</v>
       </c>
       <c r="P59">
-        <v>-8.016088495999998</v>
+        <v>-8.352360224000002</v>
       </c>
       <c r="Q59">
-        <v>0.8539115040000009</v>
+        <v>0.5176397759999976</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1007569727247783</v>
+        <v>0.1020654720753683</v>
       </c>
       <c r="T59">
-        <v>1.269214150687721</v>
+        <v>1.299433535227905</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1279931901621839</v>
+        <v>0.1257864110214566</v>
       </c>
       <c r="W59">
-        <v>0.1750989674154335</v>
+        <v>0.1755420886668915</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5817872280099268</v>
+        <v>0.5717564137338935</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1446819096984517</v>
+        <v>0.1462319096984517</v>
       </c>
       <c r="C60">
-        <v>-62.28107275782931</v>
+        <v>-65.02912313521048</v>
       </c>
       <c r="D60">
-        <v>38.94492724217067</v>
+        <v>38.34387686478951</v>
       </c>
       <c r="E60">
-        <v>19.72599999999998</v>
+        <v>21.87299999999999</v>
       </c>
       <c r="F60">
-        <v>124.526</v>
+        <v>126.673</v>
       </c>
       <c r="G60">
         <v>23.3</v>
@@ -6207,37 +6207,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M60">
-        <v>25.0048208</v>
+        <v>25.4359384</v>
       </c>
       <c r="N60">
-        <v>-10.70815413333333</v>
+        <v>-11.13927173333333</v>
       </c>
       <c r="O60">
-        <v>-2.355793909333332</v>
+        <v>-2.450639781333332</v>
       </c>
       <c r="P60">
-        <v>-8.352360223999996</v>
+        <v>-8.688631951999996</v>
       </c>
       <c r="Q60">
-        <v>0.5176397760000029</v>
+        <v>0.1813680480000031</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1020654720753683</v>
+        <v>0.1034378006625724</v>
       </c>
       <c r="T60">
-        <v>1.299433535227905</v>
+        <v>1.331127036087122</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1257864110214566</v>
+        <v>0.1236544379532963</v>
       </c>
       <c r="W60">
-        <v>0.1755420886668915</v>
+        <v>0.1759701888589781</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5717564137338937</v>
+        <v>0.5620656270604378</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1462319096984517</v>
+        <v>0.1477819096984518</v>
       </c>
       <c r="C61">
-        <v>-65.02912313521048</v>
+        <v>-67.75890305486644</v>
       </c>
       <c r="D61">
-        <v>38.34387686478951</v>
+        <v>37.76109694513356</v>
       </c>
       <c r="E61">
-        <v>21.87299999999999</v>
+        <v>24.02</v>
       </c>
       <c r="F61">
-        <v>126.673</v>
+        <v>128.82</v>
       </c>
       <c r="G61">
         <v>23.3</v>
@@ -6289,37 +6289,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M61">
-        <v>25.4359384</v>
+        <v>25.867056</v>
       </c>
       <c r="N61">
-        <v>-11.13927173333333</v>
+        <v>-11.57038933333333</v>
       </c>
       <c r="O61">
-        <v>-2.450639781333332</v>
+        <v>-2.545485653333333</v>
       </c>
       <c r="P61">
-        <v>-8.688631951999996</v>
+        <v>-9.024903679999998</v>
       </c>
       <c r="Q61">
-        <v>0.1813680480000031</v>
+        <v>-0.1549036799999985</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1034378006625724</v>
+        <v>0.1048787456791367</v>
       </c>
       <c r="T61">
-        <v>1.331127036087122</v>
+        <v>1.3644052119893</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1236544379532963</v>
+        <v>0.1215935306540747</v>
       </c>
       <c r="W61">
-        <v>0.1759701888589781</v>
+        <v>0.1763840190446618</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5620656270604378</v>
+        <v>0.5526978666094305</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1477819096984518</v>
+        <v>0.1493319096984518</v>
       </c>
       <c r="C62">
-        <v>-67.75890305486644</v>
+        <v>-70.47123311045442</v>
       </c>
       <c r="D62">
-        <v>37.76109694513356</v>
+        <v>37.19576688954556</v>
       </c>
       <c r="E62">
-        <v>24.02</v>
+        <v>26.16699999999999</v>
       </c>
       <c r="F62">
-        <v>128.82</v>
+        <v>130.967</v>
       </c>
       <c r="G62">
         <v>23.3</v>
@@ -6371,37 +6371,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M62">
-        <v>25.867056</v>
+        <v>26.2981736</v>
       </c>
       <c r="N62">
-        <v>-11.57038933333333</v>
+        <v>-12.00150693333333</v>
       </c>
       <c r="O62">
-        <v>-2.545485653333333</v>
+        <v>-2.640331525333333</v>
       </c>
       <c r="P62">
-        <v>-9.024903679999998</v>
+        <v>-9.361175407999998</v>
       </c>
       <c r="Q62">
-        <v>-0.1549036799999985</v>
+        <v>-0.4911754079999984</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1048787456791367</v>
+        <v>0.1063935853119351</v>
       </c>
       <c r="T62">
-        <v>1.3644052119893</v>
+        <v>1.399389961014667</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1215935306540747</v>
+        <v>0.1196001940859751</v>
       </c>
       <c r="W62">
-        <v>0.1763840190446618</v>
+        <v>0.1767842810275362</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5526978666094305</v>
+        <v>0.5436372458453416</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1493319096984518</v>
+        <v>0.1508819096984518</v>
       </c>
       <c r="C63">
-        <v>-70.47123311045442</v>
+        <v>-73.16688547929931</v>
       </c>
       <c r="D63">
-        <v>37.19576688954556</v>
+        <v>36.6471145207007</v>
       </c>
       <c r="E63">
-        <v>26.16699999999999</v>
+        <v>28.31400000000001</v>
       </c>
       <c r="F63">
-        <v>130.967</v>
+        <v>133.114</v>
       </c>
       <c r="G63">
         <v>23.3</v>
@@ -6453,37 +6453,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M63">
-        <v>26.2981736</v>
+        <v>26.7292912</v>
       </c>
       <c r="N63">
-        <v>-12.00150693333333</v>
+        <v>-12.43262453333333</v>
       </c>
       <c r="O63">
-        <v>-2.640331525333333</v>
+        <v>-2.735177397333334</v>
       </c>
       <c r="P63">
-        <v>-9.361175407999998</v>
+        <v>-9.697447136000001</v>
       </c>
       <c r="Q63">
-        <v>-0.4911754079999984</v>
+        <v>-0.8274471360000017</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1063935853119351</v>
+        <v>0.1079881533464597</v>
       </c>
       <c r="T63">
-        <v>1.399389961014667</v>
+        <v>1.436216012620316</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1196001940859751</v>
+        <v>0.1176711586974916</v>
       </c>
       <c r="W63">
-        <v>0.1767842810275362</v>
+        <v>0.1771716313335437</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5436372458453416</v>
+        <v>0.5348689031704166</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1508819096984518</v>
+        <v>0.1524319096984517</v>
       </c>
       <c r="C64">
-        <v>-73.16688547929931</v>
+        <v>-75.8465874412891</v>
       </c>
       <c r="D64">
-        <v>36.6471145207007</v>
+        <v>36.1144125587109</v>
       </c>
       <c r="E64">
-        <v>28.31400000000001</v>
+        <v>30.461</v>
       </c>
       <c r="F64">
-        <v>133.114</v>
+        <v>135.261</v>
       </c>
       <c r="G64">
         <v>23.3</v>
@@ -6535,37 +6535,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M64">
-        <v>26.7292912</v>
+        <v>27.1604088</v>
       </c>
       <c r="N64">
-        <v>-12.43262453333333</v>
+        <v>-12.86374213333333</v>
       </c>
       <c r="O64">
-        <v>-2.735177397333334</v>
+        <v>-2.830023269333333</v>
       </c>
       <c r="P64">
-        <v>-9.697447136000001</v>
+        <v>-10.033718864</v>
       </c>
       <c r="Q64">
-        <v>-0.8274471360000017</v>
+        <v>-1.163718863999998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1079881533464597</v>
+        <v>0.1096689142477153</v>
       </c>
       <c r="T64">
-        <v>1.436216012620316</v>
+        <v>1.475032661610054</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1176711586974916</v>
+        <v>0.1158033625276902</v>
       </c>
       <c r="W64">
-        <v>0.1771716313335437</v>
+        <v>0.1775466848044398</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5348689031704166</v>
+        <v>0.52637892058041</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1524319096984517</v>
+        <v>0.1539819096984518</v>
       </c>
       <c r="C65">
-        <v>-75.8465874412891</v>
+        <v>-78.51102459526459</v>
       </c>
       <c r="D65">
-        <v>36.1144125587109</v>
+        <v>35.5969754047354</v>
       </c>
       <c r="E65">
-        <v>30.461</v>
+        <v>32.60799999999999</v>
       </c>
       <c r="F65">
-        <v>135.261</v>
+        <v>137.408</v>
       </c>
       <c r="G65">
         <v>23.3</v>
@@ -6617,37 +6617,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M65">
-        <v>27.1604088</v>
+        <v>27.5915264</v>
       </c>
       <c r="N65">
-        <v>-12.86374213333333</v>
+        <v>-13.29485973333333</v>
       </c>
       <c r="O65">
-        <v>-2.830023269333333</v>
+        <v>-2.924869141333333</v>
       </c>
       <c r="P65">
-        <v>-10.033718864</v>
+        <v>-10.369990592</v>
       </c>
       <c r="Q65">
-        <v>-1.163718863999998</v>
+        <v>-1.499990591999998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1096689142477153</v>
+        <v>0.1114430507545963</v>
       </c>
       <c r="T65">
-        <v>1.475032661610054</v>
+        <v>1.516005791099222</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1158033625276902</v>
+        <v>0.113993934988195</v>
       </c>
       <c r="W65">
-        <v>0.1775466848044398</v>
+        <v>0.1779100178543704</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.52637892058041</v>
+        <v>0.5181542499463411</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1539819096984518</v>
+        <v>0.1555319096984518</v>
       </c>
       <c r="C66">
-        <v>-78.51102459526459</v>
+        <v>-81.16084380281293</v>
       </c>
       <c r="D66">
-        <v>35.5969754047354</v>
+        <v>35.09415619718707</v>
       </c>
       <c r="E66">
-        <v>32.60799999999999</v>
+        <v>34.75500000000001</v>
       </c>
       <c r="F66">
-        <v>137.408</v>
+        <v>139.555</v>
       </c>
       <c r="G66">
         <v>23.3</v>
@@ -6699,37 +6699,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M66">
-        <v>27.5915264</v>
+        <v>28.022644</v>
       </c>
       <c r="N66">
-        <v>-13.29485973333333</v>
+        <v>-13.72597733333333</v>
       </c>
       <c r="O66">
-        <v>-2.924869141333333</v>
+        <v>-3.019715013333334</v>
       </c>
       <c r="P66">
-        <v>-10.369990592</v>
+        <v>-10.70626232</v>
       </c>
       <c r="Q66">
-        <v>-1.499990591999998</v>
+        <v>-1.836262320000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1114430507545963</v>
+        <v>0.1133185664904419</v>
       </c>
       <c r="T66">
-        <v>1.516005791099222</v>
+        <v>1.559320242273486</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.113993934988195</v>
+        <v>0.1122401821422228</v>
       </c>
       <c r="W66">
-        <v>0.1779100178543704</v>
+        <v>0.1782621714258417</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5181542499463411</v>
+        <v>0.5101826461010127</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1555319096984518</v>
+        <v>0.1570819096984517</v>
       </c>
       <c r="C67">
-        <v>-81.16084380281293</v>
+        <v>-83.79665588604406</v>
       </c>
       <c r="D67">
-        <v>35.09415619718707</v>
+        <v>34.60534411395594</v>
       </c>
       <c r="E67">
-        <v>34.75500000000001</v>
+        <v>36.902</v>
       </c>
       <c r="F67">
-        <v>139.555</v>
+        <v>141.702</v>
       </c>
       <c r="G67">
         <v>23.3</v>
@@ -6781,37 +6781,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M67">
-        <v>28.022644</v>
+        <v>28.4537616</v>
       </c>
       <c r="N67">
-        <v>-13.72597733333333</v>
+        <v>-14.15709493333333</v>
       </c>
       <c r="O67">
-        <v>-3.019715013333334</v>
+        <v>-3.114560885333333</v>
       </c>
       <c r="P67">
-        <v>-10.70626232</v>
+        <v>-11.042534048</v>
       </c>
       <c r="Q67">
-        <v>-1.836262320000001</v>
+        <v>-2.172534047999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1133185664904419</v>
+        <v>0.1153044066813373</v>
       </c>
       <c r="T67">
-        <v>1.559320242273486</v>
+        <v>1.605182602340353</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1122401821422228</v>
+        <v>0.1105395733218861</v>
       </c>
       <c r="W67">
-        <v>0.1782621714258417</v>
+        <v>0.1786036536769653</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5101826461010127</v>
+        <v>0.5024526060085732</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1570819096984517</v>
+        <v>0.182357952819133</v>
       </c>
       <c r="C68">
-        <v>-83.79665588604406</v>
+        <v>-92.34889375006549</v>
       </c>
       <c r="D68">
-        <v>34.60534411395594</v>
+        <v>28.2001062499345</v>
       </c>
       <c r="E68">
-        <v>36.902</v>
+        <v>39.04899999999999</v>
       </c>
       <c r="F68">
-        <v>141.702</v>
+        <v>143.849</v>
       </c>
       <c r="G68">
         <v>23.3</v>
@@ -6863,45 +6863,45 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M68">
-        <v>28.4537616</v>
+        <v>33.9195942</v>
       </c>
       <c r="N68">
-        <v>-14.15709493333333</v>
+        <v>-19.62292753333333</v>
       </c>
       <c r="O68">
-        <v>-3.114560885333333</v>
+        <v>-4.317044057333333</v>
       </c>
       <c r="P68">
-        <v>-11.042534048</v>
+        <v>-15.305883476</v>
       </c>
       <c r="Q68">
-        <v>-2.172534047999999</v>
+        <v>-6.435883475999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1153044066813373</v>
+        <v>0.1182470951282908</v>
       </c>
       <c r="T68">
-        <v>1.605182602340353</v>
+        <v>1.67314307455637</v>
       </c>
       <c r="U68">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1105395733218861</v>
+        <v>0.09272713134836581</v>
       </c>
       <c r="W68">
-        <v>0.1786036536769653</v>
+        <v>0.2139349424280553</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.5024526060085732</v>
+        <v>0.42148696067439</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.182357952819133</v>
+        <v>0.1842579528191331</v>
       </c>
       <c r="C69">
-        <v>-92.34889375006549</v>
+        <v>-94.88287189602201</v>
       </c>
       <c r="D69">
-        <v>28.2001062499345</v>
+        <v>27.81312810397801</v>
       </c>
       <c r="E69">
-        <v>39.04899999999999</v>
+        <v>41.19600000000001</v>
       </c>
       <c r="F69">
-        <v>143.849</v>
+        <v>145.996</v>
       </c>
       <c r="G69">
         <v>23.3</v>
@@ -6945,37 +6945,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M69">
-        <v>33.9195942</v>
+        <v>34.42585680000001</v>
       </c>
       <c r="N69">
-        <v>-19.62292753333333</v>
+        <v>-20.12919013333334</v>
       </c>
       <c r="O69">
-        <v>-4.317044057333333</v>
+        <v>-4.428421829333335</v>
       </c>
       <c r="P69">
-        <v>-15.305883476</v>
+        <v>-15.700768304</v>
       </c>
       <c r="Q69">
-        <v>-6.435883475999999</v>
+        <v>-6.830768304000005</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1182470951282908</v>
+        <v>0.1205110668510499</v>
       </c>
       <c r="T69">
-        <v>1.67314307455637</v>
+        <v>1.725428795636256</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09272713134836581</v>
+        <v>0.091363497063831</v>
       </c>
       <c r="W69">
-        <v>0.2139349424280553</v>
+        <v>0.2142564873923487</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.42148696067439</v>
+        <v>0.4152886230174136</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1842579528191331</v>
+        <v>0.1861579528191331</v>
       </c>
       <c r="C70">
-        <v>-94.88287189602201</v>
+        <v>-97.40637313685764</v>
       </c>
       <c r="D70">
-        <v>27.81312810397801</v>
+        <v>27.43662686314235</v>
       </c>
       <c r="E70">
-        <v>41.19600000000001</v>
+        <v>43.343</v>
       </c>
       <c r="F70">
-        <v>145.996</v>
+        <v>148.143</v>
       </c>
       <c r="G70">
         <v>23.3</v>
@@ -7027,37 +7027,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M70">
-        <v>34.42585680000001</v>
+        <v>34.9321194</v>
       </c>
       <c r="N70">
-        <v>-20.12919013333334</v>
+        <v>-20.63545273333334</v>
       </c>
       <c r="O70">
-        <v>-4.428421829333335</v>
+        <v>-4.539799601333335</v>
       </c>
       <c r="P70">
-        <v>-15.700768304</v>
+        <v>-16.095653132</v>
       </c>
       <c r="Q70">
-        <v>-6.830768304000005</v>
+        <v>-7.225653132000003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1205110668510499</v>
+        <v>0.1229211012655999</v>
       </c>
       <c r="T70">
-        <v>1.725428795636256</v>
+        <v>1.781087789043878</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.091363497063831</v>
+        <v>0.090039388410732</v>
       </c>
       <c r="W70">
-        <v>0.2142564873923487</v>
+        <v>0.2145687122127494</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4152886230174136</v>
+        <v>0.4092699473215091</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1861579528191331</v>
+        <v>0.1880579528191331</v>
       </c>
       <c r="C71">
-        <v>-97.40637313685764</v>
+        <v>-99.91981726182162</v>
       </c>
       <c r="D71">
-        <v>27.43662686314235</v>
+        <v>27.0701827381784</v>
       </c>
       <c r="E71">
-        <v>43.343</v>
+        <v>45.49000000000002</v>
       </c>
       <c r="F71">
-        <v>148.143</v>
+        <v>150.29</v>
       </c>
       <c r="G71">
         <v>23.3</v>
@@ -7109,37 +7109,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M71">
-        <v>34.9321194</v>
+        <v>35.438382</v>
       </c>
       <c r="N71">
-        <v>-20.63545273333334</v>
+        <v>-21.14171533333334</v>
       </c>
       <c r="O71">
-        <v>-4.539799601333335</v>
+        <v>-4.651177373333335</v>
       </c>
       <c r="P71">
-        <v>-16.095653132</v>
+        <v>-16.49053796</v>
       </c>
       <c r="Q71">
-        <v>-7.225653132000003</v>
+        <v>-7.620537960000005</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1229211012655999</v>
+        <v>0.1254918046411199</v>
       </c>
       <c r="T71">
-        <v>1.781087789043878</v>
+        <v>1.840457382012007</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.090039388410732</v>
+        <v>0.08875311143343584</v>
       </c>
       <c r="W71">
-        <v>0.2145687122127494</v>
+        <v>0.2148720163239958</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4092699473215091</v>
+        <v>0.4034232337883447</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1880579528191331</v>
+        <v>0.1899579528191331</v>
       </c>
       <c r="C72">
-        <v>-99.91981726182162</v>
+        <v>-102.4236019288949</v>
       </c>
       <c r="D72">
-        <v>27.0701827381784</v>
+        <v>26.71339807110513</v>
       </c>
       <c r="E72">
-        <v>45.49000000000002</v>
+        <v>47.63700000000001</v>
       </c>
       <c r="F72">
-        <v>150.29</v>
+        <v>152.437</v>
       </c>
       <c r="G72">
         <v>23.3</v>
@@ -7191,37 +7191,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M72">
-        <v>35.438382</v>
+        <v>35.9446446</v>
       </c>
       <c r="N72">
-        <v>-21.14171533333334</v>
+        <v>-21.64797793333334</v>
       </c>
       <c r="O72">
-        <v>-4.651177373333335</v>
+        <v>-4.762555145333335</v>
       </c>
       <c r="P72">
-        <v>-16.49053796</v>
+        <v>-16.885422788</v>
       </c>
       <c r="Q72">
-        <v>-7.620537960000005</v>
+        <v>-8.015422788000004</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1254918046411199</v>
+        <v>0.1282397979046068</v>
       </c>
       <c r="T72">
-        <v>1.840457382012007</v>
+        <v>1.903921429667593</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08875311143343584</v>
+        <v>0.0875030676104297</v>
       </c>
       <c r="W72">
-        <v>0.2148720163239958</v>
+        <v>0.2151667766574607</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4034232337883447</v>
+        <v>0.397741216411044</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.189957952819133</v>
+        <v>0.191857952819133</v>
       </c>
       <c r="C73">
-        <v>-102.4236019288949</v>
+        <v>-104.9181041042673</v>
       </c>
       <c r="D73">
-        <v>26.71339807110513</v>
+        <v>26.36589589573266</v>
       </c>
       <c r="E73">
-        <v>47.63699999999999</v>
+        <v>49.78399999999998</v>
       </c>
       <c r="F73">
-        <v>152.437</v>
+        <v>154.584</v>
       </c>
       <c r="G73">
         <v>23.3</v>
@@ -7273,37 +7273,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M73">
-        <v>35.9446446</v>
+        <v>36.4509072</v>
       </c>
       <c r="N73">
-        <v>-21.64797793333333</v>
+        <v>-22.15424053333333</v>
       </c>
       <c r="O73">
-        <v>-4.762555145333333</v>
+        <v>-4.873932917333333</v>
       </c>
       <c r="P73">
-        <v>-16.885422788</v>
+        <v>-17.28030761599999</v>
       </c>
       <c r="Q73">
-        <v>-8.015422787999997</v>
+        <v>-8.410307615999995</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1282397979046067</v>
+        <v>0.1311840764011999</v>
       </c>
       <c r="T73">
-        <v>1.903921429667593</v>
+        <v>1.971918623584293</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08750306761042971</v>
+        <v>0.08628774722695152</v>
       </c>
       <c r="W73">
-        <v>0.2151667766574607</v>
+        <v>0.2154533492038848</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3977412164110441</v>
+        <v>0.3922170328497796</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.191857952819133</v>
+        <v>0.1937579528191331</v>
       </c>
       <c r="C74">
-        <v>-104.9181041042673</v>
+        <v>-107.4036813909045</v>
       </c>
       <c r="D74">
-        <v>26.36589589573266</v>
+        <v>26.02731860909548</v>
       </c>
       <c r="E74">
-        <v>49.78399999999998</v>
+        <v>51.931</v>
       </c>
       <c r="F74">
-        <v>154.584</v>
+        <v>156.731</v>
       </c>
       <c r="G74">
         <v>23.3</v>
@@ -7355,37 +7355,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M74">
-        <v>36.4509072</v>
+        <v>36.9571698</v>
       </c>
       <c r="N74">
-        <v>-22.15424053333333</v>
+        <v>-22.66050313333334</v>
       </c>
       <c r="O74">
-        <v>-4.873932917333333</v>
+        <v>-4.985310689333334</v>
       </c>
       <c r="P74">
-        <v>-17.28030761599999</v>
+        <v>-17.675192444</v>
       </c>
       <c r="Q74">
-        <v>-8.410307615999995</v>
+        <v>-8.805192444000005</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1311840764011999</v>
+        <v>0.1343464496012443</v>
       </c>
       <c r="T74">
-        <v>1.971918623584293</v>
+        <v>2.044952646680007</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08628774722695152</v>
+        <v>0.08510572329233573</v>
       </c>
       <c r="W74">
-        <v>0.2154533492038848</v>
+        <v>0.2157320704476672</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3922170328497796</v>
+        <v>0.3868441967833443</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1937579528191331</v>
+        <v>0.1956579528191331</v>
       </c>
       <c r="C75">
-        <v>-107.4036813909045</v>
+        <v>-109.8806732560474</v>
       </c>
       <c r="D75">
-        <v>26.02731860909548</v>
+        <v>25.69732674395258</v>
       </c>
       <c r="E75">
-        <v>51.931</v>
+        <v>54.07799999999999</v>
       </c>
       <c r="F75">
-        <v>156.731</v>
+        <v>158.878</v>
       </c>
       <c r="G75">
         <v>23.3</v>
@@ -7437,37 +7437,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M75">
-        <v>36.9571698</v>
+        <v>37.46343239999999</v>
       </c>
       <c r="N75">
-        <v>-22.66050313333334</v>
+        <v>-23.16676573333333</v>
       </c>
       <c r="O75">
-        <v>-4.985310689333334</v>
+        <v>-5.096688461333332</v>
       </c>
       <c r="P75">
-        <v>-17.675192444</v>
+        <v>-18.070077272</v>
       </c>
       <c r="Q75">
-        <v>-8.805192444000005</v>
+        <v>-9.200077271999996</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1343464496012443</v>
+        <v>0.1377520822782152</v>
       </c>
       <c r="T75">
-        <v>2.044952646680007</v>
+        <v>2.123604671552315</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08510572329233573</v>
+        <v>0.08395564595054743</v>
       </c>
       <c r="W75">
-        <v>0.2157320704476672</v>
+        <v>0.2160032586848609</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3868441967833443</v>
+        <v>0.3816165725024883</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1956579528191331</v>
+        <v>0.197557952819133</v>
       </c>
       <c r="C76">
-        <v>-109.8806732560474</v>
+        <v>-112.3494021665032</v>
       </c>
       <c r="D76">
-        <v>25.69732674395258</v>
+        <v>25.37559783349674</v>
       </c>
       <c r="E76">
-        <v>54.07799999999999</v>
+        <v>56.22499999999998</v>
       </c>
       <c r="F76">
-        <v>158.878</v>
+        <v>161.025</v>
       </c>
       <c r="G76">
         <v>23.3</v>
@@ -7519,37 +7519,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M76">
-        <v>37.46343239999999</v>
+        <v>37.96969499999999</v>
       </c>
       <c r="N76">
-        <v>-23.16676573333333</v>
+        <v>-23.67302833333333</v>
       </c>
       <c r="O76">
-        <v>-5.096688461333332</v>
+        <v>-5.208066233333332</v>
       </c>
       <c r="P76">
-        <v>-18.070077272</v>
+        <v>-18.46496209999999</v>
       </c>
       <c r="Q76">
-        <v>-9.200077271999996</v>
+        <v>-9.594962099999995</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1377520822782152</v>
+        <v>0.1414301655693438</v>
       </c>
       <c r="T76">
-        <v>2.123604671552315</v>
+        <v>2.208548858414408</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08395564595054743</v>
+        <v>0.08283623733787347</v>
       </c>
       <c r="W76">
-        <v>0.2160032586848609</v>
+        <v>0.2162672152357294</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3816165725024883</v>
+        <v>0.3765283515357885</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.197557952819133</v>
+        <v>0.199457952819133</v>
       </c>
       <c r="C77">
-        <v>-112.3494021665032</v>
+        <v>-114.810174639708</v>
       </c>
       <c r="D77">
-        <v>25.37559783349674</v>
+        <v>25.06182536029195</v>
       </c>
       <c r="E77">
-        <v>56.22499999999998</v>
+        <v>58.372</v>
       </c>
       <c r="F77">
-        <v>161.025</v>
+        <v>163.172</v>
       </c>
       <c r="G77">
         <v>23.3</v>
@@ -7601,37 +7601,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M77">
-        <v>37.96969499999999</v>
+        <v>38.4759576</v>
       </c>
       <c r="N77">
-        <v>-23.67302833333333</v>
+        <v>-24.17929093333333</v>
       </c>
       <c r="O77">
-        <v>-5.208066233333332</v>
+        <v>-5.319444005333334</v>
       </c>
       <c r="P77">
-        <v>-18.46496209999999</v>
+        <v>-18.859846928</v>
       </c>
       <c r="Q77">
-        <v>-9.594962099999995</v>
+        <v>-9.989846928</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1414301655693438</v>
+        <v>0.1454147558013998</v>
       </c>
       <c r="T77">
-        <v>2.208548858414408</v>
+        <v>2.300571727515008</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08283623733787347</v>
+        <v>0.08174628684658565</v>
       </c>
       <c r="W77">
-        <v>0.2162672152357294</v>
+        <v>0.2165242255615751</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3765283515357885</v>
+        <v>0.3715740311208438</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.199457952819133</v>
+        <v>0.201357952819133</v>
       </c>
       <c r="C78">
-        <v>-114.810174639708</v>
+        <v>-117.2632822177624</v>
       </c>
       <c r="D78">
-        <v>25.06182536029195</v>
+        <v>24.75571778223762</v>
       </c>
       <c r="E78">
-        <v>58.372</v>
+        <v>60.51899999999999</v>
       </c>
       <c r="F78">
-        <v>163.172</v>
+        <v>165.319</v>
       </c>
       <c r="G78">
         <v>23.3</v>
@@ -7683,37 +7683,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M78">
-        <v>38.4759576</v>
+        <v>38.9822202</v>
       </c>
       <c r="N78">
-        <v>-24.17929093333333</v>
+        <v>-24.68555353333333</v>
       </c>
       <c r="O78">
-        <v>-5.319444005333334</v>
+        <v>-5.430821777333334</v>
       </c>
       <c r="P78">
-        <v>-18.859846928</v>
+        <v>-19.254731756</v>
       </c>
       <c r="Q78">
-        <v>-9.989846928</v>
+        <v>-10.384731756</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1454147558013998</v>
+        <v>0.1497458321405911</v>
       </c>
       <c r="T78">
-        <v>2.300571727515008</v>
+        <v>2.400596585233052</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08174628684658565</v>
+        <v>0.08068464675766895</v>
       </c>
       <c r="W78">
-        <v>0.2165242255615751</v>
+        <v>0.2167745602945417</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3715740311208438</v>
+        <v>0.3667483943530406</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.201357952819133</v>
+        <v>0.2032579528191331</v>
       </c>
       <c r="C79">
-        <v>-117.2632822177624</v>
+        <v>-119.7090023709469</v>
       </c>
       <c r="D79">
-        <v>24.75571778223762</v>
+        <v>24.4569976290531</v>
       </c>
       <c r="E79">
-        <v>60.51899999999999</v>
+        <v>62.66600000000001</v>
       </c>
       <c r="F79">
-        <v>165.319</v>
+        <v>167.466</v>
       </c>
       <c r="G79">
         <v>23.3</v>
@@ -7765,37 +7765,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M79">
-        <v>38.9822202</v>
+        <v>39.48848280000001</v>
       </c>
       <c r="N79">
-        <v>-24.68555353333333</v>
+        <v>-25.19181613333334</v>
       </c>
       <c r="O79">
-        <v>-5.430821777333334</v>
+        <v>-5.542199549333334</v>
       </c>
       <c r="P79">
-        <v>-19.254731756</v>
+        <v>-19.64961658400001</v>
       </c>
       <c r="Q79">
-        <v>-10.384731756</v>
+        <v>-10.77961658400001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1497458321405911</v>
+        <v>0.1544706426924362</v>
       </c>
       <c r="T79">
-        <v>2.400596585233052</v>
+        <v>2.509714611834555</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08068464675766895</v>
+        <v>0.07965022820949369</v>
       </c>
       <c r="W79">
-        <v>0.2167745602945417</v>
+        <v>0.2170184761882014</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3667483943530406</v>
+        <v>0.362046491861335</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2032579528191331</v>
+        <v>0.2051579528191331</v>
       </c>
       <c r="C80">
-        <v>-119.7090023709469</v>
+        <v>-122.1475993366028</v>
       </c>
       <c r="D80">
-        <v>24.4569976290531</v>
+        <v>24.16540066339716</v>
       </c>
       <c r="E80">
-        <v>62.66600000000001</v>
+        <v>64.813</v>
       </c>
       <c r="F80">
-        <v>167.466</v>
+        <v>169.613</v>
       </c>
       <c r="G80">
         <v>23.3</v>
@@ -7847,37 +7847,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M80">
-        <v>39.48848280000001</v>
+        <v>39.9947454</v>
       </c>
       <c r="N80">
-        <v>-25.19181613333334</v>
+        <v>-25.69807873333333</v>
       </c>
       <c r="O80">
-        <v>-5.542199549333334</v>
+        <v>-5.653577321333334</v>
       </c>
       <c r="P80">
-        <v>-19.64961658400001</v>
+        <v>-20.044501412</v>
       </c>
       <c r="Q80">
-        <v>-10.77961658400001</v>
+        <v>-11.174501412</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1544706426924362</v>
+        <v>0.1596454352015998</v>
       </c>
       <c r="T80">
-        <v>2.509714611834555</v>
+        <v>2.629224831445724</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07965022820949369</v>
+        <v>0.07864199747266468</v>
       </c>
       <c r="W80">
-        <v>0.2170184761882014</v>
+        <v>0.2172562169959457</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.362046491861335</v>
+        <v>0.3574636248757485</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2051579528191331</v>
+        <v>0.2070579528191331</v>
       </c>
       <c r="C81">
-        <v>-122.1475993366028</v>
+        <v>-124.5793248987086</v>
       </c>
       <c r="D81">
-        <v>24.16540066339716</v>
+        <v>23.8806751012914</v>
       </c>
       <c r="E81">
-        <v>64.813</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="F81">
-        <v>169.613</v>
+        <v>171.76</v>
       </c>
       <c r="G81">
         <v>23.3</v>
@@ -7929,37 +7929,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M81">
-        <v>39.9947454</v>
+        <v>40.501008</v>
       </c>
       <c r="N81">
-        <v>-25.69807873333333</v>
+        <v>-26.20434133333333</v>
       </c>
       <c r="O81">
-        <v>-5.653577321333334</v>
+        <v>-5.764955093333333</v>
       </c>
       <c r="P81">
-        <v>-20.044501412</v>
+        <v>-20.43938624</v>
       </c>
       <c r="Q81">
-        <v>-11.174501412</v>
+        <v>-11.56938624</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1596454352015998</v>
+        <v>0.1653377069616798</v>
       </c>
       <c r="T81">
-        <v>2.629224831445724</v>
+        <v>2.76068607301801</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07864199747266468</v>
+        <v>0.07765897250425637</v>
       </c>
       <c r="W81">
-        <v>0.2172562169959457</v>
+        <v>0.2174880142834964</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3574636248757485</v>
+        <v>0.3529953295648016</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2070579528191331</v>
+        <v>0.2089579528191331</v>
       </c>
       <c r="C82">
-        <v>-124.5793248987086</v>
+        <v>-127.0044191129867</v>
       </c>
       <c r="D82">
-        <v>23.8806751012914</v>
+        <v>23.60258088701333</v>
       </c>
       <c r="E82">
-        <v>66.95999999999999</v>
+        <v>69.10700000000001</v>
       </c>
       <c r="F82">
-        <v>171.76</v>
+        <v>173.907</v>
       </c>
       <c r="G82">
         <v>23.3</v>
@@ -8011,37 +8011,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M82">
-        <v>40.501008</v>
+        <v>41.00727060000001</v>
       </c>
       <c r="N82">
-        <v>-26.20434133333333</v>
+        <v>-26.71060393333334</v>
       </c>
       <c r="O82">
-        <v>-5.764955093333333</v>
+        <v>-5.876332865333334</v>
       </c>
       <c r="P82">
-        <v>-20.43938624</v>
+        <v>-20.834271068</v>
       </c>
       <c r="Q82">
-        <v>-11.56938624</v>
+        <v>-11.964271068</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1653377069616798</v>
+        <v>0.1716291652228209</v>
       </c>
       <c r="T82">
-        <v>2.76068607301801</v>
+        <v>2.905985340018959</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07765897250425637</v>
+        <v>0.07670021975729022</v>
       </c>
       <c r="W82">
-        <v>0.2174880142834964</v>
+        <v>0.217714088181231</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3529953295648016</v>
+        <v>0.3486373625331374</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2089579528191331</v>
+        <v>0.2108579528191331</v>
       </c>
       <c r="C83">
-        <v>-127.0044191129867</v>
+        <v>-129.4231109819296</v>
       </c>
       <c r="D83">
-        <v>23.60258088701333</v>
+        <v>23.3308890180704</v>
       </c>
       <c r="E83">
-        <v>69.10700000000001</v>
+        <v>71.254</v>
       </c>
       <c r="F83">
-        <v>173.907</v>
+        <v>176.054</v>
       </c>
       <c r="G83">
         <v>23.3</v>
@@ -8093,37 +8093,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M83">
-        <v>41.00727060000001</v>
+        <v>41.5135332</v>
       </c>
       <c r="N83">
-        <v>-26.71060393333334</v>
+        <v>-27.21686653333334</v>
       </c>
       <c r="O83">
-        <v>-5.876332865333334</v>
+        <v>-5.987710637333334</v>
       </c>
       <c r="P83">
-        <v>-20.834271068</v>
+        <v>-21.229155896</v>
       </c>
       <c r="Q83">
-        <v>-11.964271068</v>
+        <v>-12.359155896</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1716291652228209</v>
+        <v>0.1786196744018665</v>
       </c>
       <c r="T83">
-        <v>2.905985340018959</v>
+        <v>3.067428970020012</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07670021975729022</v>
+        <v>0.07576485122366475</v>
       </c>
       <c r="W83">
-        <v>0.217714088181231</v>
+        <v>0.2179346480814599</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3486373625331374</v>
+        <v>0.3443856873802942</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2108579528191331</v>
+        <v>0.2127579528191331</v>
       </c>
       <c r="C84">
-        <v>-129.4231109819296</v>
+        <v>-131.8356190837351</v>
       </c>
       <c r="D84">
-        <v>23.3308890180704</v>
+        <v>23.06538091626493</v>
       </c>
       <c r="E84">
-        <v>71.254</v>
+        <v>73.401</v>
       </c>
       <c r="F84">
-        <v>176.054</v>
+        <v>178.201</v>
       </c>
       <c r="G84">
         <v>23.3</v>
@@ -8175,37 +8175,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M84">
-        <v>41.5135332</v>
+        <v>42.0197958</v>
       </c>
       <c r="N84">
-        <v>-27.21686653333334</v>
+        <v>-27.72312913333333</v>
       </c>
       <c r="O84">
-        <v>-5.987710637333334</v>
+        <v>-6.099088409333333</v>
       </c>
       <c r="P84">
-        <v>-21.229155896</v>
+        <v>-21.624040724</v>
       </c>
       <c r="Q84">
-        <v>-12.359155896</v>
+        <v>-12.754040724</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1786196744018665</v>
+        <v>0.1864325964255057</v>
       </c>
       <c r="T84">
-        <v>3.067428970020012</v>
+        <v>3.247865968256483</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07576485122366475</v>
+        <v>0.07485202169084951</v>
       </c>
       <c r="W84">
-        <v>0.2179346480814599</v>
+        <v>0.2181498932852977</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3443856873802942</v>
+        <v>0.3402364622311341</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2127579528191331</v>
+        <v>0.2146579528191331</v>
       </c>
       <c r="C85">
-        <v>-131.8356190837351</v>
+        <v>-134.2421521587798</v>
       </c>
       <c r="D85">
-        <v>23.06538091626493</v>
+        <v>22.80584784122023</v>
       </c>
       <c r="E85">
-        <v>73.401</v>
+        <v>75.54800000000002</v>
       </c>
       <c r="F85">
-        <v>178.201</v>
+        <v>180.348</v>
       </c>
       <c r="G85">
         <v>23.3</v>
@@ -8257,37 +8257,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M85">
-        <v>42.0197958</v>
+        <v>42.5260584</v>
       </c>
       <c r="N85">
-        <v>-27.72312913333333</v>
+        <v>-28.22939173333334</v>
       </c>
       <c r="O85">
-        <v>-6.099088409333333</v>
+        <v>-6.210466181333334</v>
       </c>
       <c r="P85">
-        <v>-21.624040724</v>
+        <v>-22.018925552</v>
       </c>
       <c r="Q85">
-        <v>-12.754040724</v>
+        <v>-13.148925552</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1864325964255057</v>
+        <v>0.1952221337020998</v>
       </c>
       <c r="T85">
-        <v>3.247865968256483</v>
+        <v>3.450857591272514</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07485202169084951</v>
+        <v>0.07396092619452986</v>
       </c>
       <c r="W85">
-        <v>0.2181498932852977</v>
+        <v>0.2183600136033299</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3402364622311341</v>
+        <v>0.3361860281569539</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2146579528191331</v>
+        <v>0.216557952819133</v>
       </c>
       <c r="C86">
-        <v>-134.2421521587798</v>
+        <v>-136.6429096569398</v>
       </c>
       <c r="D86">
-        <v>22.80584784122023</v>
+        <v>22.55209034306016</v>
       </c>
       <c r="E86">
-        <v>75.54799999999999</v>
+        <v>77.69499999999998</v>
       </c>
       <c r="F86">
-        <v>180.348</v>
+        <v>182.495</v>
       </c>
       <c r="G86">
         <v>23.3</v>
@@ -8339,37 +8339,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M86">
-        <v>42.5260584</v>
+        <v>43.032321</v>
       </c>
       <c r="N86">
-        <v>-28.22939173333333</v>
+        <v>-28.73565433333333</v>
       </c>
       <c r="O86">
-        <v>-6.210466181333333</v>
+        <v>-6.321843953333333</v>
       </c>
       <c r="P86">
-        <v>-22.018925552</v>
+        <v>-22.41381038</v>
       </c>
       <c r="Q86">
-        <v>-13.148925552</v>
+        <v>-13.54381038</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1952221337020997</v>
+        <v>0.2051836092822397</v>
       </c>
       <c r="T86">
-        <v>3.450857591272511</v>
+        <v>3.680914764024013</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07396092619452987</v>
+        <v>0.07309079765106483</v>
       </c>
       <c r="W86">
-        <v>0.2183600136033299</v>
+        <v>0.2185651899138789</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.336186028156954</v>
+        <v>0.3322308984139309</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.216557952819133</v>
+        <v>0.218457952819133</v>
       </c>
       <c r="C87">
-        <v>-136.6429096569398</v>
+        <v>-139.0380822487735</v>
       </c>
       <c r="D87">
-        <v>22.55209034306016</v>
+        <v>22.30391775122652</v>
       </c>
       <c r="E87">
-        <v>77.69499999999998</v>
+        <v>79.842</v>
       </c>
       <c r="F87">
-        <v>182.495</v>
+        <v>184.642</v>
       </c>
       <c r="G87">
         <v>23.3</v>
@@ -8421,37 +8421,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M87">
-        <v>43.032321</v>
+        <v>43.5385836</v>
       </c>
       <c r="N87">
-        <v>-28.73565433333333</v>
+        <v>-29.24191693333334</v>
       </c>
       <c r="O87">
-        <v>-6.321843953333333</v>
+        <v>-6.433221725333333</v>
       </c>
       <c r="P87">
-        <v>-22.41381038</v>
+        <v>-22.808695208</v>
       </c>
       <c r="Q87">
-        <v>-13.54381038</v>
+        <v>-13.938695208</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2051836092822397</v>
+        <v>0.2165681528023997</v>
       </c>
       <c r="T87">
-        <v>3.680914764024013</v>
+        <v>3.943837247168585</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07309079765106483</v>
+        <v>0.07224090465512219</v>
       </c>
       <c r="W87">
-        <v>0.2185651899138789</v>
+        <v>0.2187655946823222</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3322308984139309</v>
+        <v>0.3283677484323736</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.218457952819133</v>
+        <v>0.2203579528191331</v>
       </c>
       <c r="C88">
-        <v>-139.0380822487735</v>
+        <v>-141.4278523033194</v>
       </c>
       <c r="D88">
-        <v>22.30391775122652</v>
+        <v>22.06114769668057</v>
       </c>
       <c r="E88">
-        <v>79.842</v>
+        <v>81.98899999999999</v>
       </c>
       <c r="F88">
-        <v>184.642</v>
+        <v>186.789</v>
       </c>
       <c r="G88">
         <v>23.3</v>
@@ -8503,37 +8503,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M88">
-        <v>43.5385836</v>
+        <v>44.0448462</v>
       </c>
       <c r="N88">
-        <v>-29.24191693333334</v>
+        <v>-29.74817953333334</v>
       </c>
       <c r="O88">
-        <v>-6.433221725333333</v>
+        <v>-6.544599497333333</v>
       </c>
       <c r="P88">
-        <v>-22.808695208</v>
+        <v>-23.203580036</v>
       </c>
       <c r="Q88">
-        <v>-13.938695208</v>
+        <v>-14.333580036</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2165681528023997</v>
+        <v>0.2297041645564304</v>
       </c>
       <c r="T88">
-        <v>3.943837247168585</v>
+        <v>4.24720934310463</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07224090465512219</v>
+        <v>0.07141054942920125</v>
       </c>
       <c r="W88">
-        <v>0.2187655946823222</v>
+        <v>0.2189613924445944</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3283677484323736</v>
+        <v>0.3245934064963693</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2203579528191331</v>
+        <v>0.222257952819133</v>
       </c>
       <c r="C89">
-        <v>-141.4278523033194</v>
+        <v>-143.8123943350274</v>
       </c>
       <c r="D89">
-        <v>22.06114769668057</v>
+        <v>21.82360566497256</v>
       </c>
       <c r="E89">
-        <v>81.98899999999999</v>
+        <v>84.13599999999998</v>
       </c>
       <c r="F89">
-        <v>186.789</v>
+        <v>188.936</v>
       </c>
       <c r="G89">
         <v>23.3</v>
@@ -8585,37 +8585,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M89">
-        <v>44.0448462</v>
+        <v>44.55110879999999</v>
       </c>
       <c r="N89">
-        <v>-29.74817953333334</v>
+        <v>-30.25444213333333</v>
       </c>
       <c r="O89">
-        <v>-6.544599497333333</v>
+        <v>-6.655977269333332</v>
       </c>
       <c r="P89">
-        <v>-23.203580036</v>
+        <v>-23.598464864</v>
       </c>
       <c r="Q89">
-        <v>-14.333580036</v>
+        <v>-14.728464864</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2297041645564304</v>
+        <v>0.2450295116027997</v>
       </c>
       <c r="T89">
-        <v>4.24720934310463</v>
+        <v>4.601143455030017</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07141054942920125</v>
+        <v>0.07059906591296035</v>
       </c>
       <c r="W89">
-        <v>0.2189613924445944</v>
+        <v>0.2191527402577239</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3245934064963693</v>
+        <v>0.3209048450589106</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.222257952819133</v>
+        <v>0.2241579528191331</v>
       </c>
       <c r="C90">
-        <v>-143.8123943350274</v>
+        <v>-146.1918754221225</v>
       </c>
       <c r="D90">
-        <v>21.82360566497256</v>
+        <v>21.59112457787746</v>
       </c>
       <c r="E90">
-        <v>84.13599999999998</v>
+        <v>86.283</v>
       </c>
       <c r="F90">
-        <v>188.936</v>
+        <v>191.083</v>
       </c>
       <c r="G90">
         <v>23.3</v>
@@ -8667,37 +8667,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M90">
-        <v>44.55110879999999</v>
+        <v>45.0573714</v>
       </c>
       <c r="N90">
-        <v>-30.25444213333333</v>
+        <v>-30.76070473333333</v>
       </c>
       <c r="O90">
-        <v>-6.655977269333332</v>
+        <v>-6.767355041333333</v>
       </c>
       <c r="P90">
-        <v>-23.598464864</v>
+        <v>-23.993349692</v>
       </c>
       <c r="Q90">
-        <v>-14.728464864</v>
+        <v>-15.123349692</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2450295116027997</v>
+        <v>0.2631412853848724</v>
       </c>
       <c r="T90">
-        <v>4.601143455030017</v>
+        <v>5.01942922366911</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07059906591296035</v>
+        <v>0.06980581798135403</v>
       </c>
       <c r="W90">
-        <v>0.2191527402577239</v>
+        <v>0.2193397881199967</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3209048450589106</v>
+        <v>0.3172991726425183</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2241579528191331</v>
+        <v>0.226057952819133</v>
       </c>
       <c r="C91">
-        <v>-146.1918754221225</v>
+        <v>-148.5664555985108</v>
       </c>
       <c r="D91">
-        <v>21.59112457787746</v>
+        <v>21.36354440148919</v>
       </c>
       <c r="E91">
-        <v>86.283</v>
+        <v>88.42999999999999</v>
       </c>
       <c r="F91">
-        <v>191.083</v>
+        <v>193.23</v>
       </c>
       <c r="G91">
         <v>23.3</v>
@@ -8749,37 +8749,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M91">
-        <v>45.0573714</v>
+        <v>45.563634</v>
       </c>
       <c r="N91">
-        <v>-30.76070473333333</v>
+        <v>-31.26696733333333</v>
       </c>
       <c r="O91">
-        <v>-6.767355041333333</v>
+        <v>-6.878732813333333</v>
       </c>
       <c r="P91">
-        <v>-23.993349692</v>
+        <v>-24.38823452</v>
       </c>
       <c r="Q91">
-        <v>-15.123349692</v>
+        <v>-15.51823452</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2631412853848724</v>
+        <v>0.2848754139233596</v>
       </c>
       <c r="T91">
-        <v>5.01942922366911</v>
+        <v>5.521372146036021</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06980581798135403</v>
+        <v>0.06903019778156121</v>
       </c>
       <c r="W91">
-        <v>0.2193397881199967</v>
+        <v>0.2195226793631079</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3172991726425183</v>
+        <v>0.3137736262798236</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.226057952819133</v>
+        <v>0.2279579528191331</v>
       </c>
       <c r="C92">
-        <v>-148.5664555985108</v>
+        <v>-150.9362882211585</v>
       </c>
       <c r="D92">
-        <v>21.36354440148919</v>
+        <v>21.14071177884145</v>
       </c>
       <c r="E92">
-        <v>88.42999999999999</v>
+        <v>90.57700000000001</v>
       </c>
       <c r="F92">
-        <v>193.23</v>
+        <v>195.377</v>
       </c>
       <c r="G92">
         <v>23.3</v>
@@ -8831,37 +8831,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M92">
-        <v>45.563634</v>
+        <v>46.06989660000001</v>
       </c>
       <c r="N92">
-        <v>-31.26696733333333</v>
+        <v>-31.77322993333334</v>
       </c>
       <c r="O92">
-        <v>-6.878732813333333</v>
+        <v>-6.990110585333335</v>
       </c>
       <c r="P92">
-        <v>-24.38823452</v>
+        <v>-24.78311934800001</v>
       </c>
       <c r="Q92">
-        <v>-15.51823452</v>
+        <v>-15.91311934800001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2848754139233596</v>
+        <v>0.311439348803733</v>
       </c>
       <c r="T92">
-        <v>5.521372146036021</v>
+        <v>6.134857940040024</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06903019778156121</v>
+        <v>0.06827162417956603</v>
       </c>
       <c r="W92">
-        <v>0.2195226793631079</v>
+        <v>0.2197015510184583</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3137736262798236</v>
+        <v>0.3103255644525728</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2279579528191331</v>
+        <v>0.2298579528191331</v>
       </c>
       <c r="C93">
-        <v>-150.9362882211585</v>
+        <v>-153.301520314717</v>
       </c>
       <c r="D93">
-        <v>21.14071177884145</v>
+        <v>20.92247968528303</v>
       </c>
       <c r="E93">
-        <v>90.57700000000001</v>
+        <v>92.724</v>
       </c>
       <c r="F93">
-        <v>195.377</v>
+        <v>197.524</v>
       </c>
       <c r="G93">
         <v>23.3</v>
@@ -8913,37 +8913,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M93">
-        <v>46.06989660000001</v>
+        <v>46.5761592</v>
       </c>
       <c r="N93">
-        <v>-31.77322993333334</v>
+        <v>-32.27949253333333</v>
       </c>
       <c r="O93">
-        <v>-6.990110585333335</v>
+        <v>-7.101488357333333</v>
       </c>
       <c r="P93">
-        <v>-24.78311934800001</v>
+        <v>-25.178004176</v>
       </c>
       <c r="Q93">
-        <v>-15.91311934800001</v>
+        <v>-16.308004176</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.311439348803733</v>
+        <v>0.3446442674041997</v>
       </c>
       <c r="T93">
-        <v>6.134857940040024</v>
+        <v>6.901715182545028</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06827162417956603</v>
+        <v>0.06752954130804902</v>
       </c>
       <c r="W93">
-        <v>0.2197015510184583</v>
+        <v>0.219876534159562</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3103255644525728</v>
+        <v>0.3069524604911319</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2298579528191331</v>
+        <v>0.2317579528191331</v>
       </c>
       <c r="C94">
-        <v>-153.301520314717</v>
+        <v>-155.6622928950201</v>
       </c>
       <c r="D94">
-        <v>20.92247968528303</v>
+        <v>20.70870710497987</v>
       </c>
       <c r="E94">
-        <v>92.724</v>
+        <v>94.871</v>
       </c>
       <c r="F94">
-        <v>197.524</v>
+        <v>199.671</v>
       </c>
       <c r="G94">
         <v>23.3</v>
@@ -8995,37 +8995,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M94">
-        <v>46.5761592</v>
+        <v>47.0824218</v>
       </c>
       <c r="N94">
-        <v>-32.27949253333333</v>
+        <v>-32.78575513333333</v>
       </c>
       <c r="O94">
-        <v>-7.101488357333333</v>
+        <v>-7.212866129333333</v>
       </c>
       <c r="P94">
-        <v>-25.178004176</v>
+        <v>-25.572889004</v>
       </c>
       <c r="Q94">
-        <v>-16.308004176</v>
+        <v>-16.702889004</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3446442674041997</v>
+        <v>0.3873363056047996</v>
       </c>
       <c r="T94">
-        <v>6.901715182545028</v>
+        <v>7.887674494337176</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06752954130804902</v>
+        <v>0.06680341720796246</v>
       </c>
       <c r="W94">
-        <v>0.219876534159562</v>
+        <v>0.2200477542223625</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3069524604911319</v>
+        <v>0.3036518963998294</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2317579528191331</v>
+        <v>0.233657952819133</v>
       </c>
       <c r="C95">
-        <v>-155.6622928950201</v>
+        <v>-158.0187412729514</v>
       </c>
       <c r="D95">
-        <v>20.70870710497987</v>
+        <v>20.49925872704857</v>
       </c>
       <c r="E95">
-        <v>94.871</v>
+        <v>97.01800000000001</v>
       </c>
       <c r="F95">
-        <v>199.671</v>
+        <v>201.818</v>
       </c>
       <c r="G95">
         <v>23.3</v>
@@ -9077,37 +9077,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M95">
-        <v>47.0824218</v>
+        <v>47.58868440000001</v>
       </c>
       <c r="N95">
-        <v>-32.78575513333333</v>
+        <v>-33.29201773333334</v>
       </c>
       <c r="O95">
-        <v>-7.212866129333333</v>
+        <v>-7.324243901333334</v>
       </c>
       <c r="P95">
-        <v>-25.572889004</v>
+        <v>-25.96777383200001</v>
       </c>
       <c r="Q95">
-        <v>-16.702889004</v>
+        <v>-17.09777383200001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3873363056047996</v>
+        <v>0.4442590232055997</v>
       </c>
       <c r="T95">
-        <v>7.887674494337176</v>
+        <v>9.202286910060041</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06680341720796246</v>
+        <v>0.06609274255681392</v>
       </c>
       <c r="W95">
-        <v>0.2200477542223625</v>
+        <v>0.2202153313051033</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3036518963998294</v>
+        <v>0.3004215570764269</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.233657952819133</v>
+        <v>0.2355579528191331</v>
       </c>
       <c r="C96">
-        <v>-158.0187412729514</v>
+        <v>-160.3709953400551</v>
       </c>
       <c r="D96">
-        <v>20.49925872704857</v>
+        <v>20.2940046599449</v>
       </c>
       <c r="E96">
-        <v>97.01800000000001</v>
+        <v>99.16500000000001</v>
       </c>
       <c r="F96">
-        <v>201.818</v>
+        <v>203.965</v>
       </c>
       <c r="G96">
         <v>23.3</v>
@@ -9159,37 +9159,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M96">
-        <v>47.58868440000001</v>
+        <v>48.094947</v>
       </c>
       <c r="N96">
-        <v>-33.29201773333334</v>
+        <v>-33.79828033333334</v>
       </c>
       <c r="O96">
-        <v>-7.324243901333334</v>
+        <v>-7.435621673333334</v>
       </c>
       <c r="P96">
-        <v>-25.96777383200001</v>
+        <v>-26.36265866</v>
       </c>
       <c r="Q96">
-        <v>-17.09777383200001</v>
+        <v>-17.49265866</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4442590232055997</v>
+        <v>0.5239508278467199</v>
       </c>
       <c r="T96">
-        <v>9.202286910060041</v>
+        <v>11.04274429207205</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06609274255681392</v>
+        <v>0.06539702947726851</v>
       </c>
       <c r="W96">
-        <v>0.2202153313051033</v>
+        <v>0.2203793804492601</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3004215570764269</v>
+        <v>0.297259224896675</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2355579528191331</v>
+        <v>0.237457952819133</v>
       </c>
       <c r="C97">
-        <v>-160.3709953400551</v>
+        <v>-162.7191798371591</v>
       </c>
       <c r="D97">
-        <v>20.2940046599449</v>
+        <v>20.09282016284093</v>
       </c>
       <c r="E97">
-        <v>99.16500000000001</v>
+        <v>101.312</v>
       </c>
       <c r="F97">
-        <v>203.965</v>
+        <v>206.112</v>
       </c>
       <c r="G97">
         <v>23.3</v>
@@ -9241,37 +9241,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M97">
-        <v>48.094947</v>
+        <v>48.6012096</v>
       </c>
       <c r="N97">
-        <v>-33.79828033333334</v>
+        <v>-34.30454293333334</v>
       </c>
       <c r="O97">
-        <v>-7.435621673333334</v>
+        <v>-7.546999445333334</v>
       </c>
       <c r="P97">
-        <v>-26.36265866</v>
+        <v>-26.757543488</v>
       </c>
       <c r="Q97">
-        <v>-17.49265866</v>
+        <v>-17.88754348800001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5239508278467199</v>
+        <v>0.6434885348084001</v>
       </c>
       <c r="T97">
-        <v>11.04274429207205</v>
+        <v>13.80343036509007</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06539702947726851</v>
+        <v>0.06471581042021364</v>
       </c>
       <c r="W97">
-        <v>0.2203793804492601</v>
+        <v>0.2205400119029136</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.297259224896675</v>
+        <v>0.2941627746373346</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.237457952819133</v>
+        <v>0.2393579528191331</v>
       </c>
       <c r="C98">
-        <v>-162.7191798371591</v>
+        <v>-165.0634146071769</v>
       </c>
       <c r="D98">
-        <v>20.09282016284093</v>
+        <v>19.89558539282312</v>
       </c>
       <c r="E98">
-        <v>101.312</v>
+        <v>103.459</v>
       </c>
       <c r="F98">
-        <v>206.112</v>
+        <v>208.259</v>
       </c>
       <c r="G98">
         <v>23.3</v>
@@ -9323,37 +9323,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M98">
-        <v>48.6012096</v>
+        <v>49.1074722</v>
       </c>
       <c r="N98">
-        <v>-34.30454293333334</v>
+        <v>-34.81080553333333</v>
       </c>
       <c r="O98">
-        <v>-7.546999445333334</v>
+        <v>-7.658377217333332</v>
       </c>
       <c r="P98">
-        <v>-26.757543488</v>
+        <v>-27.152428316</v>
       </c>
       <c r="Q98">
-        <v>-17.88754348800001</v>
+        <v>-18.282428316</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6434885348083984</v>
+        <v>0.8427180464111981</v>
       </c>
       <c r="T98">
-        <v>13.80343036509004</v>
+        <v>18.40457382012005</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06471581042021364</v>
+        <v>0.06404863711691247</v>
       </c>
       <c r="W98">
-        <v>0.2205400119029136</v>
+        <v>0.2206973313678321</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2941627746373346</v>
+        <v>0.2911301687132385</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2393579528191331</v>
+        <v>0.2412579528191331</v>
       </c>
       <c r="C99">
-        <v>-165.0634146071769</v>
+        <v>-167.4038148331648</v>
       </c>
       <c r="D99">
-        <v>19.89558539282312</v>
+        <v>19.70218516683518</v>
       </c>
       <c r="E99">
-        <v>103.459</v>
+        <v>105.606</v>
       </c>
       <c r="F99">
-        <v>208.259</v>
+        <v>210.406</v>
       </c>
       <c r="G99">
         <v>23.3</v>
@@ -9405,37 +9405,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M99">
-        <v>49.1074722</v>
+        <v>49.6137348</v>
       </c>
       <c r="N99">
-        <v>-34.81080553333333</v>
+        <v>-35.31706813333333</v>
       </c>
       <c r="O99">
-        <v>-7.658377217333332</v>
+        <v>-7.769754989333332</v>
       </c>
       <c r="P99">
-        <v>-27.152428316</v>
+        <v>-27.547313144</v>
       </c>
       <c r="Q99">
-        <v>-18.282428316</v>
+        <v>-18.677313144</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8427180464111981</v>
+        <v>1.241177069616797</v>
       </c>
       <c r="T99">
-        <v>18.40457382012005</v>
+        <v>27.60686073018008</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06404863711691247</v>
+        <v>0.06339507959531132</v>
       </c>
       <c r="W99">
-        <v>0.2206973313678321</v>
+        <v>0.2208514402314256</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2911301687132385</v>
+        <v>0.2881594527059606</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2412579528191331</v>
+        <v>0.2431579528191331</v>
       </c>
       <c r="C100">
-        <v>-167.4038148331648</v>
+        <v>-169.7404912626285</v>
       </c>
       <c r="D100">
-        <v>19.70218516683518</v>
+        <v>19.51250873737152</v>
       </c>
       <c r="E100">
-        <v>105.606</v>
+        <v>107.753</v>
       </c>
       <c r="F100">
-        <v>210.406</v>
+        <v>212.553</v>
       </c>
       <c r="G100">
         <v>23.3</v>
@@ -9487,37 +9487,37 @@
         <v>14.29666666666667</v>
       </c>
       <c r="M100">
-        <v>49.6137348</v>
+        <v>50.1199974</v>
       </c>
       <c r="N100">
-        <v>-35.31706813333333</v>
+        <v>-35.82333073333334</v>
       </c>
       <c r="O100">
-        <v>-7.769754989333332</v>
+        <v>-7.881132761333334</v>
       </c>
       <c r="P100">
-        <v>-27.547313144</v>
+        <v>-27.942197972</v>
       </c>
       <c r="Q100">
-        <v>-18.677313144</v>
+        <v>-19.072197972</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.241177069616797</v>
+        <v>2.436554139233594</v>
       </c>
       <c r="T100">
-        <v>27.60686073018008</v>
+        <v>55.21372146036015</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06339507959531132</v>
+        <v>0.06275472525596475</v>
       </c>
       <c r="W100">
-        <v>0.2208514402314256</v>
+        <v>0.2210024357846435</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2881594527059606</v>
+        <v>0.285248751163476</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2431579528191331</v>
-      </c>
-      <c r="C101">
-        <v>-169.7404912626285</v>
-      </c>
-      <c r="D101">
-        <v>19.51250873737152</v>
-      </c>
-      <c r="E101">
-        <v>107.753</v>
-      </c>
-      <c r="F101">
-        <v>212.553</v>
-      </c>
-      <c r="G101">
-        <v>23.3</v>
-      </c>
-      <c r="H101">
-        <v>109.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>23.16666666666667</v>
-      </c>
-      <c r="K101">
-        <v>8.869999999999999</v>
-      </c>
-      <c r="L101">
-        <v>14.29666666666667</v>
-      </c>
-      <c r="M101">
-        <v>50.1199974</v>
-      </c>
-      <c r="N101">
-        <v>-35.82333073333334</v>
-      </c>
-      <c r="O101">
-        <v>-7.881132761333334</v>
-      </c>
-      <c r="P101">
-        <v>-27.942197972</v>
-      </c>
-      <c r="Q101">
-        <v>-19.072197972</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.436554139233594</v>
-      </c>
-      <c r="T101">
-        <v>55.21372146036015</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06275472525596475</v>
-      </c>
-      <c r="W101">
-        <v>0.2210024357846435</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.285248751163476</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
